--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -557,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-206.9680000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.55167e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-83.005</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.02468063230052142</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7223507722953233</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.725813518465618</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.027474133888236</v>
+      </c>
+      <c r="J2" t="n">
+        <v>36.66260068243022</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.39461527861948</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 21.976x + -12302.187</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>484.6443158837664</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>19228163.5771528</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.107426050646521e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9269404206140992</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-180.5890000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.53626e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.389</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3367499908956064</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.057839843674871</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.803518104362572</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.921904618626211</v>
+      </c>
+      <c r="J3" t="n">
+        <v>42.04387526295907</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.67246975244326</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 24.603x + -13530.070</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>477.610994005233</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>21988711.72870108</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.915264688983131e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9332769936041232</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-165.962</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.52538e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.628</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3097648922637231</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.194038854019889</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.90349027458267</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.328278826145074</v>
+      </c>
+      <c r="J4" t="n">
+        <v>47.79082171941959</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.80919344445904</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 26.140x + -14158.248</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>471.647745107983</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>198526337.7212156</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.800388687384269e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9371488906703588</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-157.841</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.52018e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.79000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6123541264162851</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9724603340802042</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.90186867911259</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.21257689290987</v>
+      </c>
+      <c r="J5" t="n">
+        <v>50.94373413765487</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.88978892630244</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 27.139x + -14484.736</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>466.0288724821089</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>214628173.4481199</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.725087214834107e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9398869957070792</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-147.615</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.51621e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.97199999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4059792016327246</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.205815406964122</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.853119470156728</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.41470305982541</v>
+      </c>
+      <c r="J6" t="n">
+        <v>57.59334697904124</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.89963115757922</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 27.267x + -14312.646</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>460.5595015553163</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>189707742.4385588</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.650324725381416e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9427200774762674</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-141.347</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.51403e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1433735274142708</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6890121806129709</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.755624509043857</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.140119830424565</v>
+      </c>
+      <c r="J7" t="n">
+        <v>60.26977227127002</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.84186301966545</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 26.536x + -13685.166</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>455.2543043898323</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>373937725.723335</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.593354466531468e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9449788471280697</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-138.753</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.50996e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.19499999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4770907877110659</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.142038105334138</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.941412193906207</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.445039549368193</v>
+      </c>
+      <c r="J8" t="n">
+        <v>62.49756038549588</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.98768526015695</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 28.461x + -14541.543</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>450.2182700074694</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>35605802.02243853</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.552398619253264e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.946501646498408</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-135.886</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.50784e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.295</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8641654975803801</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.681925911534731</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.881182622210962</v>
+      </c>
+      <c r="J9" t="n">
+        <v>57.15136736746962</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.94828864672735</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 27.914x + -14048.106</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>419.8404706492517</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3667.096846773316</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.563779375131226e-06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8250916320786401</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-125.828</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.50683e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.428</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5405883252969977</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.289522063031289</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.20111458711104</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.906911906355747</v>
+      </c>
+      <c r="J10" t="n">
+        <v>63.75158425048162</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.10017472847596</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 30.147x + -15050.771</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>437.8462330691353</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3627.702964538223</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.368033539037081e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9927233101423436</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-127.311</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.50499e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.474</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4443479644157224</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8819333715118952</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.972205003780633</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.27090028106383</v>
+      </c>
+      <c r="J11" t="n">
+        <v>66.112977970831</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.06272806623817</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 29.564x + -14576.068</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>416.803775935856</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3595.226063989589</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.234273032482909e-06</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8431218361672124</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +1192,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +1221,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-206.165</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.63713e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-82.971</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2446673036181181</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9152593731966566</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.475728564664138</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.58350096019537</v>
+      </c>
+      <c r="J2" t="n">
+        <v>35.13377296319581</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.3183707240958</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 21.350x + -11554.185</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>464.5669167919543</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>26010957.61006243</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.22327079787798e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9278647255626057</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-164.432</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.61359e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.666</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1174394053856148</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9804948457484631</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.895710746432112</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.223661102628612</v>
+      </c>
+      <c r="J3" t="n">
+        <v>48.28188471900242</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.7168858655324</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 25.082x + -12928.232</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>452.4099188020935</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>372410298.8638328</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.876169113099555e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9394832776535654</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-152.111</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.60231e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.902</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3945249287516861</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.039703151077775</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.922289695772817</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.941161553738549</v>
+      </c>
+      <c r="J4" t="n">
+        <v>49.39825433605395</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.79074755562127</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 25.922x + -13112.049</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>447.1016415901562</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>119782754.3855883</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.762666515441864e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9433403338041504</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-144.179</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.59858e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.02800000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2983369746051242</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.166156916020517</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.906211810464645</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.133035221180742</v>
+      </c>
+      <c r="J5" t="n">
+        <v>55.80784175569714</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.89770132987779</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 27.242x + -13642.246</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>421.6536137753115</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3646.089233381663</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7.572356582753557e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9195694953957788</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-139.024</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.5934e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.15600000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1619565725179314</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8900578908555352</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.963002120522948</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.227892630644385</v>
+      </c>
+      <c r="J6" t="n">
+        <v>59.04705274341686</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.87090305260176</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 26.898x + -13286.158</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>419.4976855283768</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3610.386733990646</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.490054047196679e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8208465766555824</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-138.9730000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.59097e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.205</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3174274232300977</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.119284581662237</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.157532684433602</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.12627003593697</v>
+      </c>
+      <c r="J7" t="n">
+        <v>56.87598220535168</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.95822994094442</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 28.050x + -13729.956</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>434.5103365912532</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>237920712.0999677</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.627429524089212e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9482649604966916</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-132.0040000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.58949e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.322</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.29527301740742</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8608834783723007</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.832577902255167</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.005411858417313</v>
+      </c>
+      <c r="J8" t="n">
+        <v>58.35427696913376</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.9994241946994</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 28.628x + -13847.858</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>430.4014385069506</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>133690707.1178724</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.58462807520919e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9499794626816725</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-128.7810000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.58908e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.414</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1903399503790306</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7391182737028369</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.838759607100537</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.960528352103645</v>
+      </c>
+      <c r="J9" t="n">
+        <v>58.97706243037763</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.94642311723564</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 27.889x + -13309.105</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>426.597419479509</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>235269496.7540282</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.55385637411946e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9512727297670936</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-124.763</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.58923e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.47799999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4548434509161758</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.033216064207229</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.901622655934532</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.114587355459048</v>
+      </c>
+      <c r="J10" t="n">
+        <v>62.21877932922133</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.0763815727701</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 29.774x + -14119.930</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>423.0732388556012</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>347548888.3566003</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.531580115747654e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9522221566648701</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-127.144</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.58747e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.50700000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4793058616906226</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9781788580511607</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.272633983505106</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.169025385319678</v>
+      </c>
+      <c r="J11" t="n">
+        <v>61.76704446443623</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.0241065231758</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 28.986x + -13594.470</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>419.7788442639665</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>343953770.7519221</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.516475567163398e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.952794073593166</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-122.708</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.58569e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.59099999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2590718093320893</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.156736815297303</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.110652735939223</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.435107798859895</v>
+      </c>
+      <c r="J12" t="n">
+        <v>68.94733370357062</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.08897335398645</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 29.971x + -13953.988</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>416.6056952702053</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>227892616.6250862</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.487872541914937e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9539326543696142</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-119.515</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.58524e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.646</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6126877421403306</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.277937536163018</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.070644721318421</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.553402897500489</v>
+      </c>
+      <c r="J13" t="n">
+        <v>70.52950130724689</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.1872777332149</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 31.597x + -14629.521</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>413.5657963968105</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>226496233.9343009</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.46955902032398e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9547084023002697</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-118.287</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.58622e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.68899999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6595714692082586</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.127844055161468</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.169452792553672</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.257961343934822</v>
+      </c>
+      <c r="J14" t="n">
+        <v>66.73759723354802</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.17638969275393</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 31.408x + -14410.467</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>410.5436983794904</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>224314187.4534663</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.457145011466897e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9553120612531133</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-122.745</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.58401e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.696</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.439150548159369</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.060714598872798</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.003288951588586</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.23180274514394</v>
+      </c>
+      <c r="J15" t="n">
+        <v>66.59737268294236</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.14866558434818</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 30.938x + -14057.289</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>407.6201432992885</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>167063955.362845</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.448318077236802e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9555942880773387</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-113.441</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.58322e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.803</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7505911752922237</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.508269154532604</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.421718148101912</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.818621091194854</v>
+      </c>
+      <c r="J16" t="n">
+        <v>77.15459975202229</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.27917396102336</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 33.285x + -15064.929</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>404.7066783950125</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>221101391.716084</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.418394142851484e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9568570504678677</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-115.513</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.58377e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.82599999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4027985990467226</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.097912256467849</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.020691678386705</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.908952317528506</v>
+      </c>
+      <c r="J17" t="n">
+        <v>66.89344000595914</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.21556661339291</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 32.098x + -14371.822</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>401.7001586722404</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>110069402.4358505</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.410235923320787e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9572641203275785</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-112.773</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.58486e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.893</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1085398713823943</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.043303564413204</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.999623576242072</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.415889358333452</v>
+      </c>
+      <c r="J18" t="n">
+        <v>74.74975790552804</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.15173826279475</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 30.989x + -13715.592</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>398.8003103118868</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>128816779.3976977</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.393441483635864e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9580869683607859</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-111.799</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.58477e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-84.928</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3205626207027286</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.291224340317331</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.253281407447089</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.70043654957548</v>
+      </c>
+      <c r="J19" t="n">
+        <v>77.23191125906266</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.25754330700138</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 32.872x + -14476.939</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>395.7982449995955</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>164083270.5618534</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.381774309808566e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9585904550350178</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-113.845</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.58436e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-84.955</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.06935331645685489</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.859158636493821</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.949797061530425</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.180265061292823</v>
+      </c>
+      <c r="J20" t="n">
+        <v>69.57133399299772</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.1554096332045</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 31.051x + -13502.758</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>392.7764364802676</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>551036241.5742298</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.372725973788375e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9589931484162577</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-109.122</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.58408e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.033</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.1893543576500098</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9435070427458986</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.053348758644695</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.446606744100502</v>
+      </c>
+      <c r="J21" t="n">
+        <v>78.03636334963925</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.19933669033118</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 31.809x + -13732.673</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>389.650751228401</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>162026564.2009178</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.350946982634335e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9599547698236929</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-106.591</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.58429e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.072</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5874310842980298</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.263513613460264</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.154060299690826</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.355606164787722</v>
+      </c>
+      <c r="J22" t="n">
+        <v>76.5484309646145</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.35404138940973</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 34.800x + -14964.801</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>386.626075689845</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>316634737.7815642</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.339554145431989e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9604898051126254</v>
       </c>
     </row>
   </sheetData>
@@ -718,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,8 +2430,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -853,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-159.962</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.58421e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-83.563</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1588128181484924</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9463621973551511</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.85621582417549</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.155244595789438</v>
+      </c>
+      <c r="J2" t="n">
+        <v>49.27083666727413</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.82463100570338</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 26.326x + -14156.609</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>474.940972567993</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>264274225.8072468</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.836824299068841e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9393328586338238</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-140.202</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.56412e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.821</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3411504199824087</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.057858784307783</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.853639314080611</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.053558006395951</v>
+      </c>
+      <c r="J3" t="n">
+        <v>56.02589409781329</v>
+      </c>
+      <c r="K3" t="n">
+        <v>88.01404903950372</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 28.839x + -15440.277</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>472.1234971601919</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>646073718.2939132</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.718775417466821e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9428675605193312</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-135.4440000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.55514e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.947</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1698722169417027</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9433693995119473</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.862990416107186</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.206003110955715</v>
+      </c>
+      <c r="J4" t="n">
+        <v>61.98454667126511</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.98906967238008</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 28.480x + -15076.164</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>468.2093199297603</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>512473875.0277551</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.659261456371368e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9447896744294128</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-126.332</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.54836e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.096</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2573662946045169</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.331040603851968</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.004209826464066</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.5788290429016</v>
+      </c>
+      <c r="J5" t="n">
+        <v>70.20916067189182</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.06437747428716</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 29.589x + -15503.248</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>463.6177622555926</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>60892684.35987416</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.595944668508762e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9470377830456328</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-121.292</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.544e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.226</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1992060104305761</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8659061100085119</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.61763705110867</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.900605420219045</v>
+      </c>
+      <c r="J6" t="n">
+        <v>65.15169910283635</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.02232667868783</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 28.960x + -14949.686</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>448.6815921335364</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3774.299972311237</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.307615251359875e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8542048937062423</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-114.8820000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.54052e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.318</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6404010617742047</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.244755352103616</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.393383817986193</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.745790557725597</v>
+      </c>
+      <c r="J7" t="n">
+        <v>77.84965516903853</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.2415176291673</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 32.572x + -16713.111</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>434.9773937411602</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3733.140458215095</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.301724932490023e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8642360737634867</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-110.843</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.54037e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.426</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3332620523280944</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9819341655054736</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.123252562679584</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.007545021771657</v>
+      </c>
+      <c r="J8" t="n">
+        <v>74.24096570731638</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.20451644591891</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 31.901x + -16136.462</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>434.7262552700104</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7441.511081075255</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.597721446077188e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9999751168535718</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-110.981</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.53716e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.496</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2645958349069977</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9017219902471229</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.727889263543213</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.720485418109289</v>
+      </c>
+      <c r="J9" t="n">
+        <v>72.85281803858638</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.13382768216373</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 30.691x + -15299.467</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>445.008667827318</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>486373584.8139477</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.441654179782531e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9530521382708723</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-108.634</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.53629e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.57299999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1608473681537302</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9080810187715076</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.017064238264356</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.437952024632305</v>
+      </c>
+      <c r="J10" t="n">
+        <v>84.34328643491419</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.14466889571358</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 30.871x + -15215.188</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>440.893649765704</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>271883201.9115602</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.414356616121575e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9542145919593925</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-108.1780000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.53481e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.61799999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4858818281318047</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9785970715954621</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.147096728032547</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.285343099581218</v>
+      </c>
+      <c r="J11" t="n">
+        <v>78.1259004128614</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.21390437859245</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 32.068x + -15663.865</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>436.9422448663099</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>179493570.8718365</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.395003737481824e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9550009412094956</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-105.3049999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.53387e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.706</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7573473565427579</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.822854315755767</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.266179193163782</v>
+      </c>
+      <c r="J12" t="n">
+        <v>85.49060355563836</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.09327901199157</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 30.038x + -14468.741</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>433.2828176238438</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>473482797.4171944</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.368441139985179e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9561329531221543</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-100.226</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.53204e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.77800000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4001676686618602</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.152927271710897</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.9875438057797</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.109394555256071</v>
+      </c>
+      <c r="J13" t="n">
+        <v>85.65882565309302</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.27045075152152</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 33.118x + -15875.791</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>429.7443921062749</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>117771042.3196444</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.343280724412004e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9571664789309613</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-96.52499999999998</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.53008e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.842</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.8026212992742908</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.584505680395904</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.15193445722186</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.409712612866524</v>
+      </c>
+      <c r="J14" t="n">
+        <v>87.53052867950232</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.38258771142314</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 35.415x + -16876.557</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>426.4700305922341</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>349439032.2707579</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.321317152969503e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9580557726845003</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-100.628</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.52919e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.86199999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2884047273209878</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.073850823114411</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.97117799440497</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.620486508216529</v>
+      </c>
+      <c r="J15" t="n">
+        <v>92.44182578631333</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.27201891195358</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 33.148x + -15598.740</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>423.1897734463594</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>231090589.7369125</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.312041895641052e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9584411570238839</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-95.27599999999995</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.52793e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.959</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.07883904940250246</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7509282484778455</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.811812607705878</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.912266849052492</v>
+      </c>
+      <c r="J16" t="n">
+        <v>85.59601206041822</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.20429940099785</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 31.897x + -14845.894</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>420.1364422536576</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>229488003.6014582</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.283815292238171e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9596587564260722</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-97.83600000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.5275e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.971</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1453075542020658</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9566086628544048</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.893820598997455</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.458725974622966</v>
+      </c>
+      <c r="J17" t="n">
+        <v>94.64255600170026</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.21897423688192</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 32.160x + -14845.285</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>417.1300157044847</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>227902862.8026039</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.278471387005311e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9598885543490819</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-95.12</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.52591e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-85.02</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3883237521182217</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.250366068075689</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.03046720832574</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.771343086547224</v>
+      </c>
+      <c r="J18" t="n">
+        <v>100.4010061051088</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.33506109208007</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 34.403x + -15811.261</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>414.3051543601015</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>460058898.2584543</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.261811176964296e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9605759033464433</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-94.02200000000005</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.52559e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-85.053</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4966249012978276</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.174901781626295</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.17465802632463</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.226629633041304</v>
+      </c>
+      <c r="J19" t="n">
+        <v>92.80058029876579</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.40596399788193</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 35.935x + -16420.465</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>411.5490035160651</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>168752308.0618253</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.251941750184349e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9610217472889362</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-90.82900000000006</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.52297e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-85.123</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.671926698576684</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.362713036006851</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.205540315116692</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.857436947350248</v>
+      </c>
+      <c r="J20" t="n">
+        <v>106.4959436450616</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.3843942276353</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 35.455x + -16062.846</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>408.8704165918489</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>168095581.7973329</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.229772076629964e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9619043666040857</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-95.35300000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.52289e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-85.11199999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4601298577318467</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.274296297074516</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.346819571812321</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.834531555693543</v>
+      </c>
+      <c r="J21" t="n">
+        <v>98.95250726861256</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.40770087856779</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 35.974x + -16189.763</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>406.284325692896</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>332543948.5380579</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.231087856751578e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.961851215372903</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-90.24400000000003</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.52152e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-85.187</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5305615207392302</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.05712558273266</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.158291421207924</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.456377305570472</v>
+      </c>
+      <c r="J22" t="n">
+        <v>103.5196344469469</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.40101844248152</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 35.823x + -16001.834</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>403.7662899693652</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>165378171.6926379</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.210059814721662e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9627495211170048</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +3668,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +3697,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-442.259</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.82179e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.95399999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4868496705966273</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9305461352244767</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.486515990899356</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.652863543536844</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.9010996237902</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.01732849397618</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.470x + -6207.443</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>451.6044662754214</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>123710028.0486032</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.987296709227189e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8860798530389814</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-335.343</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.81987e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.723</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.04672743795167802</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.700242719078051</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.503605158159591</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.511008396866347</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18.14526817472773</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.13004301724143</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.783x + -7085.928</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>405.7275238830791</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3497.19477476956</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.930271585502584e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8090104878817128</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-279.395</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.77439e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.58499999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04344880580977804</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7067497689889668</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.573202444611359</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.572315850662743</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22.35958682587758</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.73368248333327</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 17.522x + -8148.785</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>417.0788436500541</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>171108914.0719451</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.406417280158856e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9294396848737421</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-248.253</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.73509e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.063</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5325310100409251</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.083572950115151</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.051245052085944</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.086214529595213</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26.46226441848635</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.14803493896184</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 20.073x + -9233.579</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>411.95015765415</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>122678950.6087333</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.159569684637911e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9359526637122982</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-226.671</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.70279e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.426</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5056609429324158</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.186078074515096</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.173132411387343</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.247864822818564</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30.0577205542993</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.35074216504593</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 21.612x + -9791.984</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>407.2572311950503</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>166679622.0401532</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.980804043968316e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9407758982001798</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-207.532</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.68014e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.744</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3418838659433213</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9933868795111681</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.956715802572316</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.149640197916274</v>
+      </c>
+      <c r="J7" t="n">
+        <v>33.54175318950324</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.4801081196277</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 22.723x + -10126.916</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>402.3693947042688</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>219554492.4735357</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.84345606726226e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9447820658291792</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-193.646</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.65986e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.986</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4688145750425372</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.204920423547245</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.098267300836661</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.4198853832538</v>
+      </c>
+      <c r="J8" t="n">
+        <v>36.56272359303742</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.65942084978334</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 24.466x + -10775.877</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>397.3423208388615</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>216845551.8079745</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.735928600554866e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9479219536291398</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-181.3840000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.64515e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.188</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6730476019988526</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.298915375964702</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.996322071243428</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.039340365109102</v>
+      </c>
+      <c r="J9" t="n">
+        <v>38.40535605278079</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.80683387269596</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 26.112x + -11360.284</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>392.540273618457</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>222635345.1394069</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.652005862649169e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9505198874354319</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-173.999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.63282e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.34999999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5263471096558071</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.160569209941172</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.040775188615683</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.018968229501574</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40.859885876192</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.84182568801585</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 26.536x + -11370.083</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>388.0951011812932</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>423062157.5231858</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.585997180361561e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9525680438297079</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-168.372</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.62378e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.488</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2782087807888748</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.039474195010175</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.841860140978564</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.322170451791392</v>
+      </c>
+      <c r="J11" t="n">
+        <v>43.69273590542747</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.82035798253104</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 26.274x + -11075.066</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>383.9272286990046</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>254617483.0617626</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.533173101994421e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9542903154861091</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +4230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +4334,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +4363,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-298.873</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.74005e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.417</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5748356467758182</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.05960778332942</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.717089526359442</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.653771215004786</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21.76948728423834</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.57765001895916</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 16.722x + -9558.348</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>487.9594042690175</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>20870563.31481155</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.064964654546895e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.906431124011674</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-226.521</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.69425e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.57299999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3492555959743472</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.14911994905871</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.756190088455087</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.810197594637567</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.2048480491726</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.27250598703715</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 20.991x + -11400.507</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>475.5846047802367</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>62337363.4492505</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.386627859863791e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.925488981423517</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-194.9169999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.66225e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.05800000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2969679358242454</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.031316870016483</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.827728234924031</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.890325670547747</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35.6541549855468</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.55303441183727</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 23.401x + -12495.551</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>470.224807312236</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>40256233.97970039</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.126434324001954e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9328994003297738</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-175.016</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.64118e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.373</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.526966634684777</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9143536872983123</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.008143124059732</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.028628035828875</v>
+      </c>
+      <c r="J5" t="n">
+        <v>41.73157588427322</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.743258424204</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 25.376x + -13397.310</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>465.4798622222645</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>510318735.3978912</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.972672512095646e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9374266052950188</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-161.784</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.6246e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.59099999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6215597412208376</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.298853116515421</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.17532902262293</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.382107666008354</v>
+      </c>
+      <c r="J6" t="n">
+        <v>47.9111308234765</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.89947405281634</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 27.265x + -14245.031</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>460.7156419459649</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>632546268.4056382</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.863215574310486e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9407106410451536</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-147.486</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.61492e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.816</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6607842528268411</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.319963363227983</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.03249923903955</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.199499308497972</v>
+      </c>
+      <c r="J7" t="n">
+        <v>52.79919539965933</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.98571453966041</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 28.433x + -14663.556</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>455.9903720540548</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>623760284.3014617</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.770012462716079e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9438348303464029</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-142.458</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.60746e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.95099999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6185837830408326</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9657436290814027</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.190632654499531</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.225105104117374</v>
+      </c>
+      <c r="J8" t="n">
+        <v>56.28828286672975</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.94885360512119</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 27.922x + -14189.716</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>447.6027129400221</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3715.982269439966</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.771898486089274e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8228173929287063</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-138.157</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.59913e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.06699999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3559412103919379</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.032128751127427</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.954389929417107</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.248093053502418</v>
+      </c>
+      <c r="J9" t="n">
+        <v>57.27811431808519</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.99169408013763</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 28.518x + -14333.151</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>430.1826088687079</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6012.003209406022</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.648794861625218e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9981333489221115</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-130.276</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.59559e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.18600000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.56605944572541</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.283946272007962</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.166579867458769</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.471956970822943</v>
+      </c>
+      <c r="J10" t="n">
+        <v>64.85297544713929</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.08755977573321</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 29.948x + -14928.621</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>443.8291156226697</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>485415571.4548267</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.611478261242188e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9492233587210586</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-130.32</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.59046e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.254</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2463238201643122</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.89445080651793</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.829974252835309</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.818962116842231</v>
+      </c>
+      <c r="J11" t="n">
+        <v>58.47775493192427</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.03234012241425</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 29.107x + -14343.351</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>440.5091394705662</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>722536310.2237729</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.579905095827634e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9502722135641067</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-124.157</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.58745e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.33799999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5126535172226138</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.270902487066229</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.30772968572546</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.52742155028443</v>
+      </c>
+      <c r="J12" t="n">
+        <v>69.10106554047931</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.15665508396445</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 31.072x + -15231.523</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>437.4265430628149</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>183619405.8780275</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.547027152124949e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9514947352039828</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-120.739</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.58398e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.428</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2267232485201308</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.119275411450559</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.094256570402491</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.430304107782438</v>
+      </c>
+      <c r="J13" t="n">
+        <v>70.92965672324281</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.08499578560517</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 29.908x + -14498.787</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>434.5431997849405</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>475148769.1456621</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.513936096180505e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9527096493110544</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-120.115</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.58086e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.47799999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1699191449805814</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.177882813074193</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.850361767590661</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.227434718623907</v>
+      </c>
+      <c r="J14" t="n">
+        <v>69.29584418620011</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.09518927042227</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 30.068x + -14460.954</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>431.6683188885536</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>178171907.8930506</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.491869959400736e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9534823363442003</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-115.753</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.58077e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.55</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1829024069604703</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8217121245833016</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.923089042084646</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.298567079211065</v>
+      </c>
+      <c r="J15" t="n">
+        <v>72.67654801320894</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.12709752425977</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 30.581x + -14604.738</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>428.9262120647479</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>132531860.5347188</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.470279622545723e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9544215287585653</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-116.878</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.57822e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.57899999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1875191281508037</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.177907326013075</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.856041126822081</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.416883207610051</v>
+      </c>
+      <c r="J16" t="n">
+        <v>72.08253099740354</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.15007254934933</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 30.961x + -14682.520</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>426.2185258010602</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>116603561.0165156</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.455093855836768e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9549543509790713</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-114.853</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.57668e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.63200000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3389724207367263</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.054992162070655</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.733668930270764</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.959163884402924</v>
+      </c>
+      <c r="J17" t="n">
+        <v>69.06293447080684</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.13983374339404</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 30.791x + -14485.508</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>423.5447604490373</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>231617670.8661659</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.437330883833342e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9556472121466791</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-108.551</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.57459e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.69799999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.303661183557752</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.033849167717337</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.064510478208242</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.322020410244675</v>
+      </c>
+      <c r="J18" t="n">
+        <v>74.04600404857823</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.33375385228582</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 34.376x + -16154.391</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>420.8521465643094</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>345035231.1221668</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.414782119410137e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9565266153540315</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-110.7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.57329e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-84.73699999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2221367188626711</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6217592092470657</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.91243947813153</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.038954453207784</v>
+      </c>
+      <c r="J19" t="n">
+        <v>72.02067912238269</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.18140532774646</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 31.495x + -14610.468</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>418.1504168581953</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>342507630.4153895</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.400493193536306e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9570916827740816</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-108.405</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.57036e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-84.78700000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.5479085555043246</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.141181211867724</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.106621445796754</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.475691612037422</v>
+      </c>
+      <c r="J20" t="n">
+        <v>81.05592696890399</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.2608556166102</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 32.935x + -15201.226</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>415.4622142704876</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>113521306.5080879</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.380965401563013e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.957803369536288</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-106.7310000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.57127e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-84.839</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2763935460470526</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.063772525189788</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.209174426616221</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.346155537522304</v>
+      </c>
+      <c r="J21" t="n">
+        <v>80.99620197720108</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.26645523106805</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 33.041x + -15131.637</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>412.7535966023984</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>115862872.8638789</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.367067698790006e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9584805877494693</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-106.095</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.57021e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-84.876</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3248306689112525</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.076188676245403</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.152573695275685</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.25880947692925</v>
+      </c>
+      <c r="J22" t="n">
+        <v>78.97688435275302</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.26996277800785</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 33.108x + -15046.685</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>409.9987329059463</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>447755241.8436182</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.35471195665405e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9589846919945907</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +5468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +5572,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +5601,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-462.703</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.87562e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.666</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.366961488135045</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7344728535012454</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.305516669057611</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.301663182458624</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12.60961014693909</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.69042849471109</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.760x + -5675.637</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>445.3914207522574</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>33151691.97325099</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>6.166507926225259e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8846643467100372</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-341.228</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.86036e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.589</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7407254614268683</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.28419441979076</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.165334452960385</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.248009816753901</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17.79902109540234</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.11028026646228</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.707x + -6970.265</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>420.5912316038754</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>116789534.394143</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.943178437464874e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9168955139039886</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-292.5430000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.81188e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.41500000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1208609360626289</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.879768997148763</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.797881634399896</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.628180061821881</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.92427266471121</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.60238351202463</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.844x + -7716.641</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>412.6878403183973</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>451117728.3695154</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.495844151210855e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9285234756006745</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-256.046</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.76874e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-82.971</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4582943823860412</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.242753045030164</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.010984874438387</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.156901884406637</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25.20600717123226</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.02982823978692</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 19.273x + -8713.051</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>407.5198338579776</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>111323395.5913109</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.214655057801039e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9358830006248612</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-234.376</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.73642e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.34699999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2793207948066145</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9526671092969087</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.653289550951597</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.747880731698404</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27.52436405445816</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.23515113651769</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 20.707x + -9209.406</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>402.4984344616082</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>439760819.851115</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.03122837915406e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9408105351430178</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-210.663</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.712e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.68600000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.647193551036374</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.479149511399824</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.220330998105737</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.342158731231792</v>
+      </c>
+      <c r="J7" t="n">
+        <v>32.12753694434153</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.53531326335293</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 23.232x + -10243.338</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>397.6657207369928</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>162911489.1865705</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.882071865903075e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9451251787765573</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-198.189</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.69367e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.928</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5892539157361023</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.20579971014292</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.232922133307423</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.021844659399987</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.18718747294839</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.6169836842146</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 24.030x + -10413.319</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>393.0027983229647</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>428485616.9651723</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.776945056760763e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9482408226897785</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-191.136</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.67726e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.108</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8669029311801114</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.682770595395264</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.00547822619101</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35.87052335486677</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.60470699987309</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 23.906x + -10173.759</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>388.6197640005519</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>423675658.5636956</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.697160895668675e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9505455106039423</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-179.392</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.66442e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.288</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4554567317717332</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.233746928739858</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.211603091215871</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.401245553256979</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40.05877285150549</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.79350935367347</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 25.954x + -10962.091</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>384.5405361846218</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>419182986.3963848</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.625566196419015e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9527704634707345</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-172.243</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.65438e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.417</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.582621148254729</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.341671295357583</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.902322074182519</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.997720086284586</v>
+      </c>
+      <c r="J11" t="n">
+        <v>40.23841953981763</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.87956933956821</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 27.008x + -11287.125</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>380.6599388984416</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>414789006.4149199</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.57347364853231e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.954390280794259</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +6134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +6238,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +6267,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-374.2909999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.84397e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-80.36</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1724522089202629</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7816926849252308</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.301432690320966</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.293054448566362</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15.98833859934444</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.60444786453098</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 13.009x + -7313.384</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>479.8108571237261</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>263079561.5056703</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.893989755513716e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8893284196781287</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-261.54</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.75614e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.139</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2773103774693476</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9613152974731972</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.730300671867965</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.819481721014794</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24.44635738223</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.8759884752196</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 18.322x + -9757.483</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>466.0123437508557</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>192729227.9384485</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.691099528880948e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.91880454146262</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-218.7670000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.70856e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.786</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.074487207296174</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.378623896316485</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.191692665621956</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.120683026077312</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30.65456643452785</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.38538859207533</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 21.898x + -11495.013</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>460.2784191496814</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>44358802.97051834</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.316267546161293e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9287083495419479</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-197.641</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.67791e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.16200000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2017053643983824</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.148774862287414</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.966956948845334</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.161365550840937</v>
+      </c>
+      <c r="J5" t="n">
+        <v>36.01577453852055</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.49001009449013</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 22.812x + -11767.167</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>456.0211804082514</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>250219409.6483359</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.115220061307796e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9341833414340105</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-182.576</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.65727e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.43000000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.0921435694704337</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8006552880987349</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.911132927162139</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.879282877063582</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37.75025328186528</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.58149835851941</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 23.677x + -12059.020</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>451.9243178839052</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>186168449.9489576</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.980248030971606e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9380505623270022</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-170.0189999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.6437e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.629</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4834815859317756</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.128393713392375</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.974431832782421</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.436476359734484</v>
+      </c>
+      <c r="J7" t="n">
+        <v>44.89362237475584</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.75576086883666</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 25.517x + -12896.819</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>447.9321091230277</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>429146801.0924662</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.885643224081772e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9409127731355369</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-161.75</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.63508e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.792</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9071858299250994</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.815432822655203</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.0534444533181</v>
+      </c>
+      <c r="J8" t="n">
+        <v>46.25612832610045</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.73426318697842</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 25.275x + -12594.822</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>426.8191531617577</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3653.478883969704</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.592105281647223e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8352073689632808</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-154.88</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.62824e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.913</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2704488341237034</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.140742721430283</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.887011907181779</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.049682285007532</v>
+      </c>
+      <c r="J9" t="n">
+        <v>47.43081530555657</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.84293315155519</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 26.549x + -13132.416</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>425.4320827613182</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7300.385852477982</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.677177381748076e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9999740495977159</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-152.982</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.62254e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-83.98999999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1527155603781452</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8119589227703328</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.94864279596177</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.333199308210784</v>
+      </c>
+      <c r="J10" t="n">
+        <v>51.05136458947229</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.845923889647</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 26.586x + -13021.202</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>437.235899553066</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>478305514.0727226</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.722280096243427e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9462048918809975</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-145.422</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.61677e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.113</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3327716310013939</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.348387826361179</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.990617648591031</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.798414634125093</v>
+      </c>
+      <c r="J11" t="n">
+        <v>50.00527152833322</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.92420456922811</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 27.590x + -13407.732</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>434.0356234338695</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>387057710.379193</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.673077680427291e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9478872190449561</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-141.159</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.61527e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.184</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6787474647899472</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.434360233993576</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.024071817102727</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.525283747516431</v>
+      </c>
+      <c r="J12" t="n">
+        <v>55.86926507748024</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.01340184433441</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 28.830x + -13924.839</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>430.8922112294288</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>236154793.0845484</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.646095659671054e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9489188871614367</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-139.431</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.61226e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.249</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3276181384431741</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.103281480349789</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.853633461602472</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.140770967853316</v>
+      </c>
+      <c r="J13" t="n">
+        <v>54.08959453609101</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.00884948439409</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 28.764x + -13762.517</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>427.6949893090637</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>352754192.0720581</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.618877796593501e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9498751442996644</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-136.846</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.60879e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.309</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5855119891887919</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.244891054985618</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.23564402554166</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.673241269583246</v>
+      </c>
+      <c r="J14" t="n">
+        <v>59.42228396367067</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.08937905454511</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 29.977x + -14255.216</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>424.533169671479</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>290117497.2340956</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.593102726972235e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.950780547666497</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-131.502</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.60783e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.40900000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.377448655860229</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.121517452732289</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.125363248757869</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.481750619132059</v>
+      </c>
+      <c r="J15" t="n">
+        <v>59.5722292407458</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.1091289430927</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 30.290x + -14262.611</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>420.9721895559343</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>345012531.730469</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.561030430931987e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9520786928258375</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-130.049</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.60631e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.465</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7099478657649568</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.47195443880968</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.599293104277672</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.714287781044814</v>
+      </c>
+      <c r="J16" t="n">
+        <v>62.09335464102667</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.14577355566854</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 30.889x + -14416.039</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>417.5882387120285</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>118373990.5439707</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.539173651349342e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9529330964957867</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-127.9780000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.60393e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.533</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2803089928407386</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.085174505604829</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.205143872390861</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.553328053875496</v>
+      </c>
+      <c r="J17" t="n">
+        <v>64.00536129478485</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.10473863551152</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 30.220x + -13952.927</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>414.5571719338185</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>453135520.0351815</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.514813113505032e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9538487353078851</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-126.532</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.60207e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.592</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1487432716402615</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.008077297412275</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.740922904542704</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.108672279558191</v>
+      </c>
+      <c r="J18" t="n">
+        <v>59.8506151899095</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.08303827008297</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 29.878x + -13660.225</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>411.5259476161896</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>168743346.0635722</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.493103631632429e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9546866090518605</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-122.514</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.6022e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-84.648</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5060991170268129</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.456941126823257</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.322919831960715</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.451109389895034</v>
+      </c>
+      <c r="J19" t="n">
+        <v>65.00373398950133</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.21451588060602</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 32.079x + -14606.625</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>408.5105256298336</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>334777631.6739607</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.476259962158232e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9554258153262858</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-122.7719999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.60188e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-84.703</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2066005261241105</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8818063340206385</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.862697365775452</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.226556745012293</v>
+      </c>
+      <c r="J20" t="n">
+        <v>66.47584130040504</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.09506374441214</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 30.066x + -13508.934</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>405.4855688446784</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>221692713.7646232</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.45904275648366e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9561647101586777</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-121.852</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.59964e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-84.744</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2747484608873234</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9980755596547854</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.869539600957623</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.176747817082969</v>
+      </c>
+      <c r="J21" t="n">
+        <v>62.7947401717645</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.15756103992196</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 31.087x + -13874.030</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>402.5010659986688</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>331821560.834577</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.442378256849942e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9567788086081715</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-116.947</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.60098e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-84.825</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4575814987810635</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7636684644524082</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.97294173691592</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.421379707766566</v>
+      </c>
+      <c r="J22" t="n">
+        <v>70.25433658294513</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.14656903179977</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 30.903x + -13663.820</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>399.5148303094026</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>436922180.5574364</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.422039977735035e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9577455068094651</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +7372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +7476,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +7505,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-502.2120000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.92483e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-78.999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.05832978375257965</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3501916478507179</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.045387552204705</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.859219990728348</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.35399294889431</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.08308845444594</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.649x + -5134.761</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>447.2608542610588</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>360712415.1757494</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>6.787841699857573e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.872894448800701</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-347.258</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.88417e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.467</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1610562925012994</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.878908599872532</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.764882583419437</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.827204371187795</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17.17911827594043</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.96212121317983</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.166x + -6697.682</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>400.1974333256916</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3457.066656048483</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.49665477798724e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8486630098005334</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-281.103</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.8179e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.496</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4734661030547845</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.211835147549638</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.885236992423122</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.990276554438986</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21.81647924218193</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.74631749462222</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 17.591x + -8090.893</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>412.4612535545218</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>175598348.1537231</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.487309756219125e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9291018201345514</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-246.028</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.76729e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.08199999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2257247119895066</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.725495798073172</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.74489988381427</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.02747996409805</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26.22352976007612</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.07557598061601</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 19.575x + -8829.035</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>407.3470578961657</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>111318800.5883842</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.182032860857763e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9369465305917135</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-215.908</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.73217e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.53700000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4994055575734559</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9376938281383639</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.992032588693461</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.880324703570487</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30.09344380231113</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.38996086624113</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 21.937x + -9770.280</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>402.3688986980127</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>329501850.603974</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.9729317622861e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9427244016307051</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-198.8419999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.70654e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.833</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3289320236214637</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.030166638636357</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.081641892814186</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.287583005189795</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.7458248487683</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.56119821939389</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 23.479x + -10307.517</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>397.415658651056</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>218840704.1563608</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.836214915534863e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9465849246484479</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-185.855</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.68647e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.069</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2258014914453887</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.018777000642412</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.953659508152739</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.261310470619143</v>
+      </c>
+      <c r="J8" t="n">
+        <v>36.9291831417116</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.67500104510698</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 24.630x + -10652.905</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>392.7104613324146</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>107181455.5656053</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.731376418170977e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9496478548149111</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-173.868</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.6731e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.26600000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2866525502480102</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.334255229158117</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.222604763808668</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.314889060921618</v>
+      </c>
+      <c r="J9" t="n">
+        <v>40.61492801685059</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.80491201635911</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 26.089x + -11149.284</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>388.4101290095276</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>158973472.4001223</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.65152339941978e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9521606934071773</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-170.251</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.66119e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.38200000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2788963290648758</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.005641316306479</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.082315998197027</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.141565419422775</v>
+      </c>
+      <c r="J10" t="n">
+        <v>41.39207985981636</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.85530636547489</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 26.703x + -11274.804</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>384.4091790697254</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>628613980.98006</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.598723325225615e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9537048599395087</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-158.229</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.65386e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.55200000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4708472557105602</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.247027035798391</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.197560301350448</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.600923440076155</v>
+      </c>
+      <c r="J11" t="n">
+        <v>46.36607603348832</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.97109499077021</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 28.228x + -11794.199</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>380.3166287316536</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>207343975.1091103</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.539633503169021e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9557811164962613</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +8038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +8142,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +8171,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-269.9549999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.72978e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.902</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.08589381367574381</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7322018736644139</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.531328785598934</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.876668637583507</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25.37966137844364</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.6967744138974</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 17.326x + -9647.423</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>476.5721033888777</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>32616356.86377891</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.840721463029202e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9125969666869889</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-202.054</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.6855e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-82.98999999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4864740162624521</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.022808757779163</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.90887649998498</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.303926665768761</v>
+      </c>
+      <c r="J3" t="n">
+        <v>35.73218651067575</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.42191370389277</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 22.209x + -11709.437</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>462.5869755842085</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>26239456.73372998</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.217473612483152e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9308786942661749</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-178.7979999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.6613e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.38500000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02683039209782336</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9317218555363775</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.828471411141543</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.086516975556523</v>
+      </c>
+      <c r="J4" t="n">
+        <v>39.4096394709042</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.60855465954982</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 23.945x + -12376.459</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>456.9434479126721</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>188258830.4061645</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.017273873978845e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9368504156747148</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-166.908</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.64506e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.596</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3009396598473824</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8979467968107356</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.817841343633992</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.062963638468355</v>
+      </c>
+      <c r="J5" t="n">
+        <v>43.77408767666498</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.73643486088176</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 25.299x + -12926.947</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>452.2621544931089</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>124547803.1700962</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.908531247009425e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9400894695746561</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-156.376</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.63705e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-83.76300000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5592052707371536</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.215474335402579</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.154582474546298</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.28809611649389</v>
+      </c>
+      <c r="J6" t="n">
+        <v>48.08071721584412</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.90473245000915</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 27.333x + -13841.239</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>426.5961128333809</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3684.652092205249</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.335455556498187e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8709002125473967</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-149.321</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.63134e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-83.928</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9804451187032809</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.868976932712027</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.30775358718872</v>
+      </c>
+      <c r="J7" t="n">
+        <v>52.01734549078425</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.83408140324777</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 26.441x + -13149.566</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>422.6749463804728</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3642.189151459356</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.864454460717978e-06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8134851209493507</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-146.064</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.62561e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.017</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5391840590059037</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.300624804363292</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.45614081551629</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.601116585679592</v>
+      </c>
+      <c r="J8" t="n">
+        <v>54.64359704910316</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.97585160834232</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 28.294x + -13956.665</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>438.112749893103</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>179792642.771854</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.721556559962741e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9464071651728816</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-140.314</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.62244e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.142</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.138500489160394</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.092264103585721</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.785199391950761</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.144351074743126</v>
+      </c>
+      <c r="J9" t="n">
+        <v>51.69415367677249</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.96396673717531</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 28.129x + -13686.828</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>434.2094682901393</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>475241279.9076642</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.673586660074046e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9481880184656595</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-137.398</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.62047e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.211</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4725324832443177</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.170954154732291</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.855839346327214</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.029462387368145</v>
+      </c>
+      <c r="J10" t="n">
+        <v>52.83968307202336</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.00037049837363</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 28.642x + -13804.790</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>430.6504935008618</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>117791125.0711426</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.643612089453659e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9493289101683569</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-136.163</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.61863e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-84.276</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1352510484158554</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.162536144610618</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.281336380884205</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.50571657208366</v>
+      </c>
+      <c r="J11" t="n">
+        <v>58.58114754623783</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.01240660309304</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 28.815x + -13755.979</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>427.2898349614363</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>175414089.0588971</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.617815616241259e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9503068576419258</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-128.955</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.6172e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-84.386</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1328430971679162</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9428907294654837</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.125997324437837</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.435388849627961</v>
+      </c>
+      <c r="J12" t="n">
+        <v>61.1053935006763</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.04229837464453</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 29.255x + -13843.933</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>424.2052365218456</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>174333779.1887518</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.58150876896356e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9517458764680145</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-129.674</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.61548e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-84.40600000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.501081674075603</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.130024801171136</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.255924385283577</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.526964797319383</v>
+      </c>
+      <c r="J13" t="n">
+        <v>61.84809723145336</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.13913333434772</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 30.779x + -14493.377</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>421.1424903195542</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>172944089.5054938</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.569231144901565e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9521874686474737</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-126.3419999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.61366e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-84.482</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3562339036299769</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.082936589636582</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.036063820203798</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.315550488970178</v>
+      </c>
+      <c r="J14" t="n">
+        <v>60.5310899400901</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.14187484781961</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 30.824x + -14382.641</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>418.1995125728263</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>114458354.7393551</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.542281346934422e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.953230418026092</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-126.863</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.61342e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-84.527</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.04594459834366993</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8471982430348479</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.837057934566277</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.361789380249925</v>
+      </c>
+      <c r="J15" t="n">
+        <v>63.06772815281365</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.04751394560952</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 29.334x + -13528.192</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>415.2940601923247</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>113880481.0897932</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.527569266650081e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.953851472500422</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-121.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.61245e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-84.58499999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.953260025425648</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.638662884025179</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.472401677363899</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.493302894722132</v>
+      </c>
+      <c r="J16" t="n">
+        <v>64.58687898031374</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.28065316677706</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 33.314x + -15366.032</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>412.4653666218679</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>170016055.2832703</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.508072820551902e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.954636768680206</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-118.9429999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.61202e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-84.648</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.329730002088063</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.233159010663049</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.344681462730618</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.408350972405506</v>
+      </c>
+      <c r="J17" t="n">
+        <v>66.8249629500563</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.22652662564285</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 32.297x + -14747.401</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>409.6914866273248</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>223941085.9405902</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.489212786123147e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.955429408991967</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-115.905</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.61212e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.706</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5249888641857724</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.301741040405934</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.386259228231592</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.46987992931944</v>
+      </c>
+      <c r="J18" t="n">
+        <v>66.69610672591601</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.23707281632849</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 32.490x + -14718.158</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>406.9016518111838</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>445599249.1035966</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.472231600958838e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9561750058948451</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-112.6900000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.61205e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-84.77200000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6165431194578478</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.169410769897473</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.289321268072667</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.52852005495124</v>
+      </c>
+      <c r="J19" t="n">
+        <v>71.58379072361994</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.27434074236413</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 33.192x + -14929.605</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>404.0651842629732</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>661839284.8314869</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.453166066346132e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9570047943069957</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-114.655</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.60874e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-84.791</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.6148948953477004</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.167841836417439</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.252716527022888</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.498050842256809</v>
+      </c>
+      <c r="J20" t="n">
+        <v>69.82922835043733</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.29242628008754</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 33.544x + -14975.823</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>401.2731753297563</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>109954655.0377423</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.439855398064399e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9574208714504687</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-113.539</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.61001e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-84.846</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2324892365175061</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.996847922834762</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.227311044928475</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.452877909713164</v>
+      </c>
+      <c r="J21" t="n">
+        <v>69.85623554556142</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.22900338411642</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 32.342x + -14283.628</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>398.4425835561854</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>109012463.3348543</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.426062937967993e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9580991501604325</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-115.079</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.60994e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-84.86</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3632715296455039</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.251512927527007</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.378854929313955</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.619448488318949</v>
+      </c>
+      <c r="J22" t="n">
+        <v>70.59258547796802</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.26054355963502</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 32.929x + -14444.860</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>395.5741458391194</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>216197133.3926557</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.420991244525461e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9583389134329636</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +9276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +9380,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +9409,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-402.064</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.834e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.051</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06368801255861183</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6128739397867219</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.331913211709849</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.303724796468092</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15.10752563238996</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.34755638349567</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.288x + -5813.035</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>413.3995528377526</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>225684152.6048389</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.241173545103358e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9067081040977826</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-260.005</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.73136e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.092</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6460453725209708</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.415212628814962</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.108251107166484</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.106380678769282</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25.61434889727027</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.03956231471548</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 19.337x + -8647.872</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>397.8529853889657</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>112885517.5216535</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.160469132995124e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9357369062570795</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-211.74</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.683e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-83.806</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3449166687044798</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.216922438045941</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.939951878640338</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.997214950294377</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32.5820616156744</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.45931583278877</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 22.537x + -9808.825</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>391.3386659647608</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>108290984.225836</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.837920383609075e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9451749698400085</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-190.444</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.65526e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.142</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5332000933665396</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.408815121063665</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.131843190763319</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.143875779299127</v>
+      </c>
+      <c r="J5" t="n">
+        <v>37.21856224599434</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.67444672224893</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 24.624x + -10553.448</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>386.3690046309804</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>157949997.6588617</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.688402224524403e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9496075244343175</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-172.473</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.63917e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-84.42400000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3804472063088298</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.104422476028958</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.800309221911419</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.062615258812547</v>
+      </c>
+      <c r="J6" t="n">
+        <v>42.55129164322822</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.77620126723748</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 25.752x + -10847.430</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>381.3808015938022</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>518900397.9970644</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.580863380424837e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9531556670278618</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-165.8600000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.62756e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-84.581</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2331167996821988</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8825543621714648</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.668613271302677</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.767341105985299</v>
+      </c>
+      <c r="J7" t="n">
+        <v>42.7585441020376</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.82889808127788</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 26.378x + -10925.455</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>376.3327505729329</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>205146431.2838763</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.515607192078831e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9552877675534639</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-151.4440000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.62081e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-84.77500000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3957024322300078</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.248273921621915</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.035198630167017</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.818188467867079</v>
+      </c>
+      <c r="J8" t="n">
+        <v>47.87513209381097</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.00106853694072</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 28.652x + -11732.964</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>371.3978966041586</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>101185515.6043342</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.451356492579932e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9576837039638305</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-147.945</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.61662e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-84.881</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4474356256169449</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.898629288362466</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.845110574505296</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.930993900605347</v>
+      </c>
+      <c r="J9" t="n">
+        <v>49.68107767055674</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.99679155326329</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 28.590x + -11509.331</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>366.7219718483795</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>398717668.0373393</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.414772267556041e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9590654145840383</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-148.651</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.61241e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-84.98399999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.03272061506378311</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.065013422387355</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.245747161035312</v>
+      </c>
+      <c r="J10" t="n">
+        <v>46.63772311722867</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.70829093751166</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 24.988x + -9790.788</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>362.3537054803389</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>197025356.9286698</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.378478295031829e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.960453219125349</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-139.839</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.6101e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-85.069</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3198664355744759</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.356484017700686</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.046790864949957</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.214822156642091</v>
+      </c>
+      <c r="J11" t="n">
+        <v>55.22623998671386</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.08199058568086</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 29.861x + -11700.289</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>358.2962929249304</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>97464261.31029435</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.351133738062318e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9615519162759297</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -588,19 +588,19 @@
       <c r="K2" t="n">
         <v>87.39461527861948</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 21.976x + -12302.187</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-12302.18729375609</v>
       </c>
       <c r="Y2" t="n">
         <v>484.6443158837664</v>
       </c>
       <c r="Z2" t="n">
-        <v>19228163.5771528</v>
+        <v>206.9680000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>4.107426050646521e-07</v>
@@ -640,19 +640,19 @@
       <c r="K3" t="n">
         <v>87.67246975244326</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 24.603x + -13530.070</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-13530.06999235967</v>
       </c>
       <c r="Y3" t="n">
         <v>477.610994005233</v>
       </c>
       <c r="Z3" t="n">
-        <v>21988711.72870108</v>
+        <v>180.5890000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>3.915264688983131e-07</v>
@@ -692,19 +692,19 @@
       <c r="K4" t="n">
         <v>87.80919344445904</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 26.140x + -14158.248</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-14158.24750389202</v>
       </c>
       <c r="Y4" t="n">
         <v>471.647745107983</v>
       </c>
       <c r="Z4" t="n">
-        <v>198526337.7212156</v>
+        <v>165.962</v>
       </c>
       <c r="AA4" t="n">
         <v>3.800388687384269e-07</v>
@@ -744,19 +744,19 @@
       <c r="K5" t="n">
         <v>87.88978892630244</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 27.139x + -14484.736</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-14484.73554295575</v>
       </c>
       <c r="Y5" t="n">
         <v>466.0288724821089</v>
       </c>
       <c r="Z5" t="n">
-        <v>214628173.4481199</v>
+        <v>157.841</v>
       </c>
       <c r="AA5" t="n">
         <v>3.725087214834107e-07</v>
@@ -796,19 +796,19 @@
       <c r="K6" t="n">
         <v>87.89963115757922</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 27.267x + -14312.646</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-14312.64573083237</v>
       </c>
       <c r="Y6" t="n">
         <v>460.5595015553163</v>
       </c>
       <c r="Z6" t="n">
-        <v>189707742.4385588</v>
+        <v>147.615</v>
       </c>
       <c r="AA6" t="n">
         <v>3.650324725381416e-07</v>
@@ -848,19 +848,19 @@
       <c r="K7" t="n">
         <v>87.84186301966545</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 26.536x + -13685.166</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-13685.16593608196</v>
       </c>
       <c r="Y7" t="n">
         <v>455.2543043898323</v>
       </c>
       <c r="Z7" t="n">
-        <v>373937725.723335</v>
+        <v>141.347</v>
       </c>
       <c r="AA7" t="n">
         <v>3.593354466531468e-07</v>
@@ -900,19 +900,19 @@
       <c r="K8" t="n">
         <v>87.98768526015695</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 28.461x + -14541.543</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-14541.54287731682</v>
       </c>
       <c r="Y8" t="n">
         <v>450.2182700074694</v>
       </c>
       <c r="Z8" t="n">
-        <v>35605802.02243853</v>
+        <v>138.753</v>
       </c>
       <c r="AA8" t="n">
         <v>3.552398619253264e-07</v>
@@ -952,19 +952,19 @@
       <c r="K9" t="n">
         <v>87.94828864672735</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 27.914x + -14048.106</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-14048.10619405686</v>
       </c>
       <c r="Y9" t="n">
         <v>419.8404706492517</v>
       </c>
       <c r="Z9" t="n">
-        <v>3667.096846773316</v>
+        <v>135.886</v>
       </c>
       <c r="AA9" t="n">
         <v>1.563779375131226e-06</v>
@@ -1004,19 +1004,19 @@
       <c r="K10" t="n">
         <v>88.10017472847596</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 30.147x + -15050.771</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-15050.77117242096</v>
       </c>
       <c r="Y10" t="n">
         <v>437.8462330691353</v>
       </c>
       <c r="Z10" t="n">
-        <v>3627.702964538223</v>
+        <v>125.828</v>
       </c>
       <c r="AA10" t="n">
         <v>4.368033539037081e-07</v>
@@ -1056,19 +1056,19 @@
       <c r="K11" t="n">
         <v>88.06272806623817</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 29.564x + -14576.068</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-14576.0684310631</v>
       </c>
       <c r="Y11" t="n">
         <v>416.803775935856</v>
       </c>
       <c r="Z11" t="n">
-        <v>3595.226063989589</v>
+        <v>127.311</v>
       </c>
       <c r="AA11" t="n">
         <v>1.234273032482909e-06</v>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1254,19 +1254,19 @@
       <c r="K2" t="n">
         <v>87.3183707240958</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 21.350x + -11554.185</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-11554.18489641194</v>
       </c>
       <c r="Y2" t="n">
         <v>464.5669167919543</v>
       </c>
       <c r="Z2" t="n">
-        <v>26010957.61006243</v>
+        <v>206.165</v>
       </c>
       <c r="AA2" t="n">
         <v>4.22327079787798e-07</v>
@@ -1306,19 +1306,19 @@
       <c r="K3" t="n">
         <v>87.7168858655324</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 25.082x + -12928.232</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-12928.23248599209</v>
       </c>
       <c r="Y3" t="n">
         <v>452.4099188020935</v>
       </c>
       <c r="Z3" t="n">
-        <v>372410298.8638328</v>
+        <v>164.432</v>
       </c>
       <c r="AA3" t="n">
         <v>3.876169113099555e-07</v>
@@ -1358,19 +1358,19 @@
       <c r="K4" t="n">
         <v>87.79074755562127</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 25.922x + -13112.049</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-13112.04858847742</v>
       </c>
       <c r="Y4" t="n">
         <v>447.1016415901562</v>
       </c>
       <c r="Z4" t="n">
-        <v>119782754.3855883</v>
+        <v>152.111</v>
       </c>
       <c r="AA4" t="n">
         <v>3.762666515441864e-07</v>
@@ -1410,19 +1410,19 @@
       <c r="K5" t="n">
         <v>87.89770132987779</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 27.242x + -13642.246</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-13642.24631611201</v>
       </c>
       <c r="Y5" t="n">
         <v>421.6536137753115</v>
       </c>
       <c r="Z5" t="n">
-        <v>3646.089233381663</v>
+        <v>144.179</v>
       </c>
       <c r="AA5" t="n">
         <v>7.572356582753557e-07</v>
@@ -1462,19 +1462,19 @@
       <c r="K6" t="n">
         <v>87.87090305260176</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 26.898x + -13286.158</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-13286.15777740048</v>
       </c>
       <c r="Y6" t="n">
         <v>419.4976855283768</v>
       </c>
       <c r="Z6" t="n">
-        <v>3610.386733990646</v>
+        <v>139.024</v>
       </c>
       <c r="AA6" t="n">
         <v>1.490054047196679e-06</v>
@@ -1514,19 +1514,19 @@
       <c r="K7" t="n">
         <v>87.95822994094442</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 28.050x + -13729.956</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-13729.95598918011</v>
       </c>
       <c r="Y7" t="n">
         <v>434.5103365912532</v>
       </c>
       <c r="Z7" t="n">
-        <v>237920712.0999677</v>
+        <v>138.9730000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>3.627429524089212e-07</v>
@@ -1566,19 +1566,19 @@
       <c r="K8" t="n">
         <v>87.9994241946994</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 28.628x + -13847.858</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-13847.85787379509</v>
       </c>
       <c r="Y8" t="n">
         <v>430.4014385069506</v>
       </c>
       <c r="Z8" t="n">
-        <v>133690707.1178724</v>
+        <v>132.0040000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>3.58462807520919e-07</v>
@@ -1618,19 +1618,19 @@
       <c r="K9" t="n">
         <v>87.94642311723564</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 27.889x + -13309.105</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-13309.10489660023</v>
       </c>
       <c r="Y9" t="n">
         <v>426.597419479509</v>
       </c>
       <c r="Z9" t="n">
-        <v>235269496.7540282</v>
+        <v>128.7810000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>3.55385637411946e-07</v>
@@ -1670,19 +1670,19 @@
       <c r="K10" t="n">
         <v>88.0763815727701</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 29.774x + -14119.930</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-14119.92997259863</v>
       </c>
       <c r="Y10" t="n">
         <v>423.0732388556012</v>
       </c>
       <c r="Z10" t="n">
-        <v>347548888.3566003</v>
+        <v>124.763</v>
       </c>
       <c r="AA10" t="n">
         <v>3.531580115747654e-07</v>
@@ -1722,19 +1722,19 @@
       <c r="K11" t="n">
         <v>88.0241065231758</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 28.986x + -13594.470</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-13594.47007781174</v>
       </c>
       <c r="Y11" t="n">
         <v>419.7788442639665</v>
       </c>
       <c r="Z11" t="n">
-        <v>343953770.7519221</v>
+        <v>127.144</v>
       </c>
       <c r="AA11" t="n">
         <v>3.516475567163398e-07</v>
@@ -1774,19 +1774,19 @@
       <c r="K12" t="n">
         <v>88.08897335398645</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 29.971x + -13953.988</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-13953.9877206023</v>
       </c>
       <c r="Y12" t="n">
         <v>416.6056952702053</v>
       </c>
       <c r="Z12" t="n">
-        <v>227892616.6250862</v>
+        <v>122.708</v>
       </c>
       <c r="AA12" t="n">
         <v>3.487872541914937e-07</v>
@@ -1826,19 +1826,19 @@
       <c r="K13" t="n">
         <v>88.1872777332149</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 31.597x + -14629.521</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-14629.52137263942</v>
       </c>
       <c r="Y13" t="n">
         <v>413.5657963968105</v>
       </c>
       <c r="Z13" t="n">
-        <v>226496233.9343009</v>
+        <v>119.515</v>
       </c>
       <c r="AA13" t="n">
         <v>3.46955902032398e-07</v>
@@ -1878,19 +1878,19 @@
       <c r="K14" t="n">
         <v>88.17638969275393</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 31.408x + -14410.467</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-14410.46686349054</v>
       </c>
       <c r="Y14" t="n">
         <v>410.5436983794904</v>
       </c>
       <c r="Z14" t="n">
-        <v>224314187.4534663</v>
+        <v>118.287</v>
       </c>
       <c r="AA14" t="n">
         <v>3.457145011466897e-07</v>
@@ -1930,19 +1930,19 @@
       <c r="K15" t="n">
         <v>88.14866558434818</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 30.938x + -14057.289</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-14057.28857993719</v>
       </c>
       <c r="Y15" t="n">
         <v>407.6201432992885</v>
       </c>
       <c r="Z15" t="n">
-        <v>167063955.362845</v>
+        <v>122.745</v>
       </c>
       <c r="AA15" t="n">
         <v>3.448318077236802e-07</v>
@@ -1982,19 +1982,19 @@
       <c r="K16" t="n">
         <v>88.27917396102336</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 33.285x + -15064.929</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-15064.92912862336</v>
       </c>
       <c r="Y16" t="n">
         <v>404.7066783950125</v>
       </c>
       <c r="Z16" t="n">
-        <v>221101391.716084</v>
+        <v>113.441</v>
       </c>
       <c r="AA16" t="n">
         <v>3.418394142851484e-07</v>
@@ -2034,19 +2034,19 @@
       <c r="K17" t="n">
         <v>88.21556661339291</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 32.098x + -14371.822</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-14371.82169837948</v>
       </c>
       <c r="Y17" t="n">
         <v>401.7001586722404</v>
       </c>
       <c r="Z17" t="n">
-        <v>110069402.4358505</v>
+        <v>115.513</v>
       </c>
       <c r="AA17" t="n">
         <v>3.410235923320787e-07</v>
@@ -2086,19 +2086,19 @@
       <c r="K18" t="n">
         <v>88.15173826279475</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 30.989x + -13715.592</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-13715.59214289839</v>
       </c>
       <c r="Y18" t="n">
         <v>398.8003103118868</v>
       </c>
       <c r="Z18" t="n">
-        <v>128816779.3976977</v>
+        <v>112.773</v>
       </c>
       <c r="AA18" t="n">
         <v>3.393441483635864e-07</v>
@@ -2138,19 +2138,19 @@
       <c r="K19" t="n">
         <v>88.25754330700138</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 32.872x + -14476.939</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-14476.93932113545</v>
       </c>
       <c r="Y19" t="n">
         <v>395.7982449995955</v>
       </c>
       <c r="Z19" t="n">
-        <v>164083270.5618534</v>
+        <v>111.799</v>
       </c>
       <c r="AA19" t="n">
         <v>3.381774309808566e-07</v>
@@ -2190,19 +2190,19 @@
       <c r="K20" t="n">
         <v>88.1554096332045</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 31.051x + -13502.758</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-13502.75764225445</v>
       </c>
       <c r="Y20" t="n">
         <v>392.7764364802676</v>
       </c>
       <c r="Z20" t="n">
-        <v>551036241.5742298</v>
+        <v>113.845</v>
       </c>
       <c r="AA20" t="n">
         <v>3.372725973788375e-07</v>
@@ -2242,19 +2242,19 @@
       <c r="K21" t="n">
         <v>88.19933669033118</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 31.809x + -13732.673</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-13732.67334728539</v>
       </c>
       <c r="Y21" t="n">
         <v>389.650751228401</v>
       </c>
       <c r="Z21" t="n">
-        <v>162026564.2009178</v>
+        <v>109.122</v>
       </c>
       <c r="AA21" t="n">
         <v>3.350946982634335e-07</v>
@@ -2294,19 +2294,19 @@
       <c r="K22" t="n">
         <v>88.35404138940973</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 34.800x + -14964.801</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-14964.80139226499</v>
       </c>
       <c r="Y22" t="n">
         <v>386.626075689845</v>
       </c>
       <c r="Z22" t="n">
-        <v>316634737.7815642</v>
+        <v>106.591</v>
       </c>
       <c r="AA22" t="n">
         <v>3.339554145431989e-07</v>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2492,19 +2492,19 @@
       <c r="K2" t="n">
         <v>87.82463100570338</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 26.326x + -14156.609</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-14156.60907079565</v>
       </c>
       <c r="Y2" t="n">
         <v>474.940972567993</v>
       </c>
       <c r="Z2" t="n">
-        <v>264274225.8072468</v>
+        <v>159.962</v>
       </c>
       <c r="AA2" t="n">
         <v>3.836824299068841e-07</v>
@@ -2544,19 +2544,19 @@
       <c r="K3" t="n">
         <v>88.01404903950372</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 28.839x + -15440.277</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-15440.27682491637</v>
       </c>
       <c r="Y3" t="n">
         <v>472.1234971601919</v>
       </c>
       <c r="Z3" t="n">
-        <v>646073718.2939132</v>
+        <v>140.202</v>
       </c>
       <c r="AA3" t="n">
         <v>3.718775417466821e-07</v>
@@ -2596,19 +2596,19 @@
       <c r="K4" t="n">
         <v>87.98906967238008</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 28.480x + -15076.164</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-15076.16360233346</v>
       </c>
       <c r="Y4" t="n">
         <v>468.2093199297603</v>
       </c>
       <c r="Z4" t="n">
-        <v>512473875.0277551</v>
+        <v>135.4440000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>3.659261456371368e-07</v>
@@ -2648,19 +2648,19 @@
       <c r="K5" t="n">
         <v>88.06437747428716</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 29.589x + -15503.248</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-15503.24818225107</v>
       </c>
       <c r="Y5" t="n">
         <v>463.6177622555926</v>
       </c>
       <c r="Z5" t="n">
-        <v>60892684.35987416</v>
+        <v>126.332</v>
       </c>
       <c r="AA5" t="n">
         <v>3.595944668508762e-07</v>
@@ -2700,19 +2700,19 @@
       <c r="K6" t="n">
         <v>88.02232667868783</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 28.960x + -14949.686</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-14949.68620077269</v>
       </c>
       <c r="Y6" t="n">
         <v>448.6815921335364</v>
       </c>
       <c r="Z6" t="n">
-        <v>3774.299972311237</v>
+        <v>121.292</v>
       </c>
       <c r="AA6" t="n">
         <v>1.307615251359875e-06</v>
@@ -2752,19 +2752,19 @@
       <c r="K7" t="n">
         <v>88.2415176291673</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 32.572x + -16713.111</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-16713.11102416616</v>
       </c>
       <c r="Y7" t="n">
         <v>434.9773937411602</v>
       </c>
       <c r="Z7" t="n">
-        <v>3733.140458215095</v>
+        <v>114.8820000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.301724932490023e-06</v>
@@ -2804,19 +2804,19 @@
       <c r="K8" t="n">
         <v>88.20451644591891</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 31.901x + -16136.462</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-16136.46163690372</v>
       </c>
       <c r="Y8" t="n">
         <v>434.7262552700104</v>
       </c>
       <c r="Z8" t="n">
-        <v>7441.511081075255</v>
+        <v>110.843</v>
       </c>
       <c r="AA8" t="n">
         <v>3.597721446077188e-07</v>
@@ -2856,19 +2856,19 @@
       <c r="K9" t="n">
         <v>88.13382768216373</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 30.691x + -15299.467</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-15299.46735871453</v>
       </c>
       <c r="Y9" t="n">
         <v>445.008667827318</v>
       </c>
       <c r="Z9" t="n">
-        <v>486373584.8139477</v>
+        <v>110.981</v>
       </c>
       <c r="AA9" t="n">
         <v>3.441654179782531e-07</v>
@@ -2908,19 +2908,19 @@
       <c r="K10" t="n">
         <v>88.14466889571358</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 30.871x + -15215.188</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-15215.18828857467</v>
       </c>
       <c r="Y10" t="n">
         <v>440.893649765704</v>
       </c>
       <c r="Z10" t="n">
-        <v>271883201.9115602</v>
+        <v>108.634</v>
       </c>
       <c r="AA10" t="n">
         <v>3.414356616121575e-07</v>
@@ -2960,19 +2960,19 @@
       <c r="K11" t="n">
         <v>88.21390437859245</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 32.068x + -15663.865</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-15663.8652472838</v>
       </c>
       <c r="Y11" t="n">
         <v>436.9422448663099</v>
       </c>
       <c r="Z11" t="n">
-        <v>179493570.8718365</v>
+        <v>108.1780000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>3.395003737481824e-07</v>
@@ -3012,19 +3012,19 @@
       <c r="K12" t="n">
         <v>88.09327901199157</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 30.038x + -14468.741</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-14468.74078383779</v>
       </c>
       <c r="Y12" t="n">
         <v>433.2828176238438</v>
       </c>
       <c r="Z12" t="n">
-        <v>473482797.4171944</v>
+        <v>105.3049999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>3.368441139985179e-07</v>
@@ -3064,19 +3064,19 @@
       <c r="K13" t="n">
         <v>88.27045075152152</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 33.118x + -15875.791</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-15875.79091736646</v>
       </c>
       <c r="Y13" t="n">
         <v>429.7443921062749</v>
       </c>
       <c r="Z13" t="n">
-        <v>117771042.3196444</v>
+        <v>100.226</v>
       </c>
       <c r="AA13" t="n">
         <v>3.343280724412004e-07</v>
@@ -3116,19 +3116,19 @@
       <c r="K14" t="n">
         <v>88.38258771142314</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 35.415x + -16876.557</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-16876.55652121696</v>
       </c>
       <c r="Y14" t="n">
         <v>426.4700305922341</v>
       </c>
       <c r="Z14" t="n">
-        <v>349439032.2707579</v>
+        <v>96.52499999999998</v>
       </c>
       <c r="AA14" t="n">
         <v>3.321317152969503e-07</v>
@@ -3168,19 +3168,19 @@
       <c r="K15" t="n">
         <v>88.27201891195358</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 33.148x + -15598.740</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-15598.73986141956</v>
       </c>
       <c r="Y15" t="n">
         <v>423.1897734463594</v>
       </c>
       <c r="Z15" t="n">
-        <v>231090589.7369125</v>
+        <v>100.628</v>
       </c>
       <c r="AA15" t="n">
         <v>3.312041895641052e-07</v>
@@ -3220,19 +3220,19 @@
       <c r="K16" t="n">
         <v>88.20429940099785</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 31.897x + -14845.894</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-14845.89365442346</v>
       </c>
       <c r="Y16" t="n">
         <v>420.1364422536576</v>
       </c>
       <c r="Z16" t="n">
-        <v>229488003.6014582</v>
+        <v>95.27599999999995</v>
       </c>
       <c r="AA16" t="n">
         <v>3.283815292238171e-07</v>
@@ -3272,19 +3272,19 @@
       <c r="K17" t="n">
         <v>88.21897423688192</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 32.160x + -14845.285</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-14845.28514461852</v>
       </c>
       <c r="Y17" t="n">
         <v>417.1300157044847</v>
       </c>
       <c r="Z17" t="n">
-        <v>227902862.8026039</v>
+        <v>97.83600000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>3.278471387005311e-07</v>
@@ -3324,19 +3324,19 @@
       <c r="K18" t="n">
         <v>88.33506109208007</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 34.403x + -15811.261</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-15811.26067139286</v>
       </c>
       <c r="Y18" t="n">
         <v>414.3051543601015</v>
       </c>
       <c r="Z18" t="n">
-        <v>460058898.2584543</v>
+        <v>95.12</v>
       </c>
       <c r="AA18" t="n">
         <v>3.261811176964296e-07</v>
@@ -3376,19 +3376,19 @@
       <c r="K19" t="n">
         <v>88.40596399788193</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 35.935x + -16420.465</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-16420.46539105344</v>
       </c>
       <c r="Y19" t="n">
         <v>411.5490035160651</v>
       </c>
       <c r="Z19" t="n">
-        <v>168752308.0618253</v>
+        <v>94.02200000000005</v>
       </c>
       <c r="AA19" t="n">
         <v>3.251941750184349e-07</v>
@@ -3428,19 +3428,19 @@
       <c r="K20" t="n">
         <v>88.3843942276353</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 35.455x + -16062.846</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-16062.84613889791</v>
       </c>
       <c r="Y20" t="n">
         <v>408.8704165918489</v>
       </c>
       <c r="Z20" t="n">
-        <v>168095581.7973329</v>
+        <v>90.82900000000006</v>
       </c>
       <c r="AA20" t="n">
         <v>3.229772076629964e-07</v>
@@ -3480,19 +3480,19 @@
       <c r="K21" t="n">
         <v>88.40770087856779</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 35.974x + -16189.763</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-16189.76253744107</v>
       </c>
       <c r="Y21" t="n">
         <v>406.284325692896</v>
       </c>
       <c r="Z21" t="n">
-        <v>332543948.5380579</v>
+        <v>95.35300000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>3.231087856751578e-07</v>
@@ -3532,19 +3532,19 @@
       <c r="K22" t="n">
         <v>88.40101844248152</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 35.823x + -16001.834</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-16001.83436353783</v>
       </c>
       <c r="Y22" t="n">
         <v>403.7662899693652</v>
       </c>
       <c r="Z22" t="n">
-        <v>165378171.6926379</v>
+        <v>90.24400000000003</v>
       </c>
       <c r="AA22" t="n">
         <v>3.210059814721662e-07</v>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -3730,19 +3730,19 @@
       <c r="K2" t="n">
         <v>85.01732849397618</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.470x + -6207.443</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6207.442793447139</v>
       </c>
       <c r="Y2" t="n">
         <v>451.6044662754214</v>
       </c>
       <c r="Z2" t="n">
-        <v>123710028.0486032</v>
+        <v>442.259</v>
       </c>
       <c r="AA2" t="n">
         <v>5.987296709227189e-07</v>
@@ -3782,19 +3782,19 @@
       <c r="K3" t="n">
         <v>86.13004301724143</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.783x + -7085.928</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7085.928005201331</v>
       </c>
       <c r="Y3" t="n">
         <v>405.7275238830791</v>
       </c>
       <c r="Z3" t="n">
-        <v>3497.19477476956</v>
+        <v>335.343</v>
       </c>
       <c r="AA3" t="n">
         <v>1.930271585502584e-06</v>
@@ -3834,19 +3834,19 @@
       <c r="K4" t="n">
         <v>86.73368248333327</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 17.522x + -8148.785</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8148.78475507964</v>
       </c>
       <c r="Y4" t="n">
         <v>417.0788436500541</v>
       </c>
       <c r="Z4" t="n">
-        <v>171108914.0719451</v>
+        <v>279.395</v>
       </c>
       <c r="AA4" t="n">
         <v>4.406417280158856e-07</v>
@@ -3886,19 +3886,19 @@
       <c r="K5" t="n">
         <v>87.14803493896184</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 20.073x + -9233.579</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9233.578607174244</v>
       </c>
       <c r="Y5" t="n">
         <v>411.95015765415</v>
       </c>
       <c r="Z5" t="n">
-        <v>122678950.6087333</v>
+        <v>248.253</v>
       </c>
       <c r="AA5" t="n">
         <v>4.159569684637911e-07</v>
@@ -3938,19 +3938,19 @@
       <c r="K6" t="n">
         <v>87.35074216504593</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 21.612x + -9791.984</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9791.983836112289</v>
       </c>
       <c r="Y6" t="n">
         <v>407.2572311950503</v>
       </c>
       <c r="Z6" t="n">
-        <v>166679622.0401532</v>
+        <v>226.671</v>
       </c>
       <c r="AA6" t="n">
         <v>3.980804043968316e-07</v>
@@ -3990,19 +3990,19 @@
       <c r="K7" t="n">
         <v>87.4801081196277</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 22.723x + -10126.916</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10126.91612636652</v>
       </c>
       <c r="Y7" t="n">
         <v>402.3693947042688</v>
       </c>
       <c r="Z7" t="n">
-        <v>219554492.4735357</v>
+        <v>207.532</v>
       </c>
       <c r="AA7" t="n">
         <v>3.84345606726226e-07</v>
@@ -4042,19 +4042,19 @@
       <c r="K8" t="n">
         <v>87.65942084978334</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 24.466x + -10775.877</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10775.87667963186</v>
       </c>
       <c r="Y8" t="n">
         <v>397.3423208388615</v>
       </c>
       <c r="Z8" t="n">
-        <v>216845551.8079745</v>
+        <v>193.646</v>
       </c>
       <c r="AA8" t="n">
         <v>3.735928600554866e-07</v>
@@ -4094,19 +4094,19 @@
       <c r="K9" t="n">
         <v>87.80683387269596</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 26.112x + -11360.284</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11360.28440174351</v>
       </c>
       <c r="Y9" t="n">
         <v>392.540273618457</v>
       </c>
       <c r="Z9" t="n">
-        <v>222635345.1394069</v>
+        <v>181.3840000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>3.652005862649169e-07</v>
@@ -4146,19 +4146,19 @@
       <c r="K10" t="n">
         <v>87.84182568801585</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 26.536x + -11370.083</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11370.08337581963</v>
       </c>
       <c r="Y10" t="n">
         <v>388.0951011812932</v>
       </c>
       <c r="Z10" t="n">
-        <v>423062157.5231858</v>
+        <v>173.999</v>
       </c>
       <c r="AA10" t="n">
         <v>3.585997180361561e-07</v>
@@ -4198,19 +4198,19 @@
       <c r="K11" t="n">
         <v>87.82035798253104</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 26.274x + -11075.066</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11075.06631422567</v>
       </c>
       <c r="Y11" t="n">
         <v>383.9272286990046</v>
       </c>
       <c r="Z11" t="n">
-        <v>254617483.0617626</v>
+        <v>168.372</v>
       </c>
       <c r="AA11" t="n">
         <v>3.533173101994421e-07</v>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4396,19 +4396,19 @@
       <c r="K2" t="n">
         <v>86.57765001895916</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 16.722x + -9558.348</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-9558.347632635645</v>
       </c>
       <c r="Y2" t="n">
         <v>487.9594042690175</v>
       </c>
       <c r="Z2" t="n">
-        <v>20870563.31481155</v>
+        <v>298.873</v>
       </c>
       <c r="AA2" t="n">
         <v>5.064964654546895e-07</v>
@@ -4448,19 +4448,19 @@
       <c r="K3" t="n">
         <v>87.27250598703715</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 20.991x + -11400.507</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-11400.5074043747</v>
       </c>
       <c r="Y3" t="n">
         <v>475.5846047802367</v>
       </c>
       <c r="Z3" t="n">
-        <v>62337363.4492505</v>
+        <v>226.521</v>
       </c>
       <c r="AA3" t="n">
         <v>4.386627859863791e-07</v>
@@ -4500,19 +4500,19 @@
       <c r="K4" t="n">
         <v>87.55303441183727</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 23.401x + -12495.551</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-12495.55134428585</v>
       </c>
       <c r="Y4" t="n">
         <v>470.224807312236</v>
       </c>
       <c r="Z4" t="n">
-        <v>40256233.97970039</v>
+        <v>194.9169999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>4.126434324001954e-07</v>
@@ -4552,19 +4552,19 @@
       <c r="K5" t="n">
         <v>87.743258424204</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 25.376x + -13397.310</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-13397.3099027157</v>
       </c>
       <c r="Y5" t="n">
         <v>465.4798622222645</v>
       </c>
       <c r="Z5" t="n">
-        <v>510318735.3978912</v>
+        <v>175.016</v>
       </c>
       <c r="AA5" t="n">
         <v>3.972672512095646e-07</v>
@@ -4604,19 +4604,19 @@
       <c r="K6" t="n">
         <v>87.89947405281634</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 27.265x + -14245.031</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-14245.03114372677</v>
       </c>
       <c r="Y6" t="n">
         <v>460.7156419459649</v>
       </c>
       <c r="Z6" t="n">
-        <v>632546268.4056382</v>
+        <v>161.784</v>
       </c>
       <c r="AA6" t="n">
         <v>3.863215574310486e-07</v>
@@ -4656,19 +4656,19 @@
       <c r="K7" t="n">
         <v>87.98571453966041</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 28.433x + -14663.556</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-14663.55578002072</v>
       </c>
       <c r="Y7" t="n">
         <v>455.9903720540548</v>
       </c>
       <c r="Z7" t="n">
-        <v>623760284.3014617</v>
+        <v>147.486</v>
       </c>
       <c r="AA7" t="n">
         <v>3.770012462716079e-07</v>
@@ -4708,19 +4708,19 @@
       <c r="K8" t="n">
         <v>87.94885360512119</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 27.922x + -14189.716</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-14189.71567726549</v>
       </c>
       <c r="Y8" t="n">
         <v>447.6027129400221</v>
       </c>
       <c r="Z8" t="n">
-        <v>3715.982269439966</v>
+        <v>142.458</v>
       </c>
       <c r="AA8" t="n">
         <v>1.771898486089274e-06</v>
@@ -4760,19 +4760,19 @@
       <c r="K9" t="n">
         <v>87.99169408013763</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 28.518x + -14333.151</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-14333.15111980325</v>
       </c>
       <c r="Y9" t="n">
         <v>430.1826088687079</v>
       </c>
       <c r="Z9" t="n">
-        <v>6012.003209406022</v>
+        <v>138.157</v>
       </c>
       <c r="AA9" t="n">
         <v>4.648794861625218e-07</v>
@@ -4812,19 +4812,19 @@
       <c r="K10" t="n">
         <v>88.08755977573321</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 29.948x + -14928.621</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-14928.62125492235</v>
       </c>
       <c r="Y10" t="n">
         <v>443.8291156226697</v>
       </c>
       <c r="Z10" t="n">
-        <v>485415571.4548267</v>
+        <v>130.276</v>
       </c>
       <c r="AA10" t="n">
         <v>3.611478261242188e-07</v>
@@ -4864,19 +4864,19 @@
       <c r="K11" t="n">
         <v>88.03234012241425</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 29.107x + -14343.351</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-14343.35053086576</v>
       </c>
       <c r="Y11" t="n">
         <v>440.5091394705662</v>
       </c>
       <c r="Z11" t="n">
-        <v>722536310.2237729</v>
+        <v>130.32</v>
       </c>
       <c r="AA11" t="n">
         <v>3.579905095827634e-07</v>
@@ -4916,19 +4916,19 @@
       <c r="K12" t="n">
         <v>88.15665508396445</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 31.072x + -15231.523</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-15231.52346824154</v>
       </c>
       <c r="Y12" t="n">
         <v>437.4265430628149</v>
       </c>
       <c r="Z12" t="n">
-        <v>183619405.8780275</v>
+        <v>124.157</v>
       </c>
       <c r="AA12" t="n">
         <v>3.547027152124949e-07</v>
@@ -4968,19 +4968,19 @@
       <c r="K13" t="n">
         <v>88.08499578560517</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 29.908x + -14498.787</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-14498.78684531403</v>
       </c>
       <c r="Y13" t="n">
         <v>434.5431997849405</v>
       </c>
       <c r="Z13" t="n">
-        <v>475148769.1456621</v>
+        <v>120.739</v>
       </c>
       <c r="AA13" t="n">
         <v>3.513936096180505e-07</v>
@@ -5020,19 +5020,19 @@
       <c r="K14" t="n">
         <v>88.09518927042227</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 30.068x + -14460.954</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-14460.95431466357</v>
       </c>
       <c r="Y14" t="n">
         <v>431.6683188885536</v>
       </c>
       <c r="Z14" t="n">
-        <v>178171907.8930506</v>
+        <v>120.115</v>
       </c>
       <c r="AA14" t="n">
         <v>3.491869959400736e-07</v>
@@ -5072,19 +5072,19 @@
       <c r="K15" t="n">
         <v>88.12709752425977</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 30.581x + -14604.738</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-14604.73772751724</v>
       </c>
       <c r="Y15" t="n">
         <v>428.9262120647479</v>
       </c>
       <c r="Z15" t="n">
-        <v>132531860.5347188</v>
+        <v>115.753</v>
       </c>
       <c r="AA15" t="n">
         <v>3.470279622545723e-07</v>
@@ -5124,19 +5124,19 @@
       <c r="K16" t="n">
         <v>88.15007254934933</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 30.961x + -14682.520</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-14682.52046921089</v>
       </c>
       <c r="Y16" t="n">
         <v>426.2185258010602</v>
       </c>
       <c r="Z16" t="n">
-        <v>116603561.0165156</v>
+        <v>116.878</v>
       </c>
       <c r="AA16" t="n">
         <v>3.455093855836768e-07</v>
@@ -5176,19 +5176,19 @@
       <c r="K17" t="n">
         <v>88.13983374339404</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 30.791x + -14485.508</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-14485.50824843448</v>
       </c>
       <c r="Y17" t="n">
         <v>423.5447604490373</v>
       </c>
       <c r="Z17" t="n">
-        <v>231617670.8661659</v>
+        <v>114.853</v>
       </c>
       <c r="AA17" t="n">
         <v>3.437330883833342e-07</v>
@@ -5228,19 +5228,19 @@
       <c r="K18" t="n">
         <v>88.33375385228582</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 34.376x + -16154.391</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-16154.3909398742</v>
       </c>
       <c r="Y18" t="n">
         <v>420.8521465643094</v>
       </c>
       <c r="Z18" t="n">
-        <v>345035231.1221668</v>
+        <v>108.551</v>
       </c>
       <c r="AA18" t="n">
         <v>3.414782119410137e-07</v>
@@ -5280,19 +5280,19 @@
       <c r="K19" t="n">
         <v>88.18140532774646</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 31.495x + -14610.468</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-14610.46845341834</v>
       </c>
       <c r="Y19" t="n">
         <v>418.1504168581953</v>
       </c>
       <c r="Z19" t="n">
-        <v>342507630.4153895</v>
+        <v>110.7</v>
       </c>
       <c r="AA19" t="n">
         <v>3.400493193536306e-07</v>
@@ -5332,19 +5332,19 @@
       <c r="K20" t="n">
         <v>88.2608556166102</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 32.935x + -15201.226</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-15201.22609870797</v>
       </c>
       <c r="Y20" t="n">
         <v>415.4622142704876</v>
       </c>
       <c r="Z20" t="n">
-        <v>113521306.5080879</v>
+        <v>108.405</v>
       </c>
       <c r="AA20" t="n">
         <v>3.380965401563013e-07</v>
@@ -5384,19 +5384,19 @@
       <c r="K21" t="n">
         <v>88.26645523106805</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 33.041x + -15131.637</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-15131.63707616863</v>
       </c>
       <c r="Y21" t="n">
         <v>412.7535966023984</v>
       </c>
       <c r="Z21" t="n">
-        <v>115862872.8638789</v>
+        <v>106.7310000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>3.367067698790006e-07</v>
@@ -5436,19 +5436,19 @@
       <c r="K22" t="n">
         <v>88.26996277800785</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 33.108x + -15046.685</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-15046.68486187088</v>
       </c>
       <c r="Y22" t="n">
         <v>409.9987329059463</v>
       </c>
       <c r="Z22" t="n">
-        <v>447755241.8436182</v>
+        <v>106.095</v>
       </c>
       <c r="AA22" t="n">
         <v>3.35471195665405e-07</v>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5634,19 +5634,19 @@
       <c r="K2" t="n">
         <v>84.69042849471109</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.760x + -5675.637</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5675.637107472598</v>
       </c>
       <c r="Y2" t="n">
         <v>445.3914207522574</v>
       </c>
       <c r="Z2" t="n">
-        <v>33151691.97325099</v>
+        <v>462.703</v>
       </c>
       <c r="AA2" t="n">
         <v>6.166507926225259e-07</v>
@@ -5686,19 +5686,19 @@
       <c r="K3" t="n">
         <v>86.11028026646228</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.707x + -6970.265</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6970.264701729548</v>
       </c>
       <c r="Y3" t="n">
         <v>420.5912316038754</v>
       </c>
       <c r="Z3" t="n">
-        <v>116789534.394143</v>
+        <v>341.228</v>
       </c>
       <c r="AA3" t="n">
         <v>4.943178437464874e-07</v>
@@ -5738,19 +5738,19 @@
       <c r="K4" t="n">
         <v>86.60238351202463</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.844x + -7716.641</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7716.640528928568</v>
       </c>
       <c r="Y4" t="n">
         <v>412.6878403183973</v>
       </c>
       <c r="Z4" t="n">
-        <v>451117728.3695154</v>
+        <v>292.5430000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>4.495844151210855e-07</v>
@@ -5790,19 +5790,19 @@
       <c r="K5" t="n">
         <v>87.02982823978692</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 19.273x + -8713.051</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8713.051459121381</v>
       </c>
       <c r="Y5" t="n">
         <v>407.5198338579776</v>
       </c>
       <c r="Z5" t="n">
-        <v>111323395.5913109</v>
+        <v>256.046</v>
       </c>
       <c r="AA5" t="n">
         <v>4.214655057801039e-07</v>
@@ -5842,19 +5842,19 @@
       <c r="K6" t="n">
         <v>87.23515113651769</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 20.707x + -9209.406</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9209.406278370005</v>
       </c>
       <c r="Y6" t="n">
         <v>402.4984344616082</v>
       </c>
       <c r="Z6" t="n">
-        <v>439760819.851115</v>
+        <v>234.376</v>
       </c>
       <c r="AA6" t="n">
         <v>4.03122837915406e-07</v>
@@ -5894,19 +5894,19 @@
       <c r="K7" t="n">
         <v>87.53531326335293</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 23.232x + -10243.338</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10243.33841910732</v>
       </c>
       <c r="Y7" t="n">
         <v>397.6657207369928</v>
       </c>
       <c r="Z7" t="n">
-        <v>162911489.1865705</v>
+        <v>210.663</v>
       </c>
       <c r="AA7" t="n">
         <v>3.882071865903075e-07</v>
@@ -5946,19 +5946,19 @@
       <c r="K8" t="n">
         <v>87.6169836842146</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 24.030x + -10413.319</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10413.31872808785</v>
       </c>
       <c r="Y8" t="n">
         <v>393.0027983229647</v>
       </c>
       <c r="Z8" t="n">
-        <v>428485616.9651723</v>
+        <v>198.189</v>
       </c>
       <c r="AA8" t="n">
         <v>3.776945056760763e-07</v>
@@ -5998,19 +5998,19 @@
       <c r="K9" t="n">
         <v>87.60470699987309</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 23.906x + -10173.759</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-10173.75882095493</v>
       </c>
       <c r="Y9" t="n">
         <v>388.6197640005519</v>
       </c>
       <c r="Z9" t="n">
-        <v>423675658.5636956</v>
+        <v>191.136</v>
       </c>
       <c r="AA9" t="n">
         <v>3.697160895668675e-07</v>
@@ -6050,19 +6050,19 @@
       <c r="K10" t="n">
         <v>87.79350935367347</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 25.954x + -10962.091</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-10962.09122833541</v>
       </c>
       <c r="Y10" t="n">
         <v>384.5405361846218</v>
       </c>
       <c r="Z10" t="n">
-        <v>419182986.3963848</v>
+        <v>179.392</v>
       </c>
       <c r="AA10" t="n">
         <v>3.625566196419015e-07</v>
@@ -6102,19 +6102,19 @@
       <c r="K11" t="n">
         <v>87.87956933956821</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 27.008x + -11287.125</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11287.12531539341</v>
       </c>
       <c r="Y11" t="n">
         <v>380.6599388984416</v>
       </c>
       <c r="Z11" t="n">
-        <v>414789006.4149199</v>
+        <v>172.243</v>
       </c>
       <c r="AA11" t="n">
         <v>3.57347364853231e-07</v>
@@ -6240,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6300,19 +6300,19 @@
       <c r="K2" t="n">
         <v>85.60444786453098</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 13.009x + -7313.384</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-7313.383695658047</v>
       </c>
       <c r="Y2" t="n">
         <v>479.8108571237261</v>
       </c>
       <c r="Z2" t="n">
-        <v>263079561.5056703</v>
+        <v>374.2909999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>5.893989755513716e-07</v>
@@ -6352,19 +6352,19 @@
       <c r="K3" t="n">
         <v>86.8759884752196</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 18.322x + -9757.483</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-9757.482711696241</v>
       </c>
       <c r="Y3" t="n">
         <v>466.0123437508557</v>
       </c>
       <c r="Z3" t="n">
-        <v>192729227.9384485</v>
+        <v>261.54</v>
       </c>
       <c r="AA3" t="n">
         <v>4.691099528880948e-07</v>
@@ -6404,19 +6404,19 @@
       <c r="K4" t="n">
         <v>87.38538859207533</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 21.898x + -11495.013</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-11495.01299186346</v>
       </c>
       <c r="Y4" t="n">
         <v>460.2784191496814</v>
       </c>
       <c r="Z4" t="n">
-        <v>44358802.97051834</v>
+        <v>218.7670000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>4.316267546161293e-07</v>
@@ -6456,19 +6456,19 @@
       <c r="K5" t="n">
         <v>87.49001009449013</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 22.812x + -11767.167</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-11767.16723840775</v>
       </c>
       <c r="Y5" t="n">
         <v>456.0211804082514</v>
       </c>
       <c r="Z5" t="n">
-        <v>250219409.6483359</v>
+        <v>197.641</v>
       </c>
       <c r="AA5" t="n">
         <v>4.115220061307796e-07</v>
@@ -6508,19 +6508,19 @@
       <c r="K6" t="n">
         <v>87.58149835851941</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 23.677x + -12059.020</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-12059.02033481012</v>
       </c>
       <c r="Y6" t="n">
         <v>451.9243178839052</v>
       </c>
       <c r="Z6" t="n">
-        <v>186168449.9489576</v>
+        <v>182.576</v>
       </c>
       <c r="AA6" t="n">
         <v>3.980248030971606e-07</v>
@@ -6560,19 +6560,19 @@
       <c r="K7" t="n">
         <v>87.75576086883666</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 25.517x + -12896.819</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-12896.8185038987</v>
       </c>
       <c r="Y7" t="n">
         <v>447.9321091230277</v>
       </c>
       <c r="Z7" t="n">
-        <v>429146801.0924662</v>
+        <v>170.0189999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>3.885643224081772e-07</v>
@@ -6612,19 +6612,19 @@
       <c r="K8" t="n">
         <v>87.73426318697842</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 25.275x + -12594.822</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-12594.82157947218</v>
       </c>
       <c r="Y8" t="n">
         <v>426.8191531617577</v>
       </c>
       <c r="Z8" t="n">
-        <v>3653.478883969704</v>
+        <v>161.75</v>
       </c>
       <c r="AA8" t="n">
         <v>1.592105281647223e-06</v>
@@ -6664,19 +6664,19 @@
       <c r="K9" t="n">
         <v>87.84293315155519</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 26.549x + -13132.416</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-13132.41584036204</v>
       </c>
       <c r="Y9" t="n">
         <v>425.4320827613182</v>
       </c>
       <c r="Z9" t="n">
-        <v>7300.385852477982</v>
+        <v>154.88</v>
       </c>
       <c r="AA9" t="n">
         <v>3.677177381748076e-07</v>
@@ -6716,19 +6716,19 @@
       <c r="K10" t="n">
         <v>87.845923889647</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 26.586x + -13021.202</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-13021.20211902497</v>
       </c>
       <c r="Y10" t="n">
         <v>437.235899553066</v>
       </c>
       <c r="Z10" t="n">
-        <v>478305514.0727226</v>
+        <v>152.982</v>
       </c>
       <c r="AA10" t="n">
         <v>3.722280096243427e-07</v>
@@ -6768,19 +6768,19 @@
       <c r="K11" t="n">
         <v>87.92420456922811</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 27.590x + -13407.732</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-13407.73164438409</v>
       </c>
       <c r="Y11" t="n">
         <v>434.0356234338695</v>
       </c>
       <c r="Z11" t="n">
-        <v>387057710.379193</v>
+        <v>145.422</v>
       </c>
       <c r="AA11" t="n">
         <v>3.673077680427291e-07</v>
@@ -6820,19 +6820,19 @@
       <c r="K12" t="n">
         <v>88.01340184433441</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 28.830x + -13924.839</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-13924.8385968852</v>
       </c>
       <c r="Y12" t="n">
         <v>430.8922112294288</v>
       </c>
       <c r="Z12" t="n">
-        <v>236154793.0845484</v>
+        <v>141.159</v>
       </c>
       <c r="AA12" t="n">
         <v>3.646095659671054e-07</v>
@@ -6872,19 +6872,19 @@
       <c r="K13" t="n">
         <v>88.00884948439409</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 28.764x + -13762.517</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-13762.51679414403</v>
       </c>
       <c r="Y13" t="n">
         <v>427.6949893090637</v>
       </c>
       <c r="Z13" t="n">
-        <v>352754192.0720581</v>
+        <v>139.431</v>
       </c>
       <c r="AA13" t="n">
         <v>3.618877796593501e-07</v>
@@ -6924,19 +6924,19 @@
       <c r="K14" t="n">
         <v>88.08937905454511</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 29.977x + -14255.216</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-14255.21617138809</v>
       </c>
       <c r="Y14" t="n">
         <v>424.533169671479</v>
       </c>
       <c r="Z14" t="n">
-        <v>290117497.2340956</v>
+        <v>136.846</v>
       </c>
       <c r="AA14" t="n">
         <v>3.593102726972235e-07</v>
@@ -6976,19 +6976,19 @@
       <c r="K15" t="n">
         <v>88.1091289430927</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 30.290x + -14262.611</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-14262.61079368881</v>
       </c>
       <c r="Y15" t="n">
         <v>420.9721895559343</v>
       </c>
       <c r="Z15" t="n">
-        <v>345012531.730469</v>
+        <v>131.502</v>
       </c>
       <c r="AA15" t="n">
         <v>3.561030430931987e-07</v>
@@ -7028,19 +7028,19 @@
       <c r="K16" t="n">
         <v>88.14577355566854</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 30.889x + -14416.039</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-14416.03887302562</v>
       </c>
       <c r="Y16" t="n">
         <v>417.5882387120285</v>
       </c>
       <c r="Z16" t="n">
-        <v>118373990.5439707</v>
+        <v>130.049</v>
       </c>
       <c r="AA16" t="n">
         <v>3.539173651349342e-07</v>
@@ -7080,19 +7080,19 @@
       <c r="K17" t="n">
         <v>88.10473863551152</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 30.220x + -13952.927</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-13952.92705948735</v>
       </c>
       <c r="Y17" t="n">
         <v>414.5571719338185</v>
       </c>
       <c r="Z17" t="n">
-        <v>453135520.0351815</v>
+        <v>127.9780000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>3.514813113505032e-07</v>
@@ -7132,19 +7132,19 @@
       <c r="K18" t="n">
         <v>88.08303827008297</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 29.878x + -13660.225</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-13660.22456612663</v>
       </c>
       <c r="Y18" t="n">
         <v>411.5259476161896</v>
       </c>
       <c r="Z18" t="n">
-        <v>168743346.0635722</v>
+        <v>126.532</v>
       </c>
       <c r="AA18" t="n">
         <v>3.493103631632429e-07</v>
@@ -7184,19 +7184,19 @@
       <c r="K19" t="n">
         <v>88.21451588060602</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 32.079x + -14606.625</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-14606.62462238206</v>
       </c>
       <c r="Y19" t="n">
         <v>408.5105256298336</v>
       </c>
       <c r="Z19" t="n">
-        <v>334777631.6739607</v>
+        <v>122.514</v>
       </c>
       <c r="AA19" t="n">
         <v>3.476259962158232e-07</v>
@@ -7236,19 +7236,19 @@
       <c r="K20" t="n">
         <v>88.09506374441214</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 30.066x + -13508.934</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-13508.93400573216</v>
       </c>
       <c r="Y20" t="n">
         <v>405.4855688446784</v>
       </c>
       <c r="Z20" t="n">
-        <v>221692713.7646232</v>
+        <v>122.7719999999999</v>
       </c>
       <c r="AA20" t="n">
         <v>3.45904275648366e-07</v>
@@ -7288,19 +7288,19 @@
       <c r="K21" t="n">
         <v>88.15756103992196</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 31.087x + -13874.030</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-13874.02972793589</v>
       </c>
       <c r="Y21" t="n">
         <v>402.5010659986688</v>
       </c>
       <c r="Z21" t="n">
-        <v>331821560.834577</v>
+        <v>121.852</v>
       </c>
       <c r="AA21" t="n">
         <v>3.442378256849942e-07</v>
@@ -7340,19 +7340,19 @@
       <c r="K22" t="n">
         <v>88.14656903179977</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 30.903x + -13663.820</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-13663.81967361734</v>
       </c>
       <c r="Y22" t="n">
         <v>399.5148303094026</v>
       </c>
       <c r="Z22" t="n">
-        <v>436922180.5574364</v>
+        <v>116.947</v>
       </c>
       <c r="AA22" t="n">
         <v>3.422039977735035e-07</v>
@@ -7478,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7538,19 +7538,19 @@
       <c r="K2" t="n">
         <v>84.08308845444594</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.649x + -5134.761</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5134.761399588653</v>
       </c>
       <c r="Y2" t="n">
         <v>447.2608542610588</v>
       </c>
       <c r="Z2" t="n">
-        <v>360712415.1757494</v>
+        <v>502.2120000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>6.787841699857573e-07</v>
@@ -7590,19 +7590,19 @@
       <c r="K3" t="n">
         <v>85.96212121317983</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.166x + -6697.682</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6697.681925217379</v>
       </c>
       <c r="Y3" t="n">
         <v>400.1974333256916</v>
       </c>
       <c r="Z3" t="n">
-        <v>3457.066656048483</v>
+        <v>347.258</v>
       </c>
       <c r="AA3" t="n">
         <v>1.49665477798724e-06</v>
@@ -7642,19 +7642,19 @@
       <c r="K4" t="n">
         <v>86.74631749462222</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 17.591x + -8090.893</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8090.892774284126</v>
       </c>
       <c r="Y4" t="n">
         <v>412.4612535545218</v>
       </c>
       <c r="Z4" t="n">
-        <v>175598348.1537231</v>
+        <v>281.103</v>
       </c>
       <c r="AA4" t="n">
         <v>4.487309756219125e-07</v>
@@ -7694,19 +7694,19 @@
       <c r="K5" t="n">
         <v>87.07557598061601</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 19.575x + -8829.035</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8829.035159041612</v>
       </c>
       <c r="Y5" t="n">
         <v>407.3470578961657</v>
       </c>
       <c r="Z5" t="n">
-        <v>111318800.5883842</v>
+        <v>246.028</v>
       </c>
       <c r="AA5" t="n">
         <v>4.182032860857763e-07</v>
@@ -7746,19 +7746,19 @@
       <c r="K6" t="n">
         <v>87.38996086624113</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 21.937x + -9770.280</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-9770.280128072411</v>
       </c>
       <c r="Y6" t="n">
         <v>402.3688986980127</v>
       </c>
       <c r="Z6" t="n">
-        <v>329501850.603974</v>
+        <v>215.908</v>
       </c>
       <c r="AA6" t="n">
         <v>3.9729317622861e-07</v>
@@ -7798,19 +7798,19 @@
       <c r="K7" t="n">
         <v>87.56119821939389</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 23.479x + -10307.517</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10307.51734490165</v>
       </c>
       <c r="Y7" t="n">
         <v>397.415658651056</v>
       </c>
       <c r="Z7" t="n">
-        <v>218840704.1563608</v>
+        <v>198.8419999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>3.836214915534863e-07</v>
@@ -7850,19 +7850,19 @@
       <c r="K8" t="n">
         <v>87.67500104510698</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 24.630x + -10652.905</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-10652.90482962498</v>
       </c>
       <c r="Y8" t="n">
         <v>392.7104613324146</v>
       </c>
       <c r="Z8" t="n">
-        <v>107181455.5656053</v>
+        <v>185.855</v>
       </c>
       <c r="AA8" t="n">
         <v>3.731376418170977e-07</v>
@@ -7902,19 +7902,19 @@
       <c r="K9" t="n">
         <v>87.80491201635911</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 26.089x + -11149.284</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11149.28377621135</v>
       </c>
       <c r="Y9" t="n">
         <v>388.4101290095276</v>
       </c>
       <c r="Z9" t="n">
-        <v>158973472.4001223</v>
+        <v>173.868</v>
       </c>
       <c r="AA9" t="n">
         <v>3.65152339941978e-07</v>
@@ -7954,19 +7954,19 @@
       <c r="K10" t="n">
         <v>87.85530636547489</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 26.703x + -11274.804</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-11274.80434193135</v>
       </c>
       <c r="Y10" t="n">
         <v>384.4091790697254</v>
       </c>
       <c r="Z10" t="n">
-        <v>628613980.98006</v>
+        <v>170.251</v>
       </c>
       <c r="AA10" t="n">
         <v>3.598723325225615e-07</v>
@@ -8006,19 +8006,19 @@
       <c r="K11" t="n">
         <v>87.97109499077021</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 28.228x + -11794.199</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11794.19885323564</v>
       </c>
       <c r="Y11" t="n">
         <v>380.3166287316536</v>
       </c>
       <c r="Z11" t="n">
-        <v>207343975.1091103</v>
+        <v>158.229</v>
       </c>
       <c r="AA11" t="n">
         <v>3.539633503169021e-07</v>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -8204,19 +8204,19 @@
       <c r="K2" t="n">
         <v>86.6967744138974</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 17.326x + -9647.423</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-9647.422723588208</v>
       </c>
       <c r="Y2" t="n">
         <v>476.5721033888777</v>
       </c>
       <c r="Z2" t="n">
-        <v>32616356.86377891</v>
+        <v>269.9549999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>4.840721463029202e-07</v>
@@ -8256,19 +8256,19 @@
       <c r="K3" t="n">
         <v>87.42191370389277</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 22.209x + -11709.437</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-11709.43650743262</v>
       </c>
       <c r="Y3" t="n">
         <v>462.5869755842085</v>
       </c>
       <c r="Z3" t="n">
-        <v>26239456.73372998</v>
+        <v>202.054</v>
       </c>
       <c r="AA3" t="n">
         <v>4.217473612483152e-07</v>
@@ -8308,19 +8308,19 @@
       <c r="K4" t="n">
         <v>87.60855465954982</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 23.945x + -12376.459</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-12376.45852350311</v>
       </c>
       <c r="Y4" t="n">
         <v>456.9434479126721</v>
       </c>
       <c r="Z4" t="n">
-        <v>188258830.4061645</v>
+        <v>178.7979999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>4.017273873978845e-07</v>
@@ -8360,19 +8360,19 @@
       <c r="K5" t="n">
         <v>87.73643486088176</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 25.299x + -12926.947</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-12926.94694102056</v>
       </c>
       <c r="Y5" t="n">
         <v>452.2621544931089</v>
       </c>
       <c r="Z5" t="n">
-        <v>124547803.1700962</v>
+        <v>166.908</v>
       </c>
       <c r="AA5" t="n">
         <v>3.908531247009425e-07</v>
@@ -8412,19 +8412,19 @@
       <c r="K6" t="n">
         <v>87.90473245000915</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 27.333x + -13841.239</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-13841.23949737114</v>
       </c>
       <c r="Y6" t="n">
         <v>426.5961128333809</v>
       </c>
       <c r="Z6" t="n">
-        <v>3684.652092205249</v>
+        <v>156.376</v>
       </c>
       <c r="AA6" t="n">
         <v>1.335455556498187e-06</v>
@@ -8464,19 +8464,19 @@
       <c r="K7" t="n">
         <v>87.83408140324777</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 26.441x + -13149.566</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-13149.56585572598</v>
       </c>
       <c r="Y7" t="n">
         <v>422.6749463804728</v>
       </c>
       <c r="Z7" t="n">
-        <v>3642.189151459356</v>
+        <v>149.321</v>
       </c>
       <c r="AA7" t="n">
         <v>1.864454460717978e-06</v>
@@ -8516,19 +8516,19 @@
       <c r="K8" t="n">
         <v>87.97585160834232</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 28.294x + -13956.665</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-13956.66516406941</v>
       </c>
       <c r="Y8" t="n">
         <v>438.112749893103</v>
       </c>
       <c r="Z8" t="n">
-        <v>179792642.771854</v>
+        <v>146.064</v>
       </c>
       <c r="AA8" t="n">
         <v>3.721556559962741e-07</v>
@@ -8568,19 +8568,19 @@
       <c r="K9" t="n">
         <v>87.96396673717531</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 28.129x + -13686.828</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-13686.82832258121</v>
       </c>
       <c r="Y9" t="n">
         <v>434.2094682901393</v>
       </c>
       <c r="Z9" t="n">
-        <v>475241279.9076642</v>
+        <v>140.314</v>
       </c>
       <c r="AA9" t="n">
         <v>3.673586660074046e-07</v>
@@ -8620,19 +8620,19 @@
       <c r="K10" t="n">
         <v>88.00037049837363</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 28.642x + -13804.790</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-13804.79004941218</v>
       </c>
       <c r="Y10" t="n">
         <v>430.6504935008618</v>
       </c>
       <c r="Z10" t="n">
-        <v>117791125.0711426</v>
+        <v>137.398</v>
       </c>
       <c r="AA10" t="n">
         <v>3.643612089453659e-07</v>
@@ -8672,19 +8672,19 @@
       <c r="K11" t="n">
         <v>88.01240660309304</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 28.815x + -13755.979</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-13755.97854030204</v>
       </c>
       <c r="Y11" t="n">
         <v>427.2898349614363</v>
       </c>
       <c r="Z11" t="n">
-        <v>175414089.0588971</v>
+        <v>136.163</v>
       </c>
       <c r="AA11" t="n">
         <v>3.617815616241259e-07</v>
@@ -8724,19 +8724,19 @@
       <c r="K12" t="n">
         <v>88.04229837464453</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 29.255x + -13843.933</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-13843.93283311992</v>
       </c>
       <c r="Y12" t="n">
         <v>424.2052365218456</v>
       </c>
       <c r="Z12" t="n">
-        <v>174333779.1887518</v>
+        <v>128.955</v>
       </c>
       <c r="AA12" t="n">
         <v>3.58150876896356e-07</v>
@@ -8776,19 +8776,19 @@
       <c r="K13" t="n">
         <v>88.13913333434772</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 30.779x + -14493.377</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-14493.37747334547</v>
       </c>
       <c r="Y13" t="n">
         <v>421.1424903195542</v>
       </c>
       <c r="Z13" t="n">
-        <v>172944089.5054938</v>
+        <v>129.674</v>
       </c>
       <c r="AA13" t="n">
         <v>3.569231144901565e-07</v>
@@ -8828,19 +8828,19 @@
       <c r="K14" t="n">
         <v>88.14187484781961</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 30.824x + -14382.641</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-14382.64092711181</v>
       </c>
       <c r="Y14" t="n">
         <v>418.1995125728263</v>
       </c>
       <c r="Z14" t="n">
-        <v>114458354.7393551</v>
+        <v>126.3419999999999</v>
       </c>
       <c r="AA14" t="n">
         <v>3.542281346934422e-07</v>
@@ -8880,19 +8880,19 @@
       <c r="K15" t="n">
         <v>88.04751394560952</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 29.334x + -13528.192</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-13528.19225082068</v>
       </c>
       <c r="Y15" t="n">
         <v>415.2940601923247</v>
       </c>
       <c r="Z15" t="n">
-        <v>113880481.0897932</v>
+        <v>126.863</v>
       </c>
       <c r="AA15" t="n">
         <v>3.527569266650081e-07</v>
@@ -8932,19 +8932,19 @@
       <c r="K16" t="n">
         <v>88.28065316677706</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 33.314x + -15366.032</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-15366.03192059773</v>
       </c>
       <c r="Y16" t="n">
         <v>412.4653666218679</v>
       </c>
       <c r="Z16" t="n">
-        <v>170016055.2832703</v>
+        <v>121.2</v>
       </c>
       <c r="AA16" t="n">
         <v>3.508072820551902e-07</v>
@@ -8984,19 +8984,19 @@
       <c r="K17" t="n">
         <v>88.22652662564285</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 32.297x + -14747.401</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-14747.40100343068</v>
       </c>
       <c r="Y17" t="n">
         <v>409.6914866273248</v>
       </c>
       <c r="Z17" t="n">
-        <v>223941085.9405902</v>
+        <v>118.9429999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>3.489212786123147e-07</v>
@@ -9036,19 +9036,19 @@
       <c r="K18" t="n">
         <v>88.23707281632849</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 32.490x + -14718.158</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-14718.15831226745</v>
       </c>
       <c r="Y18" t="n">
         <v>406.9016518111838</v>
       </c>
       <c r="Z18" t="n">
-        <v>445599249.1035966</v>
+        <v>115.905</v>
       </c>
       <c r="AA18" t="n">
         <v>3.472231600958838e-07</v>
@@ -9088,19 +9088,19 @@
       <c r="K19" t="n">
         <v>88.27434074236413</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 33.192x + -14929.605</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-14929.60479392341</v>
       </c>
       <c r="Y19" t="n">
         <v>404.0651842629732</v>
       </c>
       <c r="Z19" t="n">
-        <v>661839284.8314869</v>
+        <v>112.6900000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>3.453166066346132e-07</v>
@@ -9140,19 +9140,19 @@
       <c r="K20" t="n">
         <v>88.29242628008754</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 33.544x + -14975.823</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-14975.82267919341</v>
       </c>
       <c r="Y20" t="n">
         <v>401.2731753297563</v>
       </c>
       <c r="Z20" t="n">
-        <v>109954655.0377423</v>
+        <v>114.655</v>
       </c>
       <c r="AA20" t="n">
         <v>3.439855398064399e-07</v>
@@ -9192,19 +9192,19 @@
       <c r="K21" t="n">
         <v>88.22900338411642</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 32.342x + -14283.628</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-14283.62846338707</v>
       </c>
       <c r="Y21" t="n">
         <v>398.4425835561854</v>
       </c>
       <c r="Z21" t="n">
-        <v>109012463.3348543</v>
+        <v>113.539</v>
       </c>
       <c r="AA21" t="n">
         <v>3.426062937967993e-07</v>
@@ -9244,19 +9244,19 @@
       <c r="K22" t="n">
         <v>88.26054355963502</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 32.929x + -14444.860</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-14444.86047287876</v>
       </c>
       <c r="Y22" t="n">
         <v>395.5741458391194</v>
       </c>
       <c r="Z22" t="n">
-        <v>216197133.3926557</v>
+        <v>115.079</v>
       </c>
       <c r="AA22" t="n">
         <v>3.420991244525461e-07</v>
@@ -9382,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -9442,19 +9442,19 @@
       <c r="K2" t="n">
         <v>85.34755638349567</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.288x + -5813.035</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5813.034705871516</v>
       </c>
       <c r="Y2" t="n">
         <v>413.3995528377526</v>
       </c>
       <c r="Z2" t="n">
-        <v>225684152.6048389</v>
+        <v>402.064</v>
       </c>
       <c r="AA2" t="n">
         <v>5.241173545103358e-07</v>
@@ -9494,19 +9494,19 @@
       <c r="K3" t="n">
         <v>87.03956231471548</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 19.337x + -8647.872</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8647.872406315368</v>
       </c>
       <c r="Y3" t="n">
         <v>397.8529853889657</v>
       </c>
       <c r="Z3" t="n">
-        <v>112885517.5216535</v>
+        <v>260.005</v>
       </c>
       <c r="AA3" t="n">
         <v>4.160469132995124e-07</v>
@@ -9546,19 +9546,19 @@
       <c r="K4" t="n">
         <v>87.45931583278877</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 22.537x + -9808.825</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9808.825267630049</v>
       </c>
       <c r="Y4" t="n">
         <v>391.3386659647608</v>
       </c>
       <c r="Z4" t="n">
-        <v>108290984.225836</v>
+        <v>211.74</v>
       </c>
       <c r="AA4" t="n">
         <v>3.837920383609075e-07</v>
@@ -9598,19 +9598,19 @@
       <c r="K5" t="n">
         <v>87.67444672224893</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 24.624x + -10553.448</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-10553.44763209426</v>
       </c>
       <c r="Y5" t="n">
         <v>386.3690046309804</v>
       </c>
       <c r="Z5" t="n">
-        <v>157949997.6588617</v>
+        <v>190.444</v>
       </c>
       <c r="AA5" t="n">
         <v>3.688402224524403e-07</v>
@@ -9650,19 +9650,19 @@
       <c r="K6" t="n">
         <v>87.77620126723748</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 25.752x + -10847.430</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10847.43029960969</v>
       </c>
       <c r="Y6" t="n">
         <v>381.3808015938022</v>
       </c>
       <c r="Z6" t="n">
-        <v>518900397.9970644</v>
+        <v>172.473</v>
       </c>
       <c r="AA6" t="n">
         <v>3.580863380424837e-07</v>
@@ -9702,19 +9702,19 @@
       <c r="K7" t="n">
         <v>87.82889808127788</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 26.378x + -10925.455</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-10925.45541698337</v>
       </c>
       <c r="Y7" t="n">
         <v>376.3327505729329</v>
       </c>
       <c r="Z7" t="n">
-        <v>205146431.2838763</v>
+        <v>165.8600000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>3.515607192078831e-07</v>
@@ -9754,19 +9754,19 @@
       <c r="K8" t="n">
         <v>88.00106853694072</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 28.652x + -11732.964</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-11732.96445154462</v>
       </c>
       <c r="Y8" t="n">
         <v>371.3978966041586</v>
       </c>
       <c r="Z8" t="n">
-        <v>101185515.6043342</v>
+        <v>151.4440000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>3.451356492579932e-07</v>
@@ -9806,19 +9806,19 @@
       <c r="K9" t="n">
         <v>87.99679155326329</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 28.590x + -11509.331</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-11509.33134619516</v>
       </c>
       <c r="Y9" t="n">
         <v>366.7219718483795</v>
       </c>
       <c r="Z9" t="n">
-        <v>398717668.0373393</v>
+        <v>147.945</v>
       </c>
       <c r="AA9" t="n">
         <v>3.414772267556041e-07</v>
@@ -9858,19 +9858,19 @@
       <c r="K10" t="n">
         <v>87.70829093751166</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 24.988x + -9790.788</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-9790.787598396972</v>
       </c>
       <c r="Y10" t="n">
         <v>362.3537054803389</v>
       </c>
       <c r="Z10" t="n">
-        <v>197025356.9286698</v>
+        <v>148.651</v>
       </c>
       <c r="AA10" t="n">
         <v>3.378478295031829e-07</v>
@@ -9910,19 +9910,19 @@
       <c r="K11" t="n">
         <v>88.08199058568086</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 29.861x + -11700.289</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-11700.28864134019</v>
       </c>
       <c r="Y11" t="n">
         <v>358.2962929249304</v>
       </c>
       <c r="Z11" t="n">
-        <v>97464261.31029435</v>
+        <v>139.839</v>
       </c>
       <c r="AA11" t="n">
         <v>3.351133738062318e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>87.39461527861948</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 21.976x + -12302.187</t>
-        </is>
+      <c r="W2" t="n">
+        <v>21.97613367545502</v>
       </c>
       <c r="X2" t="n">
         <v>-12302.18729375609</v>
@@ -600,7 +598,7 @@
         <v>484.6443158837664</v>
       </c>
       <c r="Z2" t="n">
-        <v>206.9680000000001</v>
+        <v>19228163.5771528</v>
       </c>
       <c r="AA2" t="n">
         <v>4.107426050646521e-07</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>87.67246975244326</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 24.603x + -13530.070</t>
-        </is>
+      <c r="W3" t="n">
+        <v>24.60301384559166</v>
       </c>
       <c r="X3" t="n">
         <v>-13530.06999235967</v>
@@ -652,7 +648,7 @@
         <v>477.610994005233</v>
       </c>
       <c r="Z3" t="n">
-        <v>180.5890000000001</v>
+        <v>21988711.72870108</v>
       </c>
       <c r="AA3" t="n">
         <v>3.915264688983131e-07</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>87.80919344445904</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 26.140x + -14158.248</t>
-        </is>
+      <c r="W4" t="n">
+        <v>26.14007773126362</v>
       </c>
       <c r="X4" t="n">
         <v>-14158.24750389202</v>
@@ -704,7 +698,7 @@
         <v>471.647745107983</v>
       </c>
       <c r="Z4" t="n">
-        <v>165.962</v>
+        <v>198526337.7212156</v>
       </c>
       <c r="AA4" t="n">
         <v>3.800388687384269e-07</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>87.88978892630244</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 27.139x + -14484.736</t>
-        </is>
+      <c r="W5" t="n">
+        <v>27.1394039362598</v>
       </c>
       <c r="X5" t="n">
         <v>-14484.73554295575</v>
@@ -756,7 +748,7 @@
         <v>466.0288724821089</v>
       </c>
       <c r="Z5" t="n">
-        <v>157.841</v>
+        <v>214628173.4481199</v>
       </c>
       <c r="AA5" t="n">
         <v>3.725087214834107e-07</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>87.89963115757922</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 27.267x + -14312.646</t>
-        </is>
+      <c r="W6" t="n">
+        <v>27.26669273675385</v>
       </c>
       <c r="X6" t="n">
         <v>-14312.64573083237</v>
@@ -808,7 +798,7 @@
         <v>460.5595015553163</v>
       </c>
       <c r="Z6" t="n">
-        <v>147.615</v>
+        <v>189707742.4385588</v>
       </c>
       <c r="AA6" t="n">
         <v>3.650324725381416e-07</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>87.84186301966545</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 26.536x + -13685.166</t>
-        </is>
+      <c r="W7" t="n">
+        <v>26.53616564366855</v>
       </c>
       <c r="X7" t="n">
         <v>-13685.16593608196</v>
@@ -860,7 +848,7 @@
         <v>455.2543043898323</v>
       </c>
       <c r="Z7" t="n">
-        <v>141.347</v>
+        <v>373937725.723335</v>
       </c>
       <c r="AA7" t="n">
         <v>3.593354466531468e-07</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>87.98768526015695</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 28.461x + -14541.543</t>
-        </is>
+      <c r="W8" t="n">
+        <v>28.46086545289152</v>
       </c>
       <c r="X8" t="n">
         <v>-14541.54287731682</v>
@@ -912,7 +898,7 @@
         <v>450.2182700074694</v>
       </c>
       <c r="Z8" t="n">
-        <v>138.753</v>
+        <v>35605802.02243853</v>
       </c>
       <c r="AA8" t="n">
         <v>3.552398619253264e-07</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>87.94828864672735</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 27.914x + -14048.106</t>
-        </is>
+      <c r="W9" t="n">
+        <v>27.91391066599932</v>
       </c>
       <c r="X9" t="n">
         <v>-14048.10619405686</v>
@@ -964,7 +948,7 @@
         <v>419.8404706492517</v>
       </c>
       <c r="Z9" t="n">
-        <v>135.886</v>
+        <v>3667.096846773316</v>
       </c>
       <c r="AA9" t="n">
         <v>1.563779375131226e-06</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>88.10017472847596</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 30.147x + -15050.771</t>
-        </is>
+      <c r="W10" t="n">
+        <v>30.14739332413253</v>
       </c>
       <c r="X10" t="n">
         <v>-15050.77117242096</v>
@@ -1016,7 +998,7 @@
         <v>437.8462330691353</v>
       </c>
       <c r="Z10" t="n">
-        <v>125.828</v>
+        <v>3627.702964538223</v>
       </c>
       <c r="AA10" t="n">
         <v>4.368033539037081e-07</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>88.06272806623817</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 29.564x + -14576.068</t>
-        </is>
+      <c r="W11" t="n">
+        <v>29.56422516144653</v>
       </c>
       <c r="X11" t="n">
         <v>-14576.0684310631</v>
@@ -1068,7 +1048,7 @@
         <v>416.803775935856</v>
       </c>
       <c r="Z11" t="n">
-        <v>127.311</v>
+        <v>3595.226063989589</v>
       </c>
       <c r="AA11" t="n">
         <v>1.234273032482909e-06</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>87.3183707240958</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 21.350x + -11554.185</t>
-        </is>
+      <c r="W2" t="n">
+        <v>21.35042960103915</v>
       </c>
       <c r="X2" t="n">
         <v>-11554.18489641194</v>
@@ -1266,7 +1244,7 @@
         <v>464.5669167919543</v>
       </c>
       <c r="Z2" t="n">
-        <v>206.165</v>
+        <v>26010957.61006243</v>
       </c>
       <c r="AA2" t="n">
         <v>4.22327079787798e-07</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>87.7168858655324</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 25.082x + -12928.232</t>
-        </is>
+      <c r="W3" t="n">
+        <v>25.08216724749043</v>
       </c>
       <c r="X3" t="n">
         <v>-12928.23248599209</v>
@@ -1318,7 +1294,7 @@
         <v>452.4099188020935</v>
       </c>
       <c r="Z3" t="n">
-        <v>164.432</v>
+        <v>372410298.8638328</v>
       </c>
       <c r="AA3" t="n">
         <v>3.876169113099555e-07</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>87.79074755562127</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 25.922x + -13112.049</t>
-        </is>
+      <c r="W4" t="n">
+        <v>25.92161050751799</v>
       </c>
       <c r="X4" t="n">
         <v>-13112.04858847742</v>
@@ -1370,7 +1344,7 @@
         <v>447.1016415901562</v>
       </c>
       <c r="Z4" t="n">
-        <v>152.111</v>
+        <v>119782754.3855883</v>
       </c>
       <c r="AA4" t="n">
         <v>3.762666515441864e-07</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>87.89770132987779</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 27.242x + -13642.246</t>
-        </is>
+      <c r="W5" t="n">
+        <v>27.24164053426838</v>
       </c>
       <c r="X5" t="n">
         <v>-13642.24631611201</v>
@@ -1422,7 +1394,7 @@
         <v>421.6536137753115</v>
       </c>
       <c r="Z5" t="n">
-        <v>144.179</v>
+        <v>3646.089233381663</v>
       </c>
       <c r="AA5" t="n">
         <v>7.572356582753557e-07</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>87.87090305260176</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 26.898x + -13286.158</t>
-        </is>
+      <c r="W6" t="n">
+        <v>26.89844862017729</v>
       </c>
       <c r="X6" t="n">
         <v>-13286.15777740048</v>
@@ -1474,7 +1444,7 @@
         <v>419.4976855283768</v>
       </c>
       <c r="Z6" t="n">
-        <v>139.024</v>
+        <v>3610.386733990646</v>
       </c>
       <c r="AA6" t="n">
         <v>1.490054047196679e-06</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>87.95822994094442</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 28.050x + -13729.956</t>
-        </is>
+      <c r="W7" t="n">
+        <v>28.04993831943644</v>
       </c>
       <c r="X7" t="n">
         <v>-13729.95598918011</v>
@@ -1526,7 +1494,7 @@
         <v>434.5103365912532</v>
       </c>
       <c r="Z7" t="n">
-        <v>138.9730000000001</v>
+        <v>237920712.0999677</v>
       </c>
       <c r="AA7" t="n">
         <v>3.627429524089212e-07</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>87.9994241946994</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 28.628x + -13847.858</t>
-        </is>
+      <c r="W8" t="n">
+        <v>28.62800450269415</v>
       </c>
       <c r="X8" t="n">
         <v>-13847.85787379509</v>
@@ -1578,7 +1544,7 @@
         <v>430.4014385069506</v>
       </c>
       <c r="Z8" t="n">
-        <v>132.0040000000001</v>
+        <v>133690707.1178724</v>
       </c>
       <c r="AA8" t="n">
         <v>3.58462807520919e-07</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>87.94642311723564</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 27.889x + -13309.105</t>
-        </is>
+      <c r="W9" t="n">
+        <v>27.88853115028803</v>
       </c>
       <c r="X9" t="n">
         <v>-13309.10489660023</v>
@@ -1630,7 +1594,7 @@
         <v>426.597419479509</v>
       </c>
       <c r="Z9" t="n">
-        <v>128.7810000000001</v>
+        <v>235269496.7540282</v>
       </c>
       <c r="AA9" t="n">
         <v>3.55385637411946e-07</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>88.0763815727701</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 29.774x + -14119.930</t>
-        </is>
+      <c r="W10" t="n">
+        <v>29.77422630497227</v>
       </c>
       <c r="X10" t="n">
         <v>-14119.92997259863</v>
@@ -1682,7 +1644,7 @@
         <v>423.0732388556012</v>
       </c>
       <c r="Z10" t="n">
-        <v>124.763</v>
+        <v>347548888.3566003</v>
       </c>
       <c r="AA10" t="n">
         <v>3.531580115747654e-07</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>88.0241065231758</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 28.986x + -13594.470</t>
-        </is>
+      <c r="W11" t="n">
+        <v>28.98590684697566</v>
       </c>
       <c r="X11" t="n">
         <v>-13594.47007781174</v>
@@ -1734,7 +1694,7 @@
         <v>419.7788442639665</v>
       </c>
       <c r="Z11" t="n">
-        <v>127.144</v>
+        <v>343953770.7519221</v>
       </c>
       <c r="AA11" t="n">
         <v>3.516475567163398e-07</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>88.08897335398645</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 29.971x + -13953.988</t>
-        </is>
+      <c r="W12" t="n">
+        <v>29.97055611390621</v>
       </c>
       <c r="X12" t="n">
         <v>-13953.9877206023</v>
@@ -1786,7 +1744,7 @@
         <v>416.6056952702053</v>
       </c>
       <c r="Z12" t="n">
-        <v>122.708</v>
+        <v>227892616.6250862</v>
       </c>
       <c r="AA12" t="n">
         <v>3.487872541914937e-07</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>88.1872777332149</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 31.597x + -14629.521</t>
-        </is>
+      <c r="W13" t="n">
+        <v>31.59704182746031</v>
       </c>
       <c r="X13" t="n">
         <v>-14629.52137263942</v>
@@ -1838,7 +1794,7 @@
         <v>413.5657963968105</v>
       </c>
       <c r="Z13" t="n">
-        <v>119.515</v>
+        <v>226496233.9343009</v>
       </c>
       <c r="AA13" t="n">
         <v>3.46955902032398e-07</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>88.17638969275393</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 31.408x + -14410.467</t>
-        </is>
+      <c r="W14" t="n">
+        <v>31.40826232809791</v>
       </c>
       <c r="X14" t="n">
         <v>-14410.46686349054</v>
@@ -1890,7 +1844,7 @@
         <v>410.5436983794904</v>
       </c>
       <c r="Z14" t="n">
-        <v>118.287</v>
+        <v>224314187.4534663</v>
       </c>
       <c r="AA14" t="n">
         <v>3.457145011466897e-07</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>88.14866558434818</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 30.938x + -14057.289</t>
-        </is>
+      <c r="W15" t="n">
+        <v>30.93759701559114</v>
       </c>
       <c r="X15" t="n">
         <v>-14057.28857993719</v>
@@ -1942,7 +1894,7 @@
         <v>407.6201432992885</v>
       </c>
       <c r="Z15" t="n">
-        <v>122.745</v>
+        <v>167063955.362845</v>
       </c>
       <c r="AA15" t="n">
         <v>3.448318077236802e-07</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>88.27917396102336</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 33.285x + -15064.929</t>
-        </is>
+      <c r="W16" t="n">
+        <v>33.28549741258575</v>
       </c>
       <c r="X16" t="n">
         <v>-15064.92912862336</v>
@@ -1994,7 +1944,7 @@
         <v>404.7066783950125</v>
       </c>
       <c r="Z16" t="n">
-        <v>113.441</v>
+        <v>221101391.716084</v>
       </c>
       <c r="AA16" t="n">
         <v>3.418394142851484e-07</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>88.21556661339291</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 32.098x + -14371.822</t>
-        </is>
+      <c r="W17" t="n">
+        <v>32.09828610340357</v>
       </c>
       <c r="X17" t="n">
         <v>-14371.82169837948</v>
@@ -2046,7 +1994,7 @@
         <v>401.7001586722404</v>
       </c>
       <c r="Z17" t="n">
-        <v>115.513</v>
+        <v>110069402.4358505</v>
       </c>
       <c r="AA17" t="n">
         <v>3.410235923320787e-07</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>88.15173826279475</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 30.989x + -13715.592</t>
-        </is>
+      <c r="W18" t="n">
+        <v>30.98906560861343</v>
       </c>
       <c r="X18" t="n">
         <v>-13715.59214289839</v>
@@ -2098,7 +2044,7 @@
         <v>398.8003103118868</v>
       </c>
       <c r="Z18" t="n">
-        <v>112.773</v>
+        <v>128816779.3976977</v>
       </c>
       <c r="AA18" t="n">
         <v>3.393441483635864e-07</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>88.25754330700138</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 32.872x + -14476.939</t>
-        </is>
+      <c r="W19" t="n">
+        <v>32.87204498014256</v>
       </c>
       <c r="X19" t="n">
         <v>-14476.93932113545</v>
@@ -2150,7 +2094,7 @@
         <v>395.7982449995955</v>
       </c>
       <c r="Z19" t="n">
-        <v>111.799</v>
+        <v>164083270.5618534</v>
       </c>
       <c r="AA19" t="n">
         <v>3.381774309808566e-07</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>88.1554096332045</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 31.051x + -13502.758</t>
-        </is>
+      <c r="W20" t="n">
+        <v>31.05078729366587</v>
       </c>
       <c r="X20" t="n">
         <v>-13502.75764225445</v>
@@ -2202,7 +2144,7 @@
         <v>392.7764364802676</v>
       </c>
       <c r="Z20" t="n">
-        <v>113.845</v>
+        <v>551036241.5742298</v>
       </c>
       <c r="AA20" t="n">
         <v>3.372725973788375e-07</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>88.19933669033118</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 31.809x + -13732.673</t>
-        </is>
+      <c r="W21" t="n">
+        <v>31.80878652467958</v>
       </c>
       <c r="X21" t="n">
         <v>-13732.67334728539</v>
@@ -2254,7 +2194,7 @@
         <v>389.650751228401</v>
       </c>
       <c r="Z21" t="n">
-        <v>109.122</v>
+        <v>162026564.2009178</v>
       </c>
       <c r="AA21" t="n">
         <v>3.350946982634335e-07</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>88.35404138940973</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 34.800x + -14964.801</t>
-        </is>
+      <c r="W22" t="n">
+        <v>34.80039954130096</v>
       </c>
       <c r="X22" t="n">
         <v>-14964.80139226499</v>
@@ -2306,7 +2244,7 @@
         <v>386.626075689845</v>
       </c>
       <c r="Z22" t="n">
-        <v>106.591</v>
+        <v>316634737.7815642</v>
       </c>
       <c r="AA22" t="n">
         <v>3.339554145431989e-07</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>87.82463100570338</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 26.326x + -14156.609</t>
-        </is>
+      <c r="W2" t="n">
+        <v>26.32576175233953</v>
       </c>
       <c r="X2" t="n">
         <v>-14156.60907079565</v>
@@ -2504,7 +2440,7 @@
         <v>474.940972567993</v>
       </c>
       <c r="Z2" t="n">
-        <v>159.962</v>
+        <v>264274225.8072468</v>
       </c>
       <c r="AA2" t="n">
         <v>3.836824299068841e-07</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>88.01404903950372</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 28.839x + -15440.277</t>
-        </is>
+      <c r="W3" t="n">
+        <v>28.83899630220304</v>
       </c>
       <c r="X3" t="n">
         <v>-15440.27682491637</v>
@@ -2556,7 +2490,7 @@
         <v>472.1234971601919</v>
       </c>
       <c r="Z3" t="n">
-        <v>140.202</v>
+        <v>646073718.2939132</v>
       </c>
       <c r="AA3" t="n">
         <v>3.718775417466821e-07</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>87.98906967238008</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 28.480x + -15076.164</t>
-        </is>
+      <c r="W4" t="n">
+        <v>28.4804752716678</v>
       </c>
       <c r="X4" t="n">
         <v>-15076.16360233346</v>
@@ -2608,7 +2540,7 @@
         <v>468.2093199297603</v>
       </c>
       <c r="Z4" t="n">
-        <v>135.4440000000001</v>
+        <v>512473875.0277551</v>
       </c>
       <c r="AA4" t="n">
         <v>3.659261456371368e-07</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>88.06437747428716</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 29.589x + -15503.248</t>
-        </is>
+      <c r="W5" t="n">
+        <v>29.58943701951071</v>
       </c>
       <c r="X5" t="n">
         <v>-15503.24818225107</v>
@@ -2660,7 +2590,7 @@
         <v>463.6177622555926</v>
       </c>
       <c r="Z5" t="n">
-        <v>126.332</v>
+        <v>60892684.35987416</v>
       </c>
       <c r="AA5" t="n">
         <v>3.595944668508762e-07</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>88.02232667868783</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 28.960x + -14949.686</t>
-        </is>
+      <c r="W6" t="n">
+        <v>28.95979972881238</v>
       </c>
       <c r="X6" t="n">
         <v>-14949.68620077269</v>
@@ -2712,7 +2640,7 @@
         <v>448.6815921335364</v>
       </c>
       <c r="Z6" t="n">
-        <v>121.292</v>
+        <v>3774.299972311237</v>
       </c>
       <c r="AA6" t="n">
         <v>1.307615251359875e-06</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>88.2415176291673</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 32.572x + -16713.111</t>
-        </is>
+      <c r="W7" t="n">
+        <v>32.57228465432224</v>
       </c>
       <c r="X7" t="n">
         <v>-16713.11102416616</v>
@@ -2764,7 +2690,7 @@
         <v>434.9773937411602</v>
       </c>
       <c r="Z7" t="n">
-        <v>114.8820000000001</v>
+        <v>3733.140458215095</v>
       </c>
       <c r="AA7" t="n">
         <v>1.301724932490023e-06</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>88.20451644591891</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 31.901x + -16136.462</t>
-        </is>
+      <c r="W8" t="n">
+        <v>31.90061143838176</v>
       </c>
       <c r="X8" t="n">
         <v>-16136.46163690372</v>
@@ -2816,7 +2740,7 @@
         <v>434.7262552700104</v>
       </c>
       <c r="Z8" t="n">
-        <v>110.843</v>
+        <v>7441.511081075255</v>
       </c>
       <c r="AA8" t="n">
         <v>3.597721446077188e-07</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>88.13382768216373</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 30.691x + -15299.467</t>
-        </is>
+      <c r="W9" t="n">
+        <v>30.69144075935094</v>
       </c>
       <c r="X9" t="n">
         <v>-15299.46735871453</v>
@@ -2868,7 +2790,7 @@
         <v>445.008667827318</v>
       </c>
       <c r="Z9" t="n">
-        <v>110.981</v>
+        <v>486373584.8139477</v>
       </c>
       <c r="AA9" t="n">
         <v>3.441654179782531e-07</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>88.14466889571358</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 30.871x + -15215.188</t>
-        </is>
+      <c r="W10" t="n">
+        <v>30.87090587850576</v>
       </c>
       <c r="X10" t="n">
         <v>-15215.18828857467</v>
@@ -2920,7 +2840,7 @@
         <v>440.893649765704</v>
       </c>
       <c r="Z10" t="n">
-        <v>108.634</v>
+        <v>271883201.9115602</v>
       </c>
       <c r="AA10" t="n">
         <v>3.414356616121575e-07</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>88.21390437859245</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 32.068x + -15663.865</t>
-        </is>
+      <c r="W11" t="n">
+        <v>32.06839441071253</v>
       </c>
       <c r="X11" t="n">
         <v>-15663.8652472838</v>
@@ -2972,7 +2890,7 @@
         <v>436.9422448663099</v>
       </c>
       <c r="Z11" t="n">
-        <v>108.1780000000001</v>
+        <v>179493570.8718365</v>
       </c>
       <c r="AA11" t="n">
         <v>3.395003737481824e-07</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>88.09327901199157</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 30.038x + -14468.741</t>
-        </is>
+      <c r="W12" t="n">
+        <v>30.03828422501105</v>
       </c>
       <c r="X12" t="n">
         <v>-14468.74078383779</v>
@@ -3024,7 +2940,7 @@
         <v>433.2828176238438</v>
       </c>
       <c r="Z12" t="n">
-        <v>105.3049999999999</v>
+        <v>473482797.4171944</v>
       </c>
       <c r="AA12" t="n">
         <v>3.368441139985179e-07</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>88.27045075152152</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 33.118x + -15875.791</t>
-        </is>
+      <c r="W13" t="n">
+        <v>33.11751636561024</v>
       </c>
       <c r="X13" t="n">
         <v>-15875.79091736646</v>
@@ -3076,7 +2990,7 @@
         <v>429.7443921062749</v>
       </c>
       <c r="Z13" t="n">
-        <v>100.226</v>
+        <v>117771042.3196444</v>
       </c>
       <c r="AA13" t="n">
         <v>3.343280724412004e-07</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>88.38258771142314</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 35.415x + -16876.557</t>
-        </is>
+      <c r="W14" t="n">
+        <v>35.41494009102442</v>
       </c>
       <c r="X14" t="n">
         <v>-16876.55652121696</v>
@@ -3128,7 +3040,7 @@
         <v>426.4700305922341</v>
       </c>
       <c r="Z14" t="n">
-        <v>96.52499999999998</v>
+        <v>349439032.2707579</v>
       </c>
       <c r="AA14" t="n">
         <v>3.321317152969503e-07</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>88.27201891195358</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 33.148x + -15598.740</t>
-        </is>
+      <c r="W15" t="n">
+        <v>33.14758910579193</v>
       </c>
       <c r="X15" t="n">
         <v>-15598.73986141956</v>
@@ -3180,7 +3090,7 @@
         <v>423.1897734463594</v>
       </c>
       <c r="Z15" t="n">
-        <v>100.628</v>
+        <v>231090589.7369125</v>
       </c>
       <c r="AA15" t="n">
         <v>3.312041895641052e-07</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>88.20429940099785</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 31.897x + -14845.894</t>
-        </is>
+      <c r="W16" t="n">
+        <v>31.89675311092161</v>
       </c>
       <c r="X16" t="n">
         <v>-14845.89365442346</v>
@@ -3232,7 +3140,7 @@
         <v>420.1364422536576</v>
       </c>
       <c r="Z16" t="n">
-        <v>95.27599999999995</v>
+        <v>229488003.6014582</v>
       </c>
       <c r="AA16" t="n">
         <v>3.283815292238171e-07</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>88.21897423688192</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 32.160x + -14845.285</t>
-        </is>
+      <c r="W17" t="n">
+        <v>32.15973921060205</v>
       </c>
       <c r="X17" t="n">
         <v>-14845.28514461852</v>
@@ -3284,7 +3190,7 @@
         <v>417.1300157044847</v>
       </c>
       <c r="Z17" t="n">
-        <v>97.83600000000001</v>
+        <v>227902862.8026039</v>
       </c>
       <c r="AA17" t="n">
         <v>3.278471387005311e-07</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>88.33506109208007</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 34.403x + -15811.261</t>
-        </is>
+      <c r="W18" t="n">
+        <v>34.40345550514105</v>
       </c>
       <c r="X18" t="n">
         <v>-15811.26067139286</v>
@@ -3336,7 +3240,7 @@
         <v>414.3051543601015</v>
       </c>
       <c r="Z18" t="n">
-        <v>95.12</v>
+        <v>460058898.2584543</v>
       </c>
       <c r="AA18" t="n">
         <v>3.261811176964296e-07</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>88.40596399788193</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 35.935x + -16420.465</t>
-        </is>
+      <c r="W19" t="n">
+        <v>35.93456861809906</v>
       </c>
       <c r="X19" t="n">
         <v>-16420.46539105344</v>
@@ -3388,7 +3290,7 @@
         <v>411.5490035160651</v>
       </c>
       <c r="Z19" t="n">
-        <v>94.02200000000005</v>
+        <v>168752308.0618253</v>
       </c>
       <c r="AA19" t="n">
         <v>3.251941750184349e-07</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>88.3843942276353</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 35.455x + -16062.846</t>
-        </is>
+      <c r="W20" t="n">
+        <v>35.45456092351829</v>
       </c>
       <c r="X20" t="n">
         <v>-16062.84613889791</v>
@@ -3440,7 +3340,7 @@
         <v>408.8704165918489</v>
       </c>
       <c r="Z20" t="n">
-        <v>90.82900000000006</v>
+        <v>168095581.7973329</v>
       </c>
       <c r="AA20" t="n">
         <v>3.229772076629964e-07</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>88.40770087856779</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 35.974x + -16189.763</t>
-        </is>
+      <c r="W21" t="n">
+        <v>35.97378628632862</v>
       </c>
       <c r="X21" t="n">
         <v>-16189.76253744107</v>
@@ -3492,7 +3390,7 @@
         <v>406.284325692896</v>
       </c>
       <c r="Z21" t="n">
-        <v>95.35300000000001</v>
+        <v>332543948.5380579</v>
       </c>
       <c r="AA21" t="n">
         <v>3.231087856751578e-07</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>88.40101844248152</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 35.823x + -16001.834</t>
-        </is>
+      <c r="W22" t="n">
+        <v>35.82336766127325</v>
       </c>
       <c r="X22" t="n">
         <v>-16001.83436353783</v>
@@ -3544,7 +3440,7 @@
         <v>403.7662899693652</v>
       </c>
       <c r="Z22" t="n">
-        <v>90.24400000000003</v>
+        <v>165378171.6926379</v>
       </c>
       <c r="AA22" t="n">
         <v>3.210059814721662e-07</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>85.01732849397618</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.470x + -6207.443</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.47000536722762</v>
       </c>
       <c r="X2" t="n">
         <v>-6207.442793447139</v>
@@ -3742,7 +3636,7 @@
         <v>451.6044662754214</v>
       </c>
       <c r="Z2" t="n">
-        <v>442.259</v>
+        <v>123710028.0486032</v>
       </c>
       <c r="AA2" t="n">
         <v>5.987296709227189e-07</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>86.13004301724143</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.783x + -7085.928</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.78275420665694</v>
       </c>
       <c r="X3" t="n">
         <v>-7085.928005201331</v>
@@ -3794,7 +3686,7 @@
         <v>405.7275238830791</v>
       </c>
       <c r="Z3" t="n">
-        <v>335.343</v>
+        <v>3497.19477476956</v>
       </c>
       <c r="AA3" t="n">
         <v>1.930271585502584e-06</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>86.73368248333327</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 17.522x + -8148.785</t>
-        </is>
+      <c r="W4" t="n">
+        <v>17.52239242859145</v>
       </c>
       <c r="X4" t="n">
         <v>-8148.78475507964</v>
@@ -3846,7 +3736,7 @@
         <v>417.0788436500541</v>
       </c>
       <c r="Z4" t="n">
-        <v>279.395</v>
+        <v>171108914.0719451</v>
       </c>
       <c r="AA4" t="n">
         <v>4.406417280158856e-07</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>87.14803493896184</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 20.073x + -9233.579</t>
-        </is>
+      <c r="W5" t="n">
+        <v>20.0733355752719</v>
       </c>
       <c r="X5" t="n">
         <v>-9233.578607174244</v>
@@ -3898,7 +3786,7 @@
         <v>411.95015765415</v>
       </c>
       <c r="Z5" t="n">
-        <v>248.253</v>
+        <v>122678950.6087333</v>
       </c>
       <c r="AA5" t="n">
         <v>4.159569684637911e-07</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>87.35074216504593</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 21.612x + -9791.984</t>
-        </is>
+      <c r="W6" t="n">
+        <v>21.6116908548818</v>
       </c>
       <c r="X6" t="n">
         <v>-9791.983836112289</v>
@@ -3950,7 +3836,7 @@
         <v>407.2572311950503</v>
       </c>
       <c r="Z6" t="n">
-        <v>226.671</v>
+        <v>166679622.0401532</v>
       </c>
       <c r="AA6" t="n">
         <v>3.980804043968316e-07</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>87.4801081196277</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 22.723x + -10126.916</t>
-        </is>
+      <c r="W7" t="n">
+        <v>22.72273395339994</v>
       </c>
       <c r="X7" t="n">
         <v>-10126.91612636652</v>
@@ -4002,7 +3886,7 @@
         <v>402.3693947042688</v>
       </c>
       <c r="Z7" t="n">
-        <v>207.532</v>
+        <v>219554492.4735357</v>
       </c>
       <c r="AA7" t="n">
         <v>3.84345606726226e-07</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>87.65942084978334</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 24.466x + -10775.877</t>
-        </is>
+      <c r="W8" t="n">
+        <v>24.46569877432603</v>
       </c>
       <c r="X8" t="n">
         <v>-10775.87667963186</v>
@@ -4054,7 +3936,7 @@
         <v>397.3423208388615</v>
       </c>
       <c r="Z8" t="n">
-        <v>193.646</v>
+        <v>216845551.8079745</v>
       </c>
       <c r="AA8" t="n">
         <v>3.735928600554866e-07</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>87.80683387269596</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 26.112x + -11360.284</t>
-        </is>
+      <c r="W9" t="n">
+        <v>26.11192683974458</v>
       </c>
       <c r="X9" t="n">
         <v>-11360.28440174351</v>
@@ -4106,7 +3986,7 @@
         <v>392.540273618457</v>
       </c>
       <c r="Z9" t="n">
-        <v>181.3840000000001</v>
+        <v>222635345.1394069</v>
       </c>
       <c r="AA9" t="n">
         <v>3.652005862649169e-07</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>87.84182568801585</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 26.536x + -11370.083</t>
-        </is>
+      <c r="W10" t="n">
+        <v>26.5357061921519</v>
       </c>
       <c r="X10" t="n">
         <v>-11370.08337581963</v>
@@ -4158,7 +4036,7 @@
         <v>388.0951011812932</v>
       </c>
       <c r="Z10" t="n">
-        <v>173.999</v>
+        <v>423062157.5231858</v>
       </c>
       <c r="AA10" t="n">
         <v>3.585997180361561e-07</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>87.82035798253104</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 26.274x + -11075.066</t>
-        </is>
+      <c r="W11" t="n">
+        <v>26.27410240961785</v>
       </c>
       <c r="X11" t="n">
         <v>-11075.06631422567</v>
@@ -4210,7 +4086,7 @@
         <v>383.9272286990046</v>
       </c>
       <c r="Z11" t="n">
-        <v>168.372</v>
+        <v>254617483.0617626</v>
       </c>
       <c r="AA11" t="n">
         <v>3.533173101994421e-07</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>86.57765001895916</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 16.722x + -9558.348</t>
-        </is>
+      <c r="W2" t="n">
+        <v>16.72173307057</v>
       </c>
       <c r="X2" t="n">
         <v>-9558.347632635645</v>
@@ -4408,7 +4282,7 @@
         <v>487.9594042690175</v>
       </c>
       <c r="Z2" t="n">
-        <v>298.873</v>
+        <v>20870563.31481155</v>
       </c>
       <c r="AA2" t="n">
         <v>5.064964654546895e-07</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>87.27250598703715</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 20.991x + -11400.507</t>
-        </is>
+      <c r="W3" t="n">
+        <v>20.99087772608685</v>
       </c>
       <c r="X3" t="n">
         <v>-11400.5074043747</v>
@@ -4460,7 +4332,7 @@
         <v>475.5846047802367</v>
       </c>
       <c r="Z3" t="n">
-        <v>226.521</v>
+        <v>62337363.4492505</v>
       </c>
       <c r="AA3" t="n">
         <v>4.386627859863791e-07</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>87.55303441183727</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 23.401x + -12495.551</t>
-        </is>
+      <c r="W4" t="n">
+        <v>23.40079520230523</v>
       </c>
       <c r="X4" t="n">
         <v>-12495.55134428585</v>
@@ -4512,7 +4382,7 @@
         <v>470.224807312236</v>
       </c>
       <c r="Z4" t="n">
-        <v>194.9169999999999</v>
+        <v>40256233.97970039</v>
       </c>
       <c r="AA4" t="n">
         <v>4.126434324001954e-07</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>87.743258424204</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 25.376x + -13397.310</t>
-        </is>
+      <c r="W5" t="n">
+        <v>25.37558924461288</v>
       </c>
       <c r="X5" t="n">
         <v>-13397.3099027157</v>
@@ -4564,7 +4432,7 @@
         <v>465.4798622222645</v>
       </c>
       <c r="Z5" t="n">
-        <v>175.016</v>
+        <v>510318735.3978912</v>
       </c>
       <c r="AA5" t="n">
         <v>3.972672512095646e-07</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>87.89947405281634</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 27.265x + -14245.031</t>
-        </is>
+      <c r="W6" t="n">
+        <v>27.26465154911606</v>
       </c>
       <c r="X6" t="n">
         <v>-14245.03114372677</v>
@@ -4616,7 +4482,7 @@
         <v>460.7156419459649</v>
       </c>
       <c r="Z6" t="n">
-        <v>161.784</v>
+        <v>632546268.4056382</v>
       </c>
       <c r="AA6" t="n">
         <v>3.863215574310486e-07</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>87.98571453966041</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 28.433x + -14663.556</t>
-        </is>
+      <c r="W7" t="n">
+        <v>28.43299721607567</v>
       </c>
       <c r="X7" t="n">
         <v>-14663.55578002072</v>
@@ -4668,7 +4532,7 @@
         <v>455.9903720540548</v>
       </c>
       <c r="Z7" t="n">
-        <v>147.486</v>
+        <v>623760284.3014617</v>
       </c>
       <c r="AA7" t="n">
         <v>3.770012462716079e-07</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>87.94885360512119</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 27.922x + -14189.716</t>
-        </is>
+      <c r="W8" t="n">
+        <v>27.92160572166736</v>
       </c>
       <c r="X8" t="n">
         <v>-14189.71567726549</v>
@@ -4720,7 +4582,7 @@
         <v>447.6027129400221</v>
       </c>
       <c r="Z8" t="n">
-        <v>142.458</v>
+        <v>3715.982269439966</v>
       </c>
       <c r="AA8" t="n">
         <v>1.771898486089274e-06</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>87.99169408013763</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 28.518x + -14333.151</t>
-        </is>
+      <c r="W9" t="n">
+        <v>28.51772345981155</v>
       </c>
       <c r="X9" t="n">
         <v>-14333.15111980325</v>
@@ -4772,7 +4632,7 @@
         <v>430.1826088687079</v>
       </c>
       <c r="Z9" t="n">
-        <v>138.157</v>
+        <v>6012.003209406022</v>
       </c>
       <c r="AA9" t="n">
         <v>4.648794861625218e-07</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>88.08755977573321</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 29.948x + -14928.621</t>
-        </is>
+      <c r="W10" t="n">
+        <v>29.94838696364187</v>
       </c>
       <c r="X10" t="n">
         <v>-14928.62125492235</v>
@@ -4824,7 +4682,7 @@
         <v>443.8291156226697</v>
       </c>
       <c r="Z10" t="n">
-        <v>130.276</v>
+        <v>485415571.4548267</v>
       </c>
       <c r="AA10" t="n">
         <v>3.611478261242188e-07</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>88.03234012241425</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 29.107x + -14343.351</t>
-        </is>
+      <c r="W11" t="n">
+        <v>29.10729330903288</v>
       </c>
       <c r="X11" t="n">
         <v>-14343.35053086576</v>
@@ -4876,7 +4732,7 @@
         <v>440.5091394705662</v>
       </c>
       <c r="Z11" t="n">
-        <v>130.32</v>
+        <v>722536310.2237729</v>
       </c>
       <c r="AA11" t="n">
         <v>3.579905095827634e-07</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>88.15665508396445</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 31.072x + -15231.523</t>
-        </is>
+      <c r="W12" t="n">
+        <v>31.07178116833471</v>
       </c>
       <c r="X12" t="n">
         <v>-15231.52346824154</v>
@@ -4928,7 +4782,7 @@
         <v>437.4265430628149</v>
       </c>
       <c r="Z12" t="n">
-        <v>124.157</v>
+        <v>183619405.8780275</v>
       </c>
       <c r="AA12" t="n">
         <v>3.547027152124949e-07</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>88.08499578560517</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 29.908x + -14498.787</t>
-        </is>
+      <c r="W13" t="n">
+        <v>29.90825939147066</v>
       </c>
       <c r="X13" t="n">
         <v>-14498.78684531403</v>
@@ -4980,7 +4832,7 @@
         <v>434.5431997849405</v>
       </c>
       <c r="Z13" t="n">
-        <v>120.739</v>
+        <v>475148769.1456621</v>
       </c>
       <c r="AA13" t="n">
         <v>3.513936096180505e-07</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>88.09518927042227</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 30.068x + -14460.954</t>
-        </is>
+      <c r="W14" t="n">
+        <v>30.06843065911325</v>
       </c>
       <c r="X14" t="n">
         <v>-14460.95431466357</v>
@@ -5032,7 +4882,7 @@
         <v>431.6683188885536</v>
       </c>
       <c r="Z14" t="n">
-        <v>120.115</v>
+        <v>178171907.8930506</v>
       </c>
       <c r="AA14" t="n">
         <v>3.491869959400736e-07</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>88.12709752425977</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 30.581x + -14604.738</t>
-        </is>
+      <c r="W15" t="n">
+        <v>30.58107480726776</v>
       </c>
       <c r="X15" t="n">
         <v>-14604.73772751724</v>
@@ -5084,7 +4932,7 @@
         <v>428.9262120647479</v>
       </c>
       <c r="Z15" t="n">
-        <v>115.753</v>
+        <v>132531860.5347188</v>
       </c>
       <c r="AA15" t="n">
         <v>3.470279622545723e-07</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>88.15007254934933</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 30.961x + -14682.520</t>
-        </is>
+      <c r="W16" t="n">
+        <v>30.96114302908175</v>
       </c>
       <c r="X16" t="n">
         <v>-14682.52046921089</v>
@@ -5136,7 +4982,7 @@
         <v>426.2185258010602</v>
       </c>
       <c r="Z16" t="n">
-        <v>116.878</v>
+        <v>116603561.0165156</v>
       </c>
       <c r="AA16" t="n">
         <v>3.455093855836768e-07</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>88.13983374339404</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 30.791x + -14485.508</t>
-        </is>
+      <c r="W17" t="n">
+        <v>30.79060657063703</v>
       </c>
       <c r="X17" t="n">
         <v>-14485.50824843448</v>
@@ -5188,7 +5032,7 @@
         <v>423.5447604490373</v>
       </c>
       <c r="Z17" t="n">
-        <v>114.853</v>
+        <v>231617670.8661659</v>
       </c>
       <c r="AA17" t="n">
         <v>3.437330883833342e-07</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>88.33375385228582</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 34.376x + -16154.391</t>
-        </is>
+      <c r="W18" t="n">
+        <v>34.37644934918732</v>
       </c>
       <c r="X18" t="n">
         <v>-16154.3909398742</v>
@@ -5240,7 +5082,7 @@
         <v>420.8521465643094</v>
       </c>
       <c r="Z18" t="n">
-        <v>108.551</v>
+        <v>345035231.1221668</v>
       </c>
       <c r="AA18" t="n">
         <v>3.414782119410137e-07</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>88.18140532774646</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 31.495x + -14610.468</t>
-        </is>
+      <c r="W19" t="n">
+        <v>31.49494391529041</v>
       </c>
       <c r="X19" t="n">
         <v>-14610.46845341834</v>
@@ -5292,7 +5132,7 @@
         <v>418.1504168581953</v>
       </c>
       <c r="Z19" t="n">
-        <v>110.7</v>
+        <v>342507630.4153895</v>
       </c>
       <c r="AA19" t="n">
         <v>3.400493193536306e-07</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>88.2608556166102</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 32.935x + -15201.226</t>
-        </is>
+      <c r="W20" t="n">
+        <v>32.9346904344378</v>
       </c>
       <c r="X20" t="n">
         <v>-15201.22609870797</v>
@@ -5344,7 +5182,7 @@
         <v>415.4622142704876</v>
       </c>
       <c r="Z20" t="n">
-        <v>108.405</v>
+        <v>113521306.5080879</v>
       </c>
       <c r="AA20" t="n">
         <v>3.380965401563013e-07</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>88.26645523106805</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 33.041x + -15131.637</t>
-        </is>
+      <c r="W21" t="n">
+        <v>33.04113978405893</v>
       </c>
       <c r="X21" t="n">
         <v>-15131.63707616863</v>
@@ -5396,7 +5232,7 @@
         <v>412.7535966023984</v>
       </c>
       <c r="Z21" t="n">
-        <v>106.7310000000001</v>
+        <v>115862872.8638789</v>
       </c>
       <c r="AA21" t="n">
         <v>3.367067698790006e-07</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>88.26996277800785</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 33.108x + -15046.685</t>
-        </is>
+      <c r="W22" t="n">
+        <v>33.10816957625536</v>
       </c>
       <c r="X22" t="n">
         <v>-15046.68486187088</v>
@@ -5448,7 +5282,7 @@
         <v>409.9987329059463</v>
       </c>
       <c r="Z22" t="n">
-        <v>106.095</v>
+        <v>447755241.8436182</v>
       </c>
       <c r="AA22" t="n">
         <v>3.35471195665405e-07</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>84.69042849471109</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.760x + -5675.637</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.76012889062441</v>
       </c>
       <c r="X2" t="n">
         <v>-5675.637107472598</v>
@@ -5646,7 +5478,7 @@
         <v>445.3914207522574</v>
       </c>
       <c r="Z2" t="n">
-        <v>462.703</v>
+        <v>33151691.97325099</v>
       </c>
       <c r="AA2" t="n">
         <v>6.166507926225259e-07</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>86.11028026646228</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.707x + -6970.265</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.70741700445989</v>
       </c>
       <c r="X3" t="n">
         <v>-6970.264701729548</v>
@@ -5698,7 +5528,7 @@
         <v>420.5912316038754</v>
       </c>
       <c r="Z3" t="n">
-        <v>341.228</v>
+        <v>116789534.394143</v>
       </c>
       <c r="AA3" t="n">
         <v>4.943178437464874e-07</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>86.60238351202463</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.844x + -7716.641</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.84375057426774</v>
       </c>
       <c r="X4" t="n">
         <v>-7716.640528928568</v>
@@ -5750,7 +5578,7 @@
         <v>412.6878403183973</v>
       </c>
       <c r="Z4" t="n">
-        <v>292.5430000000001</v>
+        <v>451117728.3695154</v>
       </c>
       <c r="AA4" t="n">
         <v>4.495844151210855e-07</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>87.02982823978692</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 19.273x + -8713.051</t>
-        </is>
+      <c r="W5" t="n">
+        <v>19.2731098015596</v>
       </c>
       <c r="X5" t="n">
         <v>-8713.051459121381</v>
@@ -5802,7 +5628,7 @@
         <v>407.5198338579776</v>
       </c>
       <c r="Z5" t="n">
-        <v>256.046</v>
+        <v>111323395.5913109</v>
       </c>
       <c r="AA5" t="n">
         <v>4.214655057801039e-07</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>87.23515113651769</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 20.707x + -9209.406</t>
-        </is>
+      <c r="W6" t="n">
+        <v>20.70684590026306</v>
       </c>
       <c r="X6" t="n">
         <v>-9209.406278370005</v>
@@ -5854,7 +5678,7 @@
         <v>402.4984344616082</v>
       </c>
       <c r="Z6" t="n">
-        <v>234.376</v>
+        <v>439760819.851115</v>
       </c>
       <c r="AA6" t="n">
         <v>4.03122837915406e-07</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>87.53531326335293</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 23.232x + -10243.338</t>
-        </is>
+      <c r="W7" t="n">
+        <v>23.23233749803563</v>
       </c>
       <c r="X7" t="n">
         <v>-10243.33841910732</v>
@@ -5906,7 +5728,7 @@
         <v>397.6657207369928</v>
       </c>
       <c r="Z7" t="n">
-        <v>210.663</v>
+        <v>162911489.1865705</v>
       </c>
       <c r="AA7" t="n">
         <v>3.882071865903075e-07</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>87.6169836842146</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 24.030x + -10413.319</t>
-        </is>
+      <c r="W8" t="n">
+        <v>24.02951989766204</v>
       </c>
       <c r="X8" t="n">
         <v>-10413.31872808785</v>
@@ -5958,7 +5778,7 @@
         <v>393.0027983229647</v>
       </c>
       <c r="Z8" t="n">
-        <v>198.189</v>
+        <v>428485616.9651723</v>
       </c>
       <c r="AA8" t="n">
         <v>3.776945056760763e-07</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>87.60470699987309</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 23.906x + -10173.759</t>
-        </is>
+      <c r="W9" t="n">
+        <v>23.9062179925182</v>
       </c>
       <c r="X9" t="n">
         <v>-10173.75882095493</v>
@@ -6010,7 +5828,7 @@
         <v>388.6197640005519</v>
       </c>
       <c r="Z9" t="n">
-        <v>191.136</v>
+        <v>423675658.5636956</v>
       </c>
       <c r="AA9" t="n">
         <v>3.697160895668675e-07</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>87.79350935367347</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 25.954x + -10962.091</t>
-        </is>
+      <c r="W10" t="n">
+        <v>25.9540879700834</v>
       </c>
       <c r="X10" t="n">
         <v>-10962.09122833541</v>
@@ -6062,7 +5878,7 @@
         <v>384.5405361846218</v>
       </c>
       <c r="Z10" t="n">
-        <v>179.392</v>
+        <v>419182986.3963848</v>
       </c>
       <c r="AA10" t="n">
         <v>3.625566196419015e-07</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>87.87956933956821</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 27.008x + -11287.125</t>
-        </is>
+      <c r="W11" t="n">
+        <v>27.00848474292571</v>
       </c>
       <c r="X11" t="n">
         <v>-11287.12531539341</v>
@@ -6114,7 +5928,7 @@
         <v>380.6599388984416</v>
       </c>
       <c r="Z11" t="n">
-        <v>172.243</v>
+        <v>414789006.4149199</v>
       </c>
       <c r="AA11" t="n">
         <v>3.57347364853231e-07</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>85.60444786453098</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 13.009x + -7313.384</t>
-        </is>
+      <c r="W2" t="n">
+        <v>13.00936248900688</v>
       </c>
       <c r="X2" t="n">
         <v>-7313.383695658047</v>
@@ -6312,7 +6124,7 @@
         <v>479.8108571237261</v>
       </c>
       <c r="Z2" t="n">
-        <v>374.2909999999999</v>
+        <v>263079561.5056703</v>
       </c>
       <c r="AA2" t="n">
         <v>5.893989755513716e-07</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>86.8759884752196</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 18.322x + -9757.483</t>
-        </is>
+      <c r="W3" t="n">
+        <v>18.32227238467267</v>
       </c>
       <c r="X3" t="n">
         <v>-9757.482711696241</v>
@@ -6364,7 +6174,7 @@
         <v>466.0123437508557</v>
       </c>
       <c r="Z3" t="n">
-        <v>261.54</v>
+        <v>192729227.9384485</v>
       </c>
       <c r="AA3" t="n">
         <v>4.691099528880948e-07</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>87.38538859207533</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 21.898x + -11495.013</t>
-        </is>
+      <c r="W4" t="n">
+        <v>21.89847503128922</v>
       </c>
       <c r="X4" t="n">
         <v>-11495.01299186346</v>
@@ -6416,7 +6224,7 @@
         <v>460.2784191496814</v>
       </c>
       <c r="Z4" t="n">
-        <v>218.7670000000001</v>
+        <v>44358802.97051834</v>
       </c>
       <c r="AA4" t="n">
         <v>4.316267546161293e-07</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>87.49001009449013</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 22.812x + -11767.167</t>
-        </is>
+      <c r="W5" t="n">
+        <v>22.81249119607194</v>
       </c>
       <c r="X5" t="n">
         <v>-11767.16723840775</v>
@@ -6468,7 +6274,7 @@
         <v>456.0211804082514</v>
       </c>
       <c r="Z5" t="n">
-        <v>197.641</v>
+        <v>250219409.6483359</v>
       </c>
       <c r="AA5" t="n">
         <v>4.115220061307796e-07</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>87.58149835851941</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 23.677x + -12059.020</t>
-        </is>
+      <c r="W6" t="n">
+        <v>23.67653819694747</v>
       </c>
       <c r="X6" t="n">
         <v>-12059.02033481012</v>
@@ -6520,7 +6324,7 @@
         <v>451.9243178839052</v>
       </c>
       <c r="Z6" t="n">
-        <v>182.576</v>
+        <v>186168449.9489576</v>
       </c>
       <c r="AA6" t="n">
         <v>3.980248030971606e-07</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>87.75576086883666</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 25.517x + -12896.819</t>
-        </is>
+      <c r="W7" t="n">
+        <v>25.5171001678788</v>
       </c>
       <c r="X7" t="n">
         <v>-12896.8185038987</v>
@@ -6572,7 +6374,7 @@
         <v>447.9321091230277</v>
       </c>
       <c r="Z7" t="n">
-        <v>170.0189999999999</v>
+        <v>429146801.0924662</v>
       </c>
       <c r="AA7" t="n">
         <v>3.885643224081772e-07</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>87.73426318697842</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 25.275x + -12594.822</t>
-        </is>
+      <c r="W8" t="n">
+        <v>25.27474074184505</v>
       </c>
       <c r="X8" t="n">
         <v>-12594.82157947218</v>
@@ -6624,7 +6424,7 @@
         <v>426.8191531617577</v>
       </c>
       <c r="Z8" t="n">
-        <v>161.75</v>
+        <v>3653.478883969704</v>
       </c>
       <c r="AA8" t="n">
         <v>1.592105281647223e-06</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>87.84293315155519</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 26.549x + -13132.416</t>
-        </is>
+      <c r="W9" t="n">
+        <v>26.54934282808241</v>
       </c>
       <c r="X9" t="n">
         <v>-13132.41584036204</v>
@@ -6676,7 +6474,7 @@
         <v>425.4320827613182</v>
       </c>
       <c r="Z9" t="n">
-        <v>154.88</v>
+        <v>7300.385852477982</v>
       </c>
       <c r="AA9" t="n">
         <v>3.677177381748076e-07</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>87.845923889647</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 26.586x + -13021.202</t>
-        </is>
+      <c r="W10" t="n">
+        <v>26.58623899717546</v>
       </c>
       <c r="X10" t="n">
         <v>-13021.20211902497</v>
@@ -6728,7 +6524,7 @@
         <v>437.235899553066</v>
       </c>
       <c r="Z10" t="n">
-        <v>152.982</v>
+        <v>478305514.0727226</v>
       </c>
       <c r="AA10" t="n">
         <v>3.722280096243427e-07</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>87.92420456922811</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 27.590x + -13407.732</t>
-        </is>
+      <c r="W11" t="n">
+        <v>27.58976542245363</v>
       </c>
       <c r="X11" t="n">
         <v>-13407.73164438409</v>
@@ -6780,7 +6574,7 @@
         <v>434.0356234338695</v>
       </c>
       <c r="Z11" t="n">
-        <v>145.422</v>
+        <v>387057710.379193</v>
       </c>
       <c r="AA11" t="n">
         <v>3.673077680427291e-07</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>88.01340184433441</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 28.830x + -13924.839</t>
-        </is>
+      <c r="W12" t="n">
+        <v>28.82959358580806</v>
       </c>
       <c r="X12" t="n">
         <v>-13924.8385968852</v>
@@ -6832,7 +6624,7 @@
         <v>430.8922112294288</v>
       </c>
       <c r="Z12" t="n">
-        <v>141.159</v>
+        <v>236154793.0845484</v>
       </c>
       <c r="AA12" t="n">
         <v>3.646095659671054e-07</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>88.00884948439409</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 28.764x + -13762.517</t>
-        </is>
+      <c r="W13" t="n">
+        <v>28.76362767728206</v>
       </c>
       <c r="X13" t="n">
         <v>-13762.51679414403</v>
@@ -6884,7 +6674,7 @@
         <v>427.6949893090637</v>
       </c>
       <c r="Z13" t="n">
-        <v>139.431</v>
+        <v>352754192.0720581</v>
       </c>
       <c r="AA13" t="n">
         <v>3.618877796593501e-07</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>88.08937905454511</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 29.977x + -14255.216</t>
-        </is>
+      <c r="W14" t="n">
+        <v>29.97692477266407</v>
       </c>
       <c r="X14" t="n">
         <v>-14255.21617138809</v>
@@ -6936,7 +6724,7 @@
         <v>424.533169671479</v>
       </c>
       <c r="Z14" t="n">
-        <v>136.846</v>
+        <v>290117497.2340956</v>
       </c>
       <c r="AA14" t="n">
         <v>3.593102726972235e-07</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>88.1091289430927</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 30.290x + -14262.611</t>
-        </is>
+      <c r="W15" t="n">
+        <v>30.29026067009061</v>
       </c>
       <c r="X15" t="n">
         <v>-14262.61079368881</v>
@@ -6988,7 +6774,7 @@
         <v>420.9721895559343</v>
       </c>
       <c r="Z15" t="n">
-        <v>131.502</v>
+        <v>345012531.730469</v>
       </c>
       <c r="AA15" t="n">
         <v>3.561030430931987e-07</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>88.14577355566854</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 30.889x + -14416.039</t>
-        </is>
+      <c r="W16" t="n">
+        <v>30.88931015537552</v>
       </c>
       <c r="X16" t="n">
         <v>-14416.03887302562</v>
@@ -7040,7 +6824,7 @@
         <v>417.5882387120285</v>
       </c>
       <c r="Z16" t="n">
-        <v>130.049</v>
+        <v>118373990.5439707</v>
       </c>
       <c r="AA16" t="n">
         <v>3.539173651349342e-07</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>88.10473863551152</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 30.220x + -13952.927</t>
-        </is>
+      <c r="W17" t="n">
+        <v>30.22004329418343</v>
       </c>
       <c r="X17" t="n">
         <v>-13952.92705948735</v>
@@ -7092,7 +6874,7 @@
         <v>414.5571719338185</v>
       </c>
       <c r="Z17" t="n">
-        <v>127.9780000000001</v>
+        <v>453135520.0351815</v>
       </c>
       <c r="AA17" t="n">
         <v>3.514813113505032e-07</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>88.08303827008297</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 29.878x + -13660.225</t>
-        </is>
+      <c r="W18" t="n">
+        <v>29.87769564707455</v>
       </c>
       <c r="X18" t="n">
         <v>-13660.22456612663</v>
@@ -7144,7 +6924,7 @@
         <v>411.5259476161896</v>
       </c>
       <c r="Z18" t="n">
-        <v>126.532</v>
+        <v>168743346.0635722</v>
       </c>
       <c r="AA18" t="n">
         <v>3.493103631632429e-07</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>88.21451588060602</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 32.079x + -14606.625</t>
-        </is>
+      <c r="W19" t="n">
+        <v>32.07938448077157</v>
       </c>
       <c r="X19" t="n">
         <v>-14606.62462238206</v>
@@ -7196,7 +6974,7 @@
         <v>408.5105256298336</v>
       </c>
       <c r="Z19" t="n">
-        <v>122.514</v>
+        <v>334777631.6739607</v>
       </c>
       <c r="AA19" t="n">
         <v>3.476259962158232e-07</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>88.09506374441214</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 30.066x + -13508.934</t>
-        </is>
+      <c r="W20" t="n">
+        <v>30.06644783542827</v>
       </c>
       <c r="X20" t="n">
         <v>-13508.93400573216</v>
@@ -7248,7 +7024,7 @@
         <v>405.4855688446784</v>
       </c>
       <c r="Z20" t="n">
-        <v>122.7719999999999</v>
+        <v>221692713.7646232</v>
       </c>
       <c r="AA20" t="n">
         <v>3.45904275648366e-07</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>88.15756103992196</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 31.087x + -13874.030</t>
-        </is>
+      <c r="W21" t="n">
+        <v>31.08707019281993</v>
       </c>
       <c r="X21" t="n">
         <v>-13874.02972793589</v>
@@ -7300,7 +7074,7 @@
         <v>402.5010659986688</v>
       </c>
       <c r="Z21" t="n">
-        <v>121.852</v>
+        <v>331821560.834577</v>
       </c>
       <c r="AA21" t="n">
         <v>3.442378256849942e-07</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>88.14656903179977</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 30.903x + -13663.820</t>
-        </is>
+      <c r="W22" t="n">
+        <v>30.90257683236327</v>
       </c>
       <c r="X22" t="n">
         <v>-13663.81967361734</v>
@@ -7352,7 +7124,7 @@
         <v>399.5148303094026</v>
       </c>
       <c r="Z22" t="n">
-        <v>116.947</v>
+        <v>436922180.5574364</v>
       </c>
       <c r="AA22" t="n">
         <v>3.422039977735035e-07</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>84.08308845444594</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.649x + -5134.761</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.648945249555137</v>
       </c>
       <c r="X2" t="n">
         <v>-5134.761399588653</v>
@@ -7550,7 +7320,7 @@
         <v>447.2608542610588</v>
       </c>
       <c r="Z2" t="n">
-        <v>502.2120000000001</v>
+        <v>360712415.1757494</v>
       </c>
       <c r="AA2" t="n">
         <v>6.787841699857573e-07</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>85.96212121317983</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.166x + -6697.682</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.16607470847489</v>
       </c>
       <c r="X3" t="n">
         <v>-6697.681925217379</v>
@@ -7602,7 +7370,7 @@
         <v>400.1974333256916</v>
       </c>
       <c r="Z3" t="n">
-        <v>347.258</v>
+        <v>3457.066656048483</v>
       </c>
       <c r="AA3" t="n">
         <v>1.49665477798724e-06</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>86.74631749462222</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 17.591x + -8090.893</t>
-        </is>
+      <c r="W4" t="n">
+        <v>17.59058442389384</v>
       </c>
       <c r="X4" t="n">
         <v>-8090.892774284126</v>
@@ -7654,7 +7420,7 @@
         <v>412.4612535545218</v>
       </c>
       <c r="Z4" t="n">
-        <v>281.103</v>
+        <v>175598348.1537231</v>
       </c>
       <c r="AA4" t="n">
         <v>4.487309756219125e-07</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>87.07557598061601</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 19.575x + -8829.035</t>
-        </is>
+      <c r="W5" t="n">
+        <v>19.57514214166586</v>
       </c>
       <c r="X5" t="n">
         <v>-8829.035159041612</v>
@@ -7706,7 +7470,7 @@
         <v>407.3470578961657</v>
       </c>
       <c r="Z5" t="n">
-        <v>246.028</v>
+        <v>111318800.5883842</v>
       </c>
       <c r="AA5" t="n">
         <v>4.182032860857763e-07</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>87.38996086624113</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 21.937x + -9770.280</t>
-        </is>
+      <c r="W6" t="n">
+        <v>21.93689010589567</v>
       </c>
       <c r="X6" t="n">
         <v>-9770.280128072411</v>
@@ -7758,7 +7520,7 @@
         <v>402.3688986980127</v>
       </c>
       <c r="Z6" t="n">
-        <v>215.908</v>
+        <v>329501850.603974</v>
       </c>
       <c r="AA6" t="n">
         <v>3.9729317622861e-07</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>87.56119821939389</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 23.479x + -10307.517</t>
-        </is>
+      <c r="W7" t="n">
+        <v>23.4792237554284</v>
       </c>
       <c r="X7" t="n">
         <v>-10307.51734490165</v>
@@ -7810,7 +7570,7 @@
         <v>397.415658651056</v>
       </c>
       <c r="Z7" t="n">
-        <v>198.8419999999999</v>
+        <v>218840704.1563608</v>
       </c>
       <c r="AA7" t="n">
         <v>3.836214915534863e-07</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>87.67500104510698</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 24.630x + -10652.905</t>
-        </is>
+      <c r="W8" t="n">
+        <v>24.62982932380391</v>
       </c>
       <c r="X8" t="n">
         <v>-10652.90482962498</v>
@@ -7862,7 +7620,7 @@
         <v>392.7104613324146</v>
       </c>
       <c r="Z8" t="n">
-        <v>185.855</v>
+        <v>107181455.5656053</v>
       </c>
       <c r="AA8" t="n">
         <v>3.731376418170977e-07</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>87.80491201635911</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 26.089x + -11149.284</t>
-        </is>
+      <c r="W9" t="n">
+        <v>26.0890428156437</v>
       </c>
       <c r="X9" t="n">
         <v>-11149.28377621135</v>
@@ -7914,7 +7670,7 @@
         <v>388.4101290095276</v>
       </c>
       <c r="Z9" t="n">
-        <v>173.868</v>
+        <v>158973472.4001223</v>
       </c>
       <c r="AA9" t="n">
         <v>3.65152339941978e-07</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>87.85530636547489</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 26.703x + -11274.804</t>
-        </is>
+      <c r="W10" t="n">
+        <v>26.70265629484792</v>
       </c>
       <c r="X10" t="n">
         <v>-11274.80434193135</v>
@@ -7966,7 +7720,7 @@
         <v>384.4091790697254</v>
       </c>
       <c r="Z10" t="n">
-        <v>170.251</v>
+        <v>628613980.98006</v>
       </c>
       <c r="AA10" t="n">
         <v>3.598723325225615e-07</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>87.97109499077021</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 28.228x + -11794.199</t>
-        </is>
+      <c r="W11" t="n">
+        <v>28.22794989551157</v>
       </c>
       <c r="X11" t="n">
         <v>-11794.19885323564</v>
@@ -8018,7 +7770,7 @@
         <v>380.3166287316536</v>
       </c>
       <c r="Z11" t="n">
-        <v>158.229</v>
+        <v>207343975.1091103</v>
       </c>
       <c r="AA11" t="n">
         <v>3.539633503169021e-07</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>86.6967744138974</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 17.326x + -9647.423</t>
-        </is>
+      <c r="W2" t="n">
+        <v>17.3261815109941</v>
       </c>
       <c r="X2" t="n">
         <v>-9647.422723588208</v>
@@ -8216,7 +7966,7 @@
         <v>476.5721033888777</v>
       </c>
       <c r="Z2" t="n">
-        <v>269.9549999999999</v>
+        <v>32616356.86377891</v>
       </c>
       <c r="AA2" t="n">
         <v>4.840721463029202e-07</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>87.42191370389277</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 22.209x + -11709.437</t>
-        </is>
+      <c r="W3" t="n">
+        <v>22.2091504234214</v>
       </c>
       <c r="X3" t="n">
         <v>-11709.43650743262</v>
@@ -8268,7 +8016,7 @@
         <v>462.5869755842085</v>
       </c>
       <c r="Z3" t="n">
-        <v>202.054</v>
+        <v>26239456.73372998</v>
       </c>
       <c r="AA3" t="n">
         <v>4.217473612483152e-07</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>87.60855465954982</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 23.945x + -12376.459</t>
-        </is>
+      <c r="W4" t="n">
+        <v>23.94472615510886</v>
       </c>
       <c r="X4" t="n">
         <v>-12376.45852350311</v>
@@ -8320,7 +8066,7 @@
         <v>456.9434479126721</v>
       </c>
       <c r="Z4" t="n">
-        <v>178.7979999999999</v>
+        <v>188258830.4061645</v>
       </c>
       <c r="AA4" t="n">
         <v>4.017273873978845e-07</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>87.73643486088176</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 25.299x + -12926.947</t>
-        </is>
+      <c r="W5" t="n">
+        <v>25.29901472024976</v>
       </c>
       <c r="X5" t="n">
         <v>-12926.94694102056</v>
@@ -8372,7 +8116,7 @@
         <v>452.2621544931089</v>
       </c>
       <c r="Z5" t="n">
-        <v>166.908</v>
+        <v>124547803.1700962</v>
       </c>
       <c r="AA5" t="n">
         <v>3.908531247009425e-07</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>87.90473245000915</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 27.333x + -13841.239</t>
-        </is>
+      <c r="W6" t="n">
+        <v>27.33313767076428</v>
       </c>
       <c r="X6" t="n">
         <v>-13841.23949737114</v>
@@ -8424,7 +8166,7 @@
         <v>426.5961128333809</v>
       </c>
       <c r="Z6" t="n">
-        <v>156.376</v>
+        <v>3684.652092205249</v>
       </c>
       <c r="AA6" t="n">
         <v>1.335455556498187e-06</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>87.83408140324777</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 26.441x + -13149.566</t>
-        </is>
+      <c r="W7" t="n">
+        <v>26.44073728515496</v>
       </c>
       <c r="X7" t="n">
         <v>-13149.56585572598</v>
@@ -8476,7 +8216,7 @@
         <v>422.6749463804728</v>
       </c>
       <c r="Z7" t="n">
-        <v>149.321</v>
+        <v>3642.189151459356</v>
       </c>
       <c r="AA7" t="n">
         <v>1.864454460717978e-06</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>87.97585160834232</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 28.294x + -13956.665</t>
-        </is>
+      <c r="W8" t="n">
+        <v>28.29433916885763</v>
       </c>
       <c r="X8" t="n">
         <v>-13956.66516406941</v>
@@ -8528,7 +8266,7 @@
         <v>438.112749893103</v>
       </c>
       <c r="Z8" t="n">
-        <v>146.064</v>
+        <v>179792642.771854</v>
       </c>
       <c r="AA8" t="n">
         <v>3.721556559962741e-07</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>87.96396673717531</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 28.129x + -13686.828</t>
-        </is>
+      <c r="W9" t="n">
+        <v>28.12903963097849</v>
       </c>
       <c r="X9" t="n">
         <v>-13686.82832258121</v>
@@ -8580,7 +8316,7 @@
         <v>434.2094682901393</v>
       </c>
       <c r="Z9" t="n">
-        <v>140.314</v>
+        <v>475241279.9076642</v>
       </c>
       <c r="AA9" t="n">
         <v>3.673586660074046e-07</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>88.00037049837363</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 28.642x + -13804.790</t>
-        </is>
+      <c r="W10" t="n">
+        <v>28.64156342049365</v>
       </c>
       <c r="X10" t="n">
         <v>-13804.79004941218</v>
@@ -8632,7 +8366,7 @@
         <v>430.6504935008618</v>
       </c>
       <c r="Z10" t="n">
-        <v>137.398</v>
+        <v>117791125.0711426</v>
       </c>
       <c r="AA10" t="n">
         <v>3.643612089453659e-07</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>88.01240660309304</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 28.815x + -13755.979</t>
-        </is>
+      <c r="W11" t="n">
+        <v>28.81514625713078</v>
       </c>
       <c r="X11" t="n">
         <v>-13755.97854030204</v>
@@ -8684,7 +8416,7 @@
         <v>427.2898349614363</v>
       </c>
       <c r="Z11" t="n">
-        <v>136.163</v>
+        <v>175414089.0588971</v>
       </c>
       <c r="AA11" t="n">
         <v>3.617815616241259e-07</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>88.04229837464453</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 29.255x + -13843.933</t>
-        </is>
+      <c r="W12" t="n">
+        <v>29.25546972939734</v>
       </c>
       <c r="X12" t="n">
         <v>-13843.93283311992</v>
@@ -8736,7 +8466,7 @@
         <v>424.2052365218456</v>
       </c>
       <c r="Z12" t="n">
-        <v>128.955</v>
+        <v>174333779.1887518</v>
       </c>
       <c r="AA12" t="n">
         <v>3.58150876896356e-07</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>88.13913333434772</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 30.779x + -14493.377</t>
-        </is>
+      <c r="W13" t="n">
+        <v>30.77900918731363</v>
       </c>
       <c r="X13" t="n">
         <v>-14493.37747334547</v>
@@ -8788,7 +8516,7 @@
         <v>421.1424903195542</v>
       </c>
       <c r="Z13" t="n">
-        <v>129.674</v>
+        <v>172944089.5054938</v>
       </c>
       <c r="AA13" t="n">
         <v>3.569231144901565e-07</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>88.14187484781961</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 30.824x + -14382.641</t>
-        </is>
+      <c r="W14" t="n">
+        <v>30.82445305451083</v>
       </c>
       <c r="X14" t="n">
         <v>-14382.64092711181</v>
@@ -8840,7 +8566,7 @@
         <v>418.1995125728263</v>
       </c>
       <c r="Z14" t="n">
-        <v>126.3419999999999</v>
+        <v>114458354.7393551</v>
       </c>
       <c r="AA14" t="n">
         <v>3.542281346934422e-07</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>88.04751394560952</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 29.334x + -13528.192</t>
-        </is>
+      <c r="W15" t="n">
+        <v>29.33367906832878</v>
       </c>
       <c r="X15" t="n">
         <v>-13528.19225082068</v>
@@ -8892,7 +8616,7 @@
         <v>415.2940601923247</v>
       </c>
       <c r="Z15" t="n">
-        <v>126.863</v>
+        <v>113880481.0897932</v>
       </c>
       <c r="AA15" t="n">
         <v>3.527569266650081e-07</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>88.28065316677706</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 33.314x + -15366.032</t>
-        </is>
+      <c r="W16" t="n">
+        <v>33.31415114718229</v>
       </c>
       <c r="X16" t="n">
         <v>-15366.03192059773</v>
@@ -8944,7 +8666,7 @@
         <v>412.4653666218679</v>
       </c>
       <c r="Z16" t="n">
-        <v>121.2</v>
+        <v>170016055.2832703</v>
       </c>
       <c r="AA16" t="n">
         <v>3.508072820551902e-07</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>88.22652662564285</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 32.297x + -14747.401</t>
-        </is>
+      <c r="W17" t="n">
+        <v>32.29678048461521</v>
       </c>
       <c r="X17" t="n">
         <v>-14747.40100343068</v>
@@ -8996,7 +8716,7 @@
         <v>409.6914866273248</v>
       </c>
       <c r="Z17" t="n">
-        <v>118.9429999999999</v>
+        <v>223941085.9405902</v>
       </c>
       <c r="AA17" t="n">
         <v>3.489212786123147e-07</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>88.23707281632849</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 32.490x + -14718.158</t>
-        </is>
+      <c r="W18" t="n">
+        <v>32.49010951883623</v>
       </c>
       <c r="X18" t="n">
         <v>-14718.15831226745</v>
@@ -9048,7 +8766,7 @@
         <v>406.9016518111838</v>
       </c>
       <c r="Z18" t="n">
-        <v>115.905</v>
+        <v>445599249.1035966</v>
       </c>
       <c r="AA18" t="n">
         <v>3.472231600958838e-07</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>88.27434074236413</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 33.192x + -14929.605</t>
-        </is>
+      <c r="W19" t="n">
+        <v>33.19221537660921</v>
       </c>
       <c r="X19" t="n">
         <v>-14929.60479392341</v>
@@ -9100,7 +8816,7 @@
         <v>404.0651842629732</v>
       </c>
       <c r="Z19" t="n">
-        <v>112.6900000000001</v>
+        <v>661839284.8314869</v>
       </c>
       <c r="AA19" t="n">
         <v>3.453166066346132e-07</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>88.29242628008754</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 33.544x + -14975.823</t>
-        </is>
+      <c r="W20" t="n">
+        <v>33.54397784248615</v>
       </c>
       <c r="X20" t="n">
         <v>-14975.82267919341</v>
@@ -9152,7 +8866,7 @@
         <v>401.2731753297563</v>
       </c>
       <c r="Z20" t="n">
-        <v>114.655</v>
+        <v>109954655.0377423</v>
       </c>
       <c r="AA20" t="n">
         <v>3.439855398064399e-07</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>88.22900338411642</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 32.342x + -14283.628</t>
-        </is>
+      <c r="W21" t="n">
+        <v>32.34197673372037</v>
       </c>
       <c r="X21" t="n">
         <v>-14283.62846338707</v>
@@ -9204,7 +8916,7 @@
         <v>398.4425835561854</v>
       </c>
       <c r="Z21" t="n">
-        <v>113.539</v>
+        <v>109012463.3348543</v>
       </c>
       <c r="AA21" t="n">
         <v>3.426062937967993e-07</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>88.26054355963502</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 32.929x + -14444.860</t>
-        </is>
+      <c r="W22" t="n">
+        <v>32.92877834850029</v>
       </c>
       <c r="X22" t="n">
         <v>-14444.86047287876</v>
@@ -9256,7 +8966,7 @@
         <v>395.5741458391194</v>
       </c>
       <c r="Z22" t="n">
-        <v>115.079</v>
+        <v>216197133.3926557</v>
       </c>
       <c r="AA22" t="n">
         <v>3.420991244525461e-07</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>85.34755638349567</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.288x + -5813.035</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.28812254041511</v>
       </c>
       <c r="X2" t="n">
         <v>-5813.034705871516</v>
@@ -9454,7 +9162,7 @@
         <v>413.3995528377526</v>
       </c>
       <c r="Z2" t="n">
-        <v>402.064</v>
+        <v>225684152.6048389</v>
       </c>
       <c r="AA2" t="n">
         <v>5.241173545103358e-07</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>87.03956231471548</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 19.337x + -8647.872</t>
-        </is>
+      <c r="W3" t="n">
+        <v>19.33659428884635</v>
       </c>
       <c r="X3" t="n">
         <v>-8647.872406315368</v>
@@ -9506,7 +9212,7 @@
         <v>397.8529853889657</v>
       </c>
       <c r="Z3" t="n">
-        <v>260.005</v>
+        <v>112885517.5216535</v>
       </c>
       <c r="AA3" t="n">
         <v>4.160469132995124e-07</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>87.45931583278877</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 22.537x + -9808.825</t>
-        </is>
+      <c r="W4" t="n">
+        <v>22.53653611026656</v>
       </c>
       <c r="X4" t="n">
         <v>-9808.825267630049</v>
@@ -9558,7 +9262,7 @@
         <v>391.3386659647608</v>
       </c>
       <c r="Z4" t="n">
-        <v>211.74</v>
+        <v>108290984.225836</v>
       </c>
       <c r="AA4" t="n">
         <v>3.837920383609075e-07</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>87.67444672224893</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 24.624x + -10553.448</t>
-        </is>
+      <c r="W5" t="n">
+        <v>24.62395206506019</v>
       </c>
       <c r="X5" t="n">
         <v>-10553.44763209426</v>
@@ -9610,7 +9312,7 @@
         <v>386.3690046309804</v>
       </c>
       <c r="Z5" t="n">
-        <v>190.444</v>
+        <v>157949997.6588617</v>
       </c>
       <c r="AA5" t="n">
         <v>3.688402224524403e-07</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>87.77620126723748</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 25.752x + -10847.430</t>
-        </is>
+      <c r="W6" t="n">
+        <v>25.75188361344238</v>
       </c>
       <c r="X6" t="n">
         <v>-10847.43029960969</v>
@@ -9662,7 +9362,7 @@
         <v>381.3808015938022</v>
       </c>
       <c r="Z6" t="n">
-        <v>172.473</v>
+        <v>518900397.9970644</v>
       </c>
       <c r="AA6" t="n">
         <v>3.580863380424837e-07</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>87.82889808127788</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 26.378x + -10925.455</t>
-        </is>
+      <c r="W7" t="n">
+        <v>26.37755201383237</v>
       </c>
       <c r="X7" t="n">
         <v>-10925.45541698337</v>
@@ -9714,7 +9412,7 @@
         <v>376.3327505729329</v>
       </c>
       <c r="Z7" t="n">
-        <v>165.8600000000001</v>
+        <v>205146431.2838763</v>
       </c>
       <c r="AA7" t="n">
         <v>3.515607192078831e-07</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>88.00106853694072</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 28.652x + -11732.964</t>
-        </is>
+      <c r="W8" t="n">
+        <v>28.65157334687012</v>
       </c>
       <c r="X8" t="n">
         <v>-11732.96445154462</v>
@@ -9766,7 +9462,7 @@
         <v>371.3978966041586</v>
       </c>
       <c r="Z8" t="n">
-        <v>151.4440000000001</v>
+        <v>101185515.6043342</v>
       </c>
       <c r="AA8" t="n">
         <v>3.451356492579932e-07</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>87.99679155326329</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 28.590x + -11509.331</t>
-        </is>
+      <c r="W9" t="n">
+        <v>28.59035060636527</v>
       </c>
       <c r="X9" t="n">
         <v>-11509.33134619516</v>
@@ -9818,7 +9512,7 @@
         <v>366.7219718483795</v>
       </c>
       <c r="Z9" t="n">
-        <v>147.945</v>
+        <v>398717668.0373393</v>
       </c>
       <c r="AA9" t="n">
         <v>3.414772267556041e-07</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>87.70829093751166</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 24.988x + -9790.788</t>
-        </is>
+      <c r="W10" t="n">
+        <v>24.98799812700887</v>
       </c>
       <c r="X10" t="n">
         <v>-9790.787598396972</v>
@@ -9870,7 +9562,7 @@
         <v>362.3537054803389</v>
       </c>
       <c r="Z10" t="n">
-        <v>148.651</v>
+        <v>197025356.9286698</v>
       </c>
       <c r="AA10" t="n">
         <v>3.378478295031829e-07</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>88.08199058568086</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 29.861x + -11700.289</t>
-        </is>
+      <c r="W11" t="n">
+        <v>29.86136320688936</v>
       </c>
       <c r="X11" t="n">
         <v>-11700.28864134019</v>
@@ -9922,7 +9612,7 @@
         <v>358.2962929249304</v>
       </c>
       <c r="Z11" t="n">
-        <v>139.839</v>
+        <v>97464261.31029435</v>
       </c>
       <c r="AA11" t="n">
         <v>3.351133738062318e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-206.9680000000001</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-180.5890000000001</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-165.962</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-157.841</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-147.615</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-141.347</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-138.753</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-135.886</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-125.828</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-127.311</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-442.259</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-335.343</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-279.395</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-248.253</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-226.671</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-207.532</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-193.646</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-181.3840000000001</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-173.999</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-168.372</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-462.703</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-341.228</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-292.5430000000001</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-256.046</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-234.376</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-210.663</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-198.189</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-191.136</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-179.392</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-172.243</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-502.2120000000001</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-347.258</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-281.103</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-246.028</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-215.908</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-198.8419999999999</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-185.855</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-173.868</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-170.251</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-158.229</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-402.064</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-260.005</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-211.74</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-190.444</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-172.473</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-165.8600000000001</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-151.4440000000001</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-147.945</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-148.651</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-139.839</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-206.9680000000001</v>
+        <v>149.777</v>
       </c>
       <c r="D2" t="n">
         <v>2.55167e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-180.5890000000001</v>
+        <v>143.134</v>
       </c>
       <c r="D3" t="n">
         <v>2.53626e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-165.962</v>
+        <v>138.388</v>
       </c>
       <c r="D4" t="n">
         <v>2.52538e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-157.841</v>
+        <v>133.665</v>
       </c>
       <c r="D5" t="n">
         <v>2.52018e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-147.615</v>
+        <v>128.212</v>
       </c>
       <c r="D6" t="n">
         <v>2.51621e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-141.347</v>
+        <v>121.961</v>
       </c>
       <c r="D7" t="n">
         <v>2.51403e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-138.753</v>
+        <v>120.783</v>
       </c>
       <c r="D8" t="n">
         <v>2.50996e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-135.886</v>
+        <v>115.751</v>
       </c>
       <c r="D9" t="n">
         <v>2.50784e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-125.828</v>
+        <v>114.622</v>
       </c>
       <c r="D10" t="n">
         <v>2.50683e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-127.311</v>
+        <v>110.539</v>
       </c>
       <c r="D11" t="n">
         <v>2.50499e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-206.165</v>
+        <v>143.8410000000001</v>
       </c>
       <c r="D2" t="n">
         <v>2.63713e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-164.432</v>
+        <v>124.12</v>
       </c>
       <c r="D3" t="n">
         <v>2.61359e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-152.111</v>
+        <v>116.746</v>
       </c>
       <c r="D4" t="n">
         <v>2.60231e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-144.179</v>
+        <v>114.907</v>
       </c>
       <c r="D5" t="n">
         <v>2.59858e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-139.024</v>
+        <v>111.023</v>
       </c>
       <c r="D6" t="n">
         <v>2.5934e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-138.9730000000001</v>
+        <v>108.629</v>
       </c>
       <c r="D7" t="n">
         <v>2.59097e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-132.0040000000001</v>
+        <v>106.546</v>
       </c>
       <c r="D8" t="n">
         <v>2.58949e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-128.7810000000001</v>
+        <v>102.538</v>
       </c>
       <c r="D9" t="n">
         <v>2.58908e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-124.763</v>
+        <v>101.966</v>
       </c>
       <c r="D10" t="n">
         <v>2.58923e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-127.144</v>
+        <v>99.24299999999999</v>
       </c>
       <c r="D11" t="n">
         <v>2.58747e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-122.708</v>
+        <v>97.50200000000001</v>
       </c>
       <c r="D12" t="n">
         <v>2.58569e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-119.515</v>
+        <v>96.93099999999998</v>
       </c>
       <c r="D13" t="n">
         <v>2.58524e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-118.287</v>
+        <v>95.71999999999997</v>
       </c>
       <c r="D14" t="n">
         <v>2.58622e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-122.745</v>
+        <v>93.02499999999998</v>
       </c>
       <c r="D15" t="n">
         <v>2.58401e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-113.441</v>
+        <v>93.37799999999999</v>
       </c>
       <c r="D16" t="n">
         <v>2.58322e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-115.513</v>
+        <v>91.22000000000003</v>
       </c>
       <c r="D17" t="n">
         <v>2.58377e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-112.773</v>
+        <v>88.93200000000002</v>
       </c>
       <c r="D18" t="n">
         <v>2.58486e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-111.799</v>
+        <v>87.98099999999999</v>
       </c>
       <c r="D19" t="n">
         <v>2.58477e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-113.845</v>
+        <v>85.44800000000004</v>
       </c>
       <c r="D20" t="n">
         <v>2.58436e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-109.122</v>
+        <v>84.29000000000002</v>
       </c>
       <c r="D21" t="n">
         <v>2.58408e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-106.591</v>
+        <v>84.62599999999998</v>
       </c>
       <c r="D22" t="n">
         <v>2.58429e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-159.962</v>
+        <v>127.1440000000001</v>
       </c>
       <c r="D2" t="n">
         <v>2.58421e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-140.202</v>
+        <v>126.216</v>
       </c>
       <c r="D3" t="n">
         <v>2.56412e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-135.4440000000001</v>
+        <v>122.717</v>
       </c>
       <c r="D4" t="n">
         <v>2.55514e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-126.332</v>
+        <v>120.883</v>
       </c>
       <c r="D5" t="n">
         <v>2.54836e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-121.292</v>
+        <v>115.995</v>
       </c>
       <c r="D6" t="n">
         <v>2.544e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-114.8820000000001</v>
+        <v>116.777</v>
       </c>
       <c r="D7" t="n">
         <v>2.54052e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-110.843</v>
+        <v>112.283</v>
       </c>
       <c r="D8" t="n">
         <v>2.54037e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-110.981</v>
+        <v>107.853</v>
       </c>
       <c r="D9" t="n">
         <v>2.53716e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-108.634</v>
+        <v>104.977</v>
       </c>
       <c r="D10" t="n">
         <v>2.53629e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-108.1780000000001</v>
+        <v>103.166</v>
       </c>
       <c r="D11" t="n">
         <v>2.53481e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-105.3049999999999</v>
+        <v>99.22300000000001</v>
       </c>
       <c r="D12" t="n">
         <v>2.53387e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-100.226</v>
+        <v>99.452</v>
       </c>
       <c r="D13" t="n">
         <v>2.53204e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-96.52499999999998</v>
+        <v>98.798</v>
       </c>
       <c r="D14" t="n">
         <v>2.53008e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-100.628</v>
+        <v>95.03299999999996</v>
       </c>
       <c r="D15" t="n">
         <v>2.52919e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-95.27599999999995</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="D16" t="n">
         <v>2.52793e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-97.83600000000001</v>
+        <v>90.416</v>
       </c>
       <c r="D17" t="n">
         <v>2.5275e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-95.12</v>
+        <v>90.17599999999999</v>
       </c>
       <c r="D18" t="n">
         <v>2.52591e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-94.02200000000005</v>
+        <v>89.93199999999996</v>
       </c>
       <c r="D19" t="n">
         <v>2.52559e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-90.82900000000006</v>
+        <v>87.96199999999999</v>
       </c>
       <c r="D20" t="n">
         <v>2.52297e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-95.35300000000001</v>
+        <v>86.75200000000001</v>
       </c>
       <c r="D21" t="n">
         <v>2.52289e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-90.24400000000003</v>
+        <v>85.67599999999999</v>
       </c>
       <c r="D22" t="n">
         <v>2.52152e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-442.259</v>
+        <v>153.955</v>
       </c>
       <c r="D2" t="n">
         <v>2.82179e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-335.343</v>
+        <v>103.72</v>
       </c>
       <c r="D3" t="n">
         <v>2.81987e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-279.395</v>
+        <v>93.56900000000002</v>
       </c>
       <c r="D4" t="n">
         <v>2.77439e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-248.253</v>
+        <v>91.02599999999995</v>
       </c>
       <c r="D5" t="n">
         <v>2.73509e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-226.671</v>
+        <v>87.70499999999998</v>
       </c>
       <c r="D6" t="n">
         <v>2.70279e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-207.532</v>
+        <v>83.68599999999998</v>
       </c>
       <c r="D7" t="n">
         <v>2.68014e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-193.646</v>
+        <v>81.24900000000002</v>
       </c>
       <c r="D8" t="n">
         <v>2.65986e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-181.3840000000001</v>
+        <v>79.82499999999999</v>
       </c>
       <c r="D9" t="n">
         <v>2.64515e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-173.999</v>
+        <v>76.28800000000001</v>
       </c>
       <c r="D10" t="n">
         <v>2.63282e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-168.372</v>
+        <v>72.517</v>
       </c>
       <c r="D11" t="n">
         <v>2.62378e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-298.873</v>
+        <v>156.033</v>
       </c>
       <c r="D2" t="n">
         <v>2.74005e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-226.521</v>
+        <v>132.4780000000001</v>
       </c>
       <c r="D3" t="n">
         <v>2.69425e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-194.9169999999999</v>
+        <v>126.674</v>
       </c>
       <c r="D4" t="n">
         <v>2.66225e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-175.016</v>
+        <v>122.492</v>
       </c>
       <c r="D5" t="n">
         <v>2.64118e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-161.784</v>
+        <v>120.781</v>
       </c>
       <c r="D6" t="n">
         <v>2.6246e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-147.486</v>
+        <v>117.48</v>
       </c>
       <c r="D7" t="n">
         <v>2.61492e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-142.458</v>
+        <v>112.723</v>
       </c>
       <c r="D8" t="n">
         <v>2.60746e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-138.157</v>
+        <v>110.07</v>
       </c>
       <c r="D9" t="n">
         <v>2.59913e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-130.276</v>
+        <v>108.158</v>
       </c>
       <c r="D10" t="n">
         <v>2.59559e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-130.32</v>
+        <v>104.332</v>
       </c>
       <c r="D11" t="n">
         <v>2.59046e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-124.157</v>
+        <v>104.526</v>
       </c>
       <c r="D12" t="n">
         <v>2.58745e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-120.739</v>
+        <v>101.212</v>
       </c>
       <c r="D13" t="n">
         <v>2.58398e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-120.115</v>
+        <v>99.29599999999999</v>
       </c>
       <c r="D14" t="n">
         <v>2.58086e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-115.753</v>
+        <v>98.173</v>
       </c>
       <c r="D15" t="n">
         <v>2.58077e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-116.878</v>
+        <v>96.27600000000001</v>
       </c>
       <c r="D16" t="n">
         <v>2.57822e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-114.853</v>
+        <v>94.75800000000004</v>
       </c>
       <c r="D17" t="n">
         <v>2.57668e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-108.551</v>
+        <v>96.72000000000003</v>
       </c>
       <c r="D18" t="n">
         <v>2.57459e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-110.7</v>
+        <v>92.48900000000003</v>
       </c>
       <c r="D19" t="n">
         <v>2.57329e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-108.405</v>
+        <v>92.012</v>
       </c>
       <c r="D20" t="n">
         <v>2.57036e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-106.7310000000001</v>
+        <v>89.89599999999996</v>
       </c>
       <c r="D21" t="n">
         <v>2.57127e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-106.095</v>
+        <v>89.17500000000001</v>
       </c>
       <c r="D22" t="n">
         <v>2.57021e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-462.703</v>
+        <v>142.614</v>
       </c>
       <c r="D2" t="n">
         <v>2.87562e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-341.228</v>
+        <v>100.243</v>
       </c>
       <c r="D3" t="n">
         <v>2.86036e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-292.5430000000001</v>
+        <v>88.24000000000001</v>
       </c>
       <c r="D4" t="n">
         <v>2.81188e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-256.046</v>
+        <v>85.76999999999998</v>
       </c>
       <c r="D5" t="n">
         <v>2.76874e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-234.376</v>
+        <v>81.64400000000001</v>
       </c>
       <c r="D6" t="n">
         <v>2.73642e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-210.663</v>
+        <v>80.916</v>
       </c>
       <c r="D7" t="n">
         <v>2.712e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-198.189</v>
+        <v>76.28500000000003</v>
       </c>
       <c r="D8" t="n">
         <v>2.69367e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-191.136</v>
+        <v>72.05900000000003</v>
       </c>
       <c r="D9" t="n">
         <v>2.67726e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-179.392</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>2.66442e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-172.243</v>
+        <v>70.26800000000003</v>
       </c>
       <c r="D11" t="n">
         <v>2.65438e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-374.2909999999999</v>
+        <v>155.4870000000001</v>
       </c>
       <c r="D2" t="n">
         <v>2.84397e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-261.54</v>
+        <v>130.846</v>
       </c>
       <c r="D3" t="n">
         <v>2.75614e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-218.7670000000001</v>
+        <v>125.73</v>
       </c>
       <c r="D4" t="n">
         <v>2.70856e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-197.641</v>
+        <v>119.708</v>
       </c>
       <c r="D5" t="n">
         <v>2.67791e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-182.576</v>
+        <v>115.502</v>
       </c>
       <c r="D6" t="n">
         <v>2.65727e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-170.0189999999999</v>
+        <v>113.607</v>
       </c>
       <c r="D7" t="n">
         <v>2.6437e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-161.75</v>
+        <v>109.807</v>
       </c>
       <c r="D8" t="n">
         <v>2.63508e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-154.88</v>
+        <v>108.085</v>
       </c>
       <c r="D9" t="n">
         <v>2.62824e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-152.982</v>
+        <v>105.667</v>
       </c>
       <c r="D10" t="n">
         <v>2.62254e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-145.422</v>
+        <v>103.9400000000001</v>
       </c>
       <c r="D11" t="n">
         <v>2.61677e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-141.159</v>
+        <v>103.677</v>
       </c>
       <c r="D12" t="n">
         <v>2.61527e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-139.431</v>
+        <v>100.934</v>
       </c>
       <c r="D13" t="n">
         <v>2.61226e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-136.846</v>
+        <v>100.679</v>
       </c>
       <c r="D14" t="n">
         <v>2.60879e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-131.502</v>
+        <v>98.35199999999998</v>
       </c>
       <c r="D15" t="n">
         <v>2.60783e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-130.049</v>
+        <v>96.30099999999999</v>
       </c>
       <c r="D16" t="n">
         <v>2.60631e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-127.9780000000001</v>
+        <v>94.339</v>
       </c>
       <c r="D17" t="n">
         <v>2.60393e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-126.532</v>
+        <v>91.86200000000002</v>
       </c>
       <c r="D18" t="n">
         <v>2.60207e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-122.514</v>
+        <v>91.96699999999998</v>
       </c>
       <c r="D19" t="n">
         <v>2.6022e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-122.7719999999999</v>
+        <v>88.40000000000003</v>
       </c>
       <c r="D20" t="n">
         <v>2.60188e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-121.852</v>
+        <v>87.82999999999998</v>
       </c>
       <c r="D21" t="n">
         <v>2.59964e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-116.947</v>
+        <v>86.04000000000002</v>
       </c>
       <c r="D22" t="n">
         <v>2.60098e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-502.2120000000001</v>
+        <v>147.4259999999999</v>
       </c>
       <c r="D2" t="n">
         <v>2.92483e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-347.258</v>
+        <v>100.088</v>
       </c>
       <c r="D3" t="n">
         <v>2.88417e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-281.103</v>
+        <v>92.08699999999999</v>
       </c>
       <c r="D4" t="n">
         <v>2.8179e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-246.028</v>
+        <v>86.22900000000004</v>
       </c>
       <c r="D5" t="n">
         <v>2.76729e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-215.908</v>
+        <v>83.91899999999998</v>
       </c>
       <c r="D6" t="n">
         <v>2.73217e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-198.8419999999999</v>
+        <v>80.80300000000005</v>
       </c>
       <c r="D7" t="n">
         <v>2.70654e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-185.855</v>
+        <v>77.88200000000001</v>
       </c>
       <c r="D8" t="n">
         <v>2.68647e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-173.868</v>
+        <v>75.80199999999996</v>
       </c>
       <c r="D9" t="n">
         <v>2.6731e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-170.251</v>
+        <v>73.09899999999999</v>
       </c>
       <c r="D10" t="n">
         <v>2.66119e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-158.229</v>
+        <v>72.19800000000004</v>
       </c>
       <c r="D11" t="n">
         <v>2.65386e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-269.9549999999999</v>
+        <v>151.935</v>
       </c>
       <c r="D2" t="n">
         <v>2.72978e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-202.054</v>
+        <v>128.668</v>
       </c>
       <c r="D3" t="n">
         <v>2.6855e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-178.7979999999999</v>
+        <v>120.865</v>
       </c>
       <c r="D4" t="n">
         <v>2.6613e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-166.908</v>
+        <v>118.387</v>
       </c>
       <c r="D5" t="n">
         <v>2.64506e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-156.376</v>
+        <v>117.028</v>
       </c>
       <c r="D6" t="n">
         <v>2.63705e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-149.321</v>
+        <v>111.347</v>
       </c>
       <c r="D7" t="n">
         <v>2.63134e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-146.064</v>
+        <v>109.383</v>
       </c>
       <c r="D8" t="n">
         <v>2.62561e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-140.314</v>
+        <v>105.665</v>
       </c>
       <c r="D9" t="n">
         <v>2.62244e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-137.398</v>
+        <v>103.884</v>
       </c>
       <c r="D10" t="n">
         <v>2.62047e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-136.163</v>
+        <v>100.768</v>
       </c>
       <c r="D11" t="n">
         <v>2.61863e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-128.955</v>
+        <v>99.03199999999998</v>
       </c>
       <c r="D12" t="n">
         <v>2.6172e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-129.674</v>
+        <v>99.37199999999996</v>
       </c>
       <c r="D13" t="n">
         <v>2.61548e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-126.3419999999999</v>
+        <v>96.66500000000002</v>
       </c>
       <c r="D14" t="n">
         <v>2.61366e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-126.863</v>
+        <v>93.41800000000001</v>
       </c>
       <c r="D15" t="n">
         <v>2.61342e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-121.2</v>
+        <v>95.50299999999999</v>
       </c>
       <c r="D16" t="n">
         <v>2.61245e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-118.9429999999999</v>
+        <v>93.28700000000003</v>
       </c>
       <c r="D17" t="n">
         <v>2.61202e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-115.905</v>
+        <v>92.59300000000002</v>
       </c>
       <c r="D18" t="n">
         <v>2.61212e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-112.6900000000001</v>
+        <v>90.75699999999995</v>
       </c>
       <c r="D19" t="n">
         <v>2.61205e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-114.655</v>
+        <v>89.47899999999998</v>
       </c>
       <c r="D20" t="n">
         <v>2.60874e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-113.539</v>
+        <v>86.88099999999997</v>
       </c>
       <c r="D21" t="n">
         <v>2.61001e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-115.079</v>
+        <v>85.89600000000002</v>
       </c>
       <c r="D22" t="n">
         <v>2.60994e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-402.064</v>
+        <v>109.144</v>
       </c>
       <c r="D2" t="n">
         <v>2.834e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-260.005</v>
+        <v>89.58800000000002</v>
       </c>
       <c r="D3" t="n">
         <v>2.73136e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-211.74</v>
+        <v>81.76600000000002</v>
       </c>
       <c r="D4" t="n">
         <v>2.683e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-190.444</v>
+        <v>78.61800000000005</v>
       </c>
       <c r="D5" t="n">
         <v>2.65526e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-172.473</v>
+        <v>74.786</v>
       </c>
       <c r="D6" t="n">
         <v>2.63917e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-165.8600000000001</v>
+        <v>71.185</v>
       </c>
       <c r="D7" t="n">
         <v>2.62756e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-151.4440000000001</v>
+        <v>70.31399999999996</v>
       </c>
       <c r="D8" t="n">
         <v>2.62081e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-147.945</v>
+        <v>67.03799999999995</v>
       </c>
       <c r="D9" t="n">
         <v>2.61662e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-148.651</v>
+        <v>59.34199999999998</v>
       </c>
       <c r="D10" t="n">
         <v>2.61241e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-139.839</v>
+        <v>62.63499999999999</v>
       </c>
       <c r="D11" t="n">
         <v>2.6101e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>149.777</v>
       </c>
+      <c r="C2" t="n">
+        <v>800.2887631759555</v>
+      </c>
       <c r="D2" t="n">
         <v>2.55167e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>143.134</v>
       </c>
+      <c r="C3" t="n">
+        <v>792.7222289381001</v>
+      </c>
       <c r="D3" t="n">
         <v>2.53626e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>138.388</v>
       </c>
+      <c r="C4" t="n">
+        <v>820.5295595666877</v>
+      </c>
       <c r="D4" t="n">
         <v>2.52538e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>133.665</v>
       </c>
+      <c r="C5" t="n">
+        <v>798.2711549337172</v>
+      </c>
       <c r="D5" t="n">
         <v>2.52018e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>128.212</v>
       </c>
+      <c r="C6" t="n">
+        <v>797.0878286091353</v>
+      </c>
       <c r="D6" t="n">
         <v>2.51621e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>121.961</v>
       </c>
+      <c r="C7" t="n">
+        <v>769.9795539502384</v>
+      </c>
       <c r="D7" t="n">
         <v>2.51403e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>120.783</v>
       </c>
+      <c r="C8" t="n">
+        <v>798.5547285131028</v>
+      </c>
       <c r="D8" t="n">
         <v>2.50996e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>115.751</v>
       </c>
+      <c r="C9" t="n">
+        <v>775.9982923281569</v>
+      </c>
       <c r="D9" t="n">
         <v>2.50784e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>114.622</v>
       </c>
+      <c r="C10" t="n">
+        <v>815.9473033949938</v>
+      </c>
       <c r="D10" t="n">
         <v>2.50683e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>110.539</v>
+      </c>
+      <c r="C11" t="n">
+        <v>796.903194149085</v>
       </c>
       <c r="D11" t="n">
         <v>2.50499e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>143.8410000000001</v>
       </c>
+      <c r="C2" t="n">
+        <v>1059.132908162364</v>
+      </c>
       <c r="D2" t="n">
         <v>2.63713e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>124.12</v>
       </c>
+      <c r="C3" t="n">
+        <v>812.3576181256211</v>
+      </c>
       <c r="D3" t="n">
         <v>2.61359e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>116.746</v>
       </c>
+      <c r="C4" t="n">
+        <v>764.8916449328779</v>
+      </c>
       <c r="D4" t="n">
         <v>2.60231e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>114.907</v>
       </c>
+      <c r="C5" t="n">
+        <v>750.53080548607</v>
+      </c>
       <c r="D5" t="n">
         <v>2.59858e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>111.023</v>
       </c>
+      <c r="C6" t="n">
+        <v>749.0703436887376</v>
+      </c>
       <c r="D6" t="n">
         <v>2.5934e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>108.629</v>
       </c>
+      <c r="C7" t="n">
+        <v>757.8151581983441</v>
+      </c>
       <c r="D7" t="n">
         <v>2.59097e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>106.546</v>
       </c>
+      <c r="C8" t="n">
+        <v>774.7211127755741</v>
+      </c>
       <c r="D8" t="n">
         <v>2.58949e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>102.538</v>
       </c>
+      <c r="C9" t="n">
+        <v>731.8293537151964</v>
+      </c>
       <c r="D9" t="n">
         <v>2.58908e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>101.966</v>
       </c>
+      <c r="C10" t="n">
+        <v>770.0429450508918</v>
+      </c>
       <c r="D10" t="n">
         <v>2.58923e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>99.24299999999999</v>
       </c>
+      <c r="C11" t="n">
+        <v>732.5653319221127</v>
+      </c>
       <c r="D11" t="n">
         <v>2.58747e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>97.50200000000001</v>
       </c>
+      <c r="C12" t="n">
+        <v>751.3700864422563</v>
+      </c>
       <c r="D12" t="n">
         <v>2.58569e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>96.93099999999998</v>
       </c>
+      <c r="C13" t="n">
+        <v>778.0355881324057</v>
+      </c>
       <c r="D13" t="n">
         <v>2.58524e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>95.71999999999997</v>
       </c>
+      <c r="C14" t="n">
+        <v>770.0002868696703</v>
+      </c>
       <c r="D14" t="n">
         <v>2.58622e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>93.02499999999998</v>
       </c>
+      <c r="C15" t="n">
+        <v>751.8614978431298</v>
+      </c>
       <c r="D15" t="n">
         <v>2.58401e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>93.37799999999999</v>
       </c>
+      <c r="C16" t="n">
+        <v>798.8076960802003</v>
+      </c>
       <c r="D16" t="n">
         <v>2.58322e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>91.22000000000003</v>
       </c>
+      <c r="C17" t="n">
+        <v>766.4408331436923</v>
+      </c>
       <c r="D17" t="n">
         <v>2.58377e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>88.93200000000002</v>
       </c>
+      <c r="C18" t="n">
+        <v>741.4228566317064</v>
+      </c>
       <c r="D18" t="n">
         <v>2.58486e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>87.98099999999999</v>
       </c>
+      <c r="C19" t="n">
+        <v>772.3901811928334</v>
+      </c>
       <c r="D19" t="n">
         <v>2.58477e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>85.44800000000004</v>
       </c>
+      <c r="C20" t="n">
+        <v>625.505143681647</v>
+      </c>
       <c r="D20" t="n">
         <v>2.58436e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>84.29000000000002</v>
       </c>
+      <c r="C21" t="n">
+        <v>742.1748521613763</v>
+      </c>
       <c r="D21" t="n">
         <v>2.58408e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>84.62599999999998</v>
+      </c>
+      <c r="C22" t="n">
+        <v>804.2855514340722</v>
       </c>
       <c r="D22" t="n">
         <v>2.58429e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>127.1440000000001</v>
       </c>
+      <c r="C2" t="n">
+        <v>769.9790416431434</v>
+      </c>
       <c r="D2" t="n">
         <v>2.58421e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>126.216</v>
       </c>
+      <c r="C3" t="n">
+        <v>795.4993846942464</v>
+      </c>
       <c r="D3" t="n">
         <v>2.56412e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>122.717</v>
       </c>
+      <c r="C4" t="n">
+        <v>791.121108481082</v>
+      </c>
       <c r="D4" t="n">
         <v>2.55514e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>120.883</v>
       </c>
+      <c r="C5" t="n">
+        <v>814.5259067031121</v>
+      </c>
       <c r="D5" t="n">
         <v>2.54836e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>115.995</v>
       </c>
+      <c r="C6" t="n">
+        <v>786.7964868584397</v>
+      </c>
       <c r="D6" t="n">
         <v>2.544e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>116.777</v>
       </c>
+      <c r="C7" t="n">
+        <v>831.7611886766609</v>
+      </c>
       <c r="D7" t="n">
         <v>2.54052e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>112.283</v>
       </c>
+      <c r="C8" t="n">
+        <v>820.9722548703857</v>
+      </c>
       <c r="D8" t="n">
         <v>2.54037e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>107.853</v>
       </c>
+      <c r="C9" t="n">
+        <v>776.3413640131756</v>
+      </c>
       <c r="D9" t="n">
         <v>2.53716e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>104.977</v>
       </c>
+      <c r="C10" t="n">
+        <v>790.604434091499</v>
+      </c>
       <c r="D10" t="n">
         <v>2.53629e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>103.166</v>
       </c>
+      <c r="C11" t="n">
+        <v>809.5966989096476</v>
+      </c>
       <c r="D11" t="n">
         <v>2.53481e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>99.22300000000001</v>
       </c>
+      <c r="C12" t="n">
+        <v>773.5444879549773</v>
+      </c>
       <c r="D12" t="n">
         <v>2.53387e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>99.452</v>
       </c>
+      <c r="C13" t="n">
+        <v>807.0877531293008</v>
+      </c>
       <c r="D13" t="n">
         <v>2.53204e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>98.798</v>
       </c>
+      <c r="C14" t="n">
+        <v>854.6019771770884</v>
+      </c>
       <c r="D14" t="n">
         <v>2.53008e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>95.03299999999996</v>
       </c>
+      <c r="C15" t="n">
+        <v>806.9524713605816</v>
+      </c>
       <c r="D15" t="n">
         <v>2.52919e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>92.06999999999999</v>
       </c>
+      <c r="C16" t="n">
+        <v>774.8898735317663</v>
+      </c>
       <c r="D16" t="n">
         <v>2.52793e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>90.416</v>
       </c>
+      <c r="C17" t="n">
+        <v>753.2736593465946</v>
+      </c>
       <c r="D17" t="n">
         <v>2.5275e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>90.17599999999999</v>
       </c>
+      <c r="C18" t="n">
+        <v>823.7298692865413</v>
+      </c>
       <c r="D18" t="n">
         <v>2.52591e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>89.93199999999996</v>
       </c>
+      <c r="C19" t="n">
+        <v>845.0989610980768</v>
+      </c>
       <c r="D19" t="n">
         <v>2.52559e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>87.96199999999999</v>
       </c>
+      <c r="C20" t="n">
+        <v>809.5146414070073</v>
+      </c>
       <c r="D20" t="n">
         <v>2.52297e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>86.75200000000001</v>
       </c>
+      <c r="C21" t="n">
+        <v>811.8817423752565</v>
+      </c>
       <c r="D21" t="n">
         <v>2.52289e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>85.67599999999999</v>
+      </c>
+      <c r="C22" t="n">
+        <v>806.0935424308382</v>
       </c>
       <c r="D22" t="n">
         <v>2.52152e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>153.955</v>
       </c>
+      <c r="C2" t="n">
+        <v>6189.082884579291</v>
+      </c>
       <c r="D2" t="n">
         <v>2.82179e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>103.72</v>
       </c>
+      <c r="C3" t="n">
+        <v>947.9746486402793</v>
+      </c>
       <c r="D3" t="n">
         <v>2.81987e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>93.56900000000002</v>
       </c>
+      <c r="C4" t="n">
+        <v>810.7598585317664</v>
+      </c>
       <c r="D4" t="n">
         <v>2.77439e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>91.02599999999995</v>
       </c>
+      <c r="C5" t="n">
+        <v>892.1402764082138</v>
+      </c>
       <c r="D5" t="n">
         <v>2.73509e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>87.70499999999998</v>
       </c>
+      <c r="C6" t="n">
+        <v>889.1620024093568</v>
+      </c>
       <c r="D6" t="n">
         <v>2.70279e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>83.68599999999998</v>
       </c>
+      <c r="C7" t="n">
+        <v>845.0128609700602</v>
+      </c>
       <c r="D7" t="n">
         <v>2.68014e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>81.24900000000002</v>
       </c>
+      <c r="C8" t="n">
+        <v>930.5615658803188</v>
+      </c>
       <c r="D8" t="n">
         <v>2.65986e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>79.82499999999999</v>
       </c>
+      <c r="C9" t="n">
+        <v>944.9416680229909</v>
+      </c>
       <c r="D9" t="n">
         <v>2.64515e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>76.28800000000001</v>
       </c>
+      <c r="C10" t="n">
+        <v>926.2812813035268</v>
+      </c>
       <c r="D10" t="n">
         <v>2.63282e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>72.517</v>
+      </c>
+      <c r="C11" t="n">
+        <v>837.5354711499788</v>
       </c>
       <c r="D11" t="n">
         <v>2.62378e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>156.033</v>
       </c>
+      <c r="C2" t="n">
+        <v>1153.220572953452</v>
+      </c>
       <c r="D2" t="n">
         <v>2.74005e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>132.4780000000001</v>
       </c>
+      <c r="C3" t="n">
+        <v>822.4331656731661</v>
+      </c>
       <c r="D3" t="n">
         <v>2.69425e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>126.674</v>
       </c>
+      <c r="C4" t="n">
+        <v>786.7698965945493</v>
+      </c>
       <c r="D4" t="n">
         <v>2.66225e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>122.492</v>
       </c>
+      <c r="C5" t="n">
+        <v>804.9592942507388</v>
+      </c>
       <c r="D5" t="n">
         <v>2.64118e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>120.781</v>
       </c>
+      <c r="C6" t="n">
+        <v>824.3506363670142</v>
+      </c>
       <c r="D6" t="n">
         <v>2.6246e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>117.48</v>
       </c>
+      <c r="C7" t="n">
+        <v>800.2835929732237</v>
+      </c>
       <c r="D7" t="n">
         <v>2.61492e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>112.723</v>
       </c>
+      <c r="C8" t="n">
+        <v>795.2704471792111</v>
+      </c>
       <c r="D8" t="n">
         <v>2.60746e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>110.07</v>
       </c>
+      <c r="C9" t="n">
+        <v>779.3592661637773</v>
+      </c>
       <c r="D9" t="n">
         <v>2.59913e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>108.158</v>
       </c>
+      <c r="C10" t="n">
+        <v>790.9894031575437</v>
+      </c>
       <c r="D10" t="n">
         <v>2.59559e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>104.332</v>
       </c>
+      <c r="C11" t="n">
+        <v>748.8544162162301</v>
+      </c>
       <c r="D11" t="n">
         <v>2.59046e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>104.526</v>
       </c>
+      <c r="C12" t="n">
+        <v>792.9269411598302</v>
+      </c>
       <c r="D12" t="n">
         <v>2.58745e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>101.212</v>
       </c>
+      <c r="C13" t="n">
+        <v>759.7877319627366</v>
+      </c>
       <c r="D13" t="n">
         <v>2.58398e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>99.29599999999999</v>
       </c>
+      <c r="C14" t="n">
+        <v>744.447867885845</v>
+      </c>
       <c r="D14" t="n">
         <v>2.58086e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>98.173</v>
       </c>
+      <c r="C15" t="n">
+        <v>754.2133300141475</v>
+      </c>
       <c r="D15" t="n">
         <v>2.58077e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>96.27600000000001</v>
       </c>
+      <c r="C16" t="n">
+        <v>754.0969417648274</v>
+      </c>
       <c r="D16" t="n">
         <v>2.57822e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>94.75800000000004</v>
       </c>
+      <c r="C17" t="n">
+        <v>752.0200055395501</v>
+      </c>
       <c r="D17" t="n">
         <v>2.57668e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>96.72000000000003</v>
       </c>
+      <c r="C18" t="n">
+        <v>816.7804482163108</v>
+      </c>
       <c r="D18" t="n">
         <v>2.57459e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>92.48900000000003</v>
       </c>
+      <c r="C19" t="n">
+        <v>746.0535899790285</v>
+      </c>
       <c r="D19" t="n">
         <v>2.57329e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>92.012</v>
       </c>
+      <c r="C20" t="n">
+        <v>775.2709639458604</v>
+      </c>
       <c r="D20" t="n">
         <v>2.57036e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>89.89599999999996</v>
       </c>
+      <c r="C21" t="n">
+        <v>769.6214543107071</v>
+      </c>
       <c r="D21" t="n">
         <v>2.57127e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>89.17500000000001</v>
+      </c>
+      <c r="C22" t="n">
+        <v>768.280271696451</v>
       </c>
       <c r="D22" t="n">
         <v>2.57021e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>142.614</v>
       </c>
+      <c r="C2" t="n">
+        <v>7522.919433164251</v>
+      </c>
       <c r="D2" t="n">
         <v>2.87562e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>100.243</v>
       </c>
+      <c r="C3" t="n">
+        <v>1122.975886901015</v>
+      </c>
       <c r="D3" t="n">
         <v>2.86036e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>88.24000000000001</v>
       </c>
+      <c r="C4" t="n">
+        <v>864.6409521131634</v>
+      </c>
       <c r="D4" t="n">
         <v>2.81188e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>85.76999999999998</v>
       </c>
+      <c r="C5" t="n">
+        <v>866.5409159622992</v>
+      </c>
       <c r="D5" t="n">
         <v>2.76874e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>81.64400000000001</v>
       </c>
+      <c r="C6" t="n">
+        <v>856.6403052765819</v>
+      </c>
       <c r="D6" t="n">
         <v>2.73642e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>80.916</v>
       </c>
+      <c r="C7" t="n">
+        <v>986.3067278864398</v>
+      </c>
       <c r="D7" t="n">
         <v>2.712e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>76.28500000000003</v>
       </c>
+      <c r="C8" t="n">
+        <v>907.5028009567798</v>
+      </c>
       <c r="D8" t="n">
         <v>2.69367e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>72.05900000000003</v>
       </c>
+      <c r="C9" t="n">
+        <v>840.9948212866926</v>
+      </c>
       <c r="D9" t="n">
         <v>2.67726e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>71.06999999999999</v>
       </c>
+      <c r="C10" t="n">
+        <v>885.3855058677075</v>
+      </c>
       <c r="D10" t="n">
         <v>2.66442e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>70.26800000000003</v>
+      </c>
+      <c r="C11" t="n">
+        <v>997.8959805738725</v>
       </c>
       <c r="D11" t="n">
         <v>2.65438e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>155.4870000000001</v>
       </c>
+      <c r="C2" t="n">
+        <v>1099.451079010621</v>
+      </c>
       <c r="D2" t="n">
         <v>2.84397e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>130.846</v>
       </c>
+      <c r="C3" t="n">
+        <v>819.6422669150433</v>
+      </c>
       <c r="D3" t="n">
         <v>2.75614e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>125.73</v>
       </c>
+      <c r="C4" t="n">
+        <v>806.2914689555191</v>
+      </c>
       <c r="D4" t="n">
         <v>2.70856e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>119.708</v>
       </c>
+      <c r="C5" t="n">
+        <v>763.4661919803003</v>
+      </c>
       <c r="D5" t="n">
         <v>2.67791e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>115.502</v>
       </c>
+      <c r="C6" t="n">
+        <v>745.2124390752806</v>
+      </c>
       <c r="D6" t="n">
         <v>2.65727e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>113.607</v>
       </c>
+      <c r="C7" t="n">
+        <v>770.4450543658349</v>
+      </c>
       <c r="D7" t="n">
         <v>2.6437e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>109.807</v>
       </c>
+      <c r="C8" t="n">
+        <v>734.6883358508969</v>
+      </c>
       <c r="D8" t="n">
         <v>2.63508e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>108.085</v>
       </c>
+      <c r="C9" t="n">
+        <v>756.1621713841814</v>
+      </c>
       <c r="D9" t="n">
         <v>2.62824e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>105.667</v>
       </c>
+      <c r="C10" t="n">
+        <v>730.9984949561509</v>
+      </c>
       <c r="D10" t="n">
         <v>2.62254e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>103.9400000000001</v>
       </c>
+      <c r="C11" t="n">
+        <v>745.957724417341</v>
+      </c>
       <c r="D11" t="n">
         <v>2.61677e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>103.677</v>
       </c>
+      <c r="C12" t="n">
+        <v>766.1396859840642</v>
+      </c>
       <c r="D12" t="n">
         <v>2.61527e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>100.934</v>
       </c>
+      <c r="C13" t="n">
+        <v>758.7793659643439</v>
+      </c>
       <c r="D13" t="n">
         <v>2.61226e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>100.679</v>
       </c>
+      <c r="C14" t="n">
+        <v>758.4943021006861</v>
+      </c>
       <c r="D14" t="n">
         <v>2.60879e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>98.35199999999998</v>
       </c>
+      <c r="C15" t="n">
+        <v>766.1113510396697</v>
+      </c>
       <c r="D15" t="n">
         <v>2.60783e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>96.30099999999999</v>
       </c>
+      <c r="C16" t="n">
+        <v>768.4236135829952</v>
+      </c>
       <c r="D16" t="n">
         <v>2.60631e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>94.339</v>
       </c>
+      <c r="C17" t="n">
+        <v>758.3943132545231</v>
+      </c>
       <c r="D17" t="n">
         <v>2.60393e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>91.86200000000002</v>
       </c>
+      <c r="C18" t="n">
+        <v>730.0169999953633</v>
+      </c>
       <c r="D18" t="n">
         <v>2.60207e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>91.96699999999998</v>
       </c>
+      <c r="C19" t="n">
+        <v>769.0072880343744</v>
+      </c>
       <c r="D19" t="n">
         <v>2.6022e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>88.40000000000003</v>
       </c>
+      <c r="C20" t="n">
+        <v>714.4206272791724</v>
+      </c>
       <c r="D20" t="n">
         <v>2.60188e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>87.82999999999998</v>
       </c>
+      <c r="C21" t="n">
+        <v>745.020882085448</v>
+      </c>
       <c r="D21" t="n">
         <v>2.59964e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>86.04000000000002</v>
+      </c>
+      <c r="C22" t="n">
+        <v>727.0434734155206</v>
       </c>
       <c r="D22" t="n">
         <v>2.60098e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>147.4259999999999</v>
       </c>
+      <c r="C2" t="n">
+        <v>5342.922156756319</v>
+      </c>
       <c r="D2" t="n">
         <v>2.92483e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>100.088</v>
       </c>
+      <c r="C3" t="n">
+        <v>970.8397076339409</v>
+      </c>
       <c r="D3" t="n">
         <v>2.88417e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>92.08699999999999</v>
       </c>
+      <c r="C4" t="n">
+        <v>856.557096609115</v>
+      </c>
       <c r="D4" t="n">
         <v>2.8179e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>86.22900000000004</v>
       </c>
+      <c r="C5" t="n">
+        <v>791.5740628060598</v>
+      </c>
       <c r="D5" t="n">
         <v>2.76729e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>83.91899999999998</v>
       </c>
+      <c r="C6" t="n">
+        <v>822.127028168791</v>
+      </c>
       <c r="D6" t="n">
         <v>2.73217e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>80.80300000000005</v>
       </c>
+      <c r="C7" t="n">
+        <v>837.0553962204218</v>
+      </c>
       <c r="D7" t="n">
         <v>2.70654e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>77.88200000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>808.2339817889705</v>
+      </c>
       <c r="D8" t="n">
         <v>2.68647e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>75.80199999999996</v>
       </c>
+      <c r="C9" t="n">
+        <v>809.3465693700382</v>
+      </c>
       <c r="D9" t="n">
         <v>2.6731e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>73.09899999999999</v>
       </c>
+      <c r="C10" t="n">
+        <v>835.6500622061048</v>
+      </c>
       <c r="D10" t="n">
         <v>2.66119e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>72.19800000000004</v>
+      </c>
+      <c r="C11" t="n">
+        <v>817.6381060496526</v>
       </c>
       <c r="D11" t="n">
         <v>2.65386e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>151.935</v>
       </c>
+      <c r="C2" t="n">
+        <v>1075.218365368932</v>
+      </c>
       <c r="D2" t="n">
         <v>2.72978e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>128.668</v>
       </c>
+      <c r="C3" t="n">
+        <v>800.3699388318648</v>
+      </c>
       <c r="D3" t="n">
         <v>2.6855e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>120.865</v>
       </c>
+      <c r="C4" t="n">
+        <v>733.1775652583228</v>
+      </c>
       <c r="D4" t="n">
         <v>2.6613e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>118.387</v>
       </c>
+      <c r="C5" t="n">
+        <v>742.6363284171247</v>
+      </c>
       <c r="D5" t="n">
         <v>2.64506e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>117.028</v>
       </c>
+      <c r="C6" t="n">
+        <v>767.5239914743345</v>
+      </c>
       <c r="D6" t="n">
         <v>2.63705e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>111.347</v>
       </c>
+      <c r="C7" t="n">
+        <v>726.0840891802217</v>
+      </c>
       <c r="D7" t="n">
         <v>2.63134e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>109.383</v>
       </c>
+      <c r="C8" t="n">
+        <v>758.2523672785405</v>
+      </c>
       <c r="D8" t="n">
         <v>2.62561e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>105.665</v>
       </c>
+      <c r="C9" t="n">
+        <v>727.038417687603</v>
+      </c>
       <c r="D9" t="n">
         <v>2.62244e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>103.884</v>
       </c>
+      <c r="C10" t="n">
+        <v>744.9746054166079</v>
+      </c>
       <c r="D10" t="n">
         <v>2.62047e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>100.768</v>
       </c>
+      <c r="C11" t="n">
+        <v>726.1026812956326</v>
+      </c>
       <c r="D11" t="n">
         <v>2.61863e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>99.03199999999998</v>
       </c>
+      <c r="C12" t="n">
+        <v>725.1250434507513</v>
+      </c>
       <c r="D12" t="n">
         <v>2.6172e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>99.37199999999996</v>
       </c>
+      <c r="C13" t="n">
+        <v>752.2194303387037</v>
+      </c>
       <c r="D13" t="n">
         <v>2.61548e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>96.66500000000002</v>
       </c>
+      <c r="C14" t="n">
+        <v>749.4604500450446</v>
+      </c>
       <c r="D14" t="n">
         <v>2.61366e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>93.41800000000001</v>
       </c>
+      <c r="C15" t="n">
+        <v>705.6330908268736</v>
+      </c>
       <c r="D15" t="n">
         <v>2.61342e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>95.50299999999999</v>
       </c>
+      <c r="C16" t="n">
+        <v>790.1110086801538</v>
+      </c>
       <c r="D16" t="n">
         <v>2.61245e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>93.28700000000003</v>
       </c>
+      <c r="C17" t="n">
+        <v>743.471555208539</v>
+      </c>
       <c r="D17" t="n">
         <v>2.61202e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>92.59300000000002</v>
       </c>
+      <c r="C18" t="n">
+        <v>752.270313649955</v>
+      </c>
       <c r="D18" t="n">
         <v>2.61212e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>90.75699999999995</v>
       </c>
+      <c r="C19" t="n">
+        <v>748.0573938704252</v>
+      </c>
       <c r="D19" t="n">
         <v>2.61205e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>89.47899999999998</v>
       </c>
+      <c r="C20" t="n">
+        <v>757.4092679406039</v>
+      </c>
       <c r="D20" t="n">
         <v>2.60874e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>86.88099999999997</v>
       </c>
+      <c r="C21" t="n">
+        <v>734.4330713570612</v>
+      </c>
       <c r="D21" t="n">
         <v>2.61001e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>85.89600000000002</v>
+      </c>
+      <c r="C22" t="n">
+        <v>736.2240680977075</v>
       </c>
       <c r="D22" t="n">
         <v>2.60994e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>109.144</v>
       </c>
+      <c r="C2" t="n">
+        <v>2386.675364230263</v>
+      </c>
       <c r="D2" t="n">
         <v>2.834e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>89.58800000000002</v>
       </c>
+      <c r="C3" t="n">
+        <v>1328.558266342234</v>
+      </c>
       <c r="D3" t="n">
         <v>2.73136e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>81.76600000000002</v>
       </c>
+      <c r="C4" t="n">
+        <v>995.6471073911562</v>
+      </c>
       <c r="D4" t="n">
         <v>2.683e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>78.61800000000005</v>
       </c>
+      <c r="C5" t="n">
+        <v>1053.265476699659</v>
+      </c>
       <c r="D5" t="n">
         <v>2.65526e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>74.786</v>
       </c>
+      <c r="C6" t="n">
+        <v>972.5608252219367</v>
+      </c>
       <c r="D6" t="n">
         <v>2.63917e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>71.185</v>
       </c>
+      <c r="C7" t="n">
+        <v>1005.947245365639</v>
+      </c>
       <c r="D7" t="n">
         <v>2.62756e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>70.31399999999996</v>
       </c>
+      <c r="C8" t="n">
+        <v>1190.784595482574</v>
+      </c>
       <c r="D8" t="n">
         <v>2.62081e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>67.03799999999995</v>
       </c>
+      <c r="C9" t="n">
+        <v>1053.185439353647</v>
+      </c>
       <c r="D9" t="n">
         <v>2.61662e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>59.34199999999998</v>
       </c>
+      <c r="C10" t="n">
+        <v>777.9372346278989</v>
+      </c>
       <c r="D10" t="n">
         <v>2.61241e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>62.63499999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1140.851635996534</v>
       </c>
       <c r="D11" t="n">
         <v>2.6101e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
@@ -565,7 +565,7 @@
         <v>149.777</v>
       </c>
       <c r="C2" t="n">
-        <v>800.2887631759555</v>
+        <v>149.777</v>
       </c>
       <c r="D2" t="n">
         <v>2.55167e-07</v>
@@ -597,11 +597,10 @@
       <c r="X2" t="n">
         <v>-12302.18729375609</v>
       </c>
-      <c r="Y2" t="n">
-        <v>484.6443158837664</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>19228163.5771528</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>4.107426050646521e-07</v>
@@ -618,7 +617,7 @@
         <v>143.134</v>
       </c>
       <c r="C3" t="n">
-        <v>792.7222289381001</v>
+        <v>340.3160227094097</v>
       </c>
       <c r="D3" t="n">
         <v>2.53626e-07</v>
@@ -651,16 +650,13 @@
         <v>-13530.06999235967</v>
       </c>
       <c r="Y3" t="n">
-        <v>477.610994005233</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>21988711.72870108</v>
+        <v>189.7385131128233</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.915264688983131e-07</v>
+        <v>3.573172753981609e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9332769936041232</v>
+        <v>0.9438819616480066</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +667,7 @@
         <v>138.388</v>
       </c>
       <c r="C4" t="n">
-        <v>820.5295595666877</v>
+        <v>333.0685903256355</v>
       </c>
       <c r="D4" t="n">
         <v>2.52538e-07</v>
@@ -704,16 +700,13 @@
         <v>-14158.24750389202</v>
       </c>
       <c r="Y4" t="n">
-        <v>471.647745107983</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>198526337.7212156</v>
+        <v>189.5884509402983</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.800388687384269e-07</v>
+        <v>3.445478441652766e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9371488906703588</v>
+        <v>0.9492963132567708</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +717,7 @@
         <v>133.665</v>
       </c>
       <c r="C5" t="n">
-        <v>798.2711549337172</v>
+        <v>310.7015471167241</v>
       </c>
       <c r="D5" t="n">
         <v>2.52018e-07</v>
@@ -757,16 +750,13 @@
         <v>-14484.73554295575</v>
       </c>
       <c r="Y5" t="n">
-        <v>466.0288724821089</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>214628173.4481199</v>
+        <v>205.739592179875</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.725087214834107e-07</v>
+        <v>3.596141278376962e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9398869957070792</v>
+        <v>0.9553299231171217</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +767,7 @@
         <v>128.212</v>
       </c>
       <c r="C6" t="n">
-        <v>797.0878286091353</v>
+        <v>128.212</v>
       </c>
       <c r="D6" t="n">
         <v>2.51621e-07</v>
@@ -809,11 +799,10 @@
       <c r="X6" t="n">
         <v>-14312.64573083237</v>
       </c>
-      <c r="Y6" t="n">
-        <v>460.5595015553163</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>189707742.4385588</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>3.650324725381416e-07</v>
@@ -830,7 +819,7 @@
         <v>121.961</v>
       </c>
       <c r="C7" t="n">
-        <v>769.9795539502384</v>
+        <v>121.961</v>
       </c>
       <c r="D7" t="n">
         <v>2.51403e-07</v>
@@ -862,11 +851,10 @@
       <c r="X7" t="n">
         <v>-13685.16593608196</v>
       </c>
-      <c r="Y7" t="n">
-        <v>455.2543043898323</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>373937725.723335</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>3.593354466531468e-07</v>
@@ -883,7 +871,7 @@
         <v>120.783</v>
       </c>
       <c r="C8" t="n">
-        <v>798.5547285131028</v>
+        <v>394.6108317671102</v>
       </c>
       <c r="D8" t="n">
         <v>2.50996e-07</v>
@@ -916,16 +904,13 @@
         <v>-14541.54287731682</v>
       </c>
       <c r="Y8" t="n">
-        <v>450.2182700074694</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>35605802.02243853</v>
+        <v>101.8267267547828</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.552398619253264e-07</v>
+        <v>2.773893140745787e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.946501646498408</v>
+        <v>0.9393534256200012</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +921,7 @@
         <v>115.751</v>
       </c>
       <c r="C9" t="n">
-        <v>775.9982923281569</v>
+        <v>115.751</v>
       </c>
       <c r="D9" t="n">
         <v>2.50784e-07</v>
@@ -968,11 +953,10 @@
       <c r="X9" t="n">
         <v>-14048.10619405686</v>
       </c>
-      <c r="Y9" t="n">
-        <v>419.8404706492517</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3667.096846773316</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>1.563779375131226e-06</v>
@@ -989,7 +973,7 @@
         <v>114.622</v>
       </c>
       <c r="C10" t="n">
-        <v>815.9473033949938</v>
+        <v>321.702057503768</v>
       </c>
       <c r="D10" t="n">
         <v>2.50683e-07</v>
@@ -1022,16 +1006,13 @@
         <v>-15050.77117242096</v>
       </c>
       <c r="Y10" t="n">
-        <v>437.8462330691353</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3627.702964538223</v>
+        <v>164.3100300531758</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.368033539037081e-07</v>
+        <v>3.022183319738761e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9927233101423436</v>
+        <v>0.957905433029238</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1023,7 @@
         <v>110.539</v>
       </c>
       <c r="C11" t="n">
-        <v>796.903194149085</v>
+        <v>380.0923604059603</v>
       </c>
       <c r="D11" t="n">
         <v>2.50499e-07</v>
@@ -1075,16 +1056,13 @@
         <v>-14576.0684310631</v>
       </c>
       <c r="Y11" t="n">
-        <v>416.803775935856</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3595.226063989589</v>
+        <v>101.1323760633984</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.234273032482909e-06</v>
+        <v>2.681229948486294e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8431218361672124</v>
+        <v>0.9433677950310474</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1219,7 @@
         <v>143.8410000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1059.132908162364</v>
+        <v>302.6950039910162</v>
       </c>
       <c r="D2" t="n">
         <v>2.63713e-07</v>
@@ -1274,16 +1252,13 @@
         <v>-11554.18489641194</v>
       </c>
       <c r="Y2" t="n">
-        <v>464.5669167919543</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>26010957.61006243</v>
+        <v>209.1732189043341</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.22327079787798e-07</v>
+        <v>3.179507607013029e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9278647255626057</v>
+        <v>0.9638737141470989</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1269,7 @@
         <v>124.12</v>
       </c>
       <c r="C3" t="n">
-        <v>812.3576181256211</v>
+        <v>124.12</v>
       </c>
       <c r="D3" t="n">
         <v>2.61359e-07</v>
@@ -1326,11 +1301,10 @@
       <c r="X3" t="n">
         <v>-12928.23248599209</v>
       </c>
-      <c r="Y3" t="n">
-        <v>452.4099188020935</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>372410298.8638328</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>3.876169113099555e-07</v>
@@ -1347,7 +1321,7 @@
         <v>116.746</v>
       </c>
       <c r="C4" t="n">
-        <v>764.8916449328779</v>
+        <v>293.7083023799225</v>
       </c>
       <c r="D4" t="n">
         <v>2.60231e-07</v>
@@ -1380,16 +1354,13 @@
         <v>-13112.04858847742</v>
       </c>
       <c r="Y4" t="n">
-        <v>447.1016415901562</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>119782754.3855883</v>
+        <v>200.5010199463136</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.762666515441864e-07</v>
+        <v>3.595006791002225e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9433403338041504</v>
+        <v>0.9600194558847074</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1371,7 @@
         <v>114.907</v>
       </c>
       <c r="C5" t="n">
-        <v>750.53080548607</v>
+        <v>306.5344189361768</v>
       </c>
       <c r="D5" t="n">
         <v>2.59858e-07</v>
@@ -1433,16 +1404,13 @@
         <v>-13642.24631611201</v>
       </c>
       <c r="Y5" t="n">
-        <v>421.6536137753115</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3646.089233381663</v>
+        <v>182.3183053170525</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.572356582753557e-07</v>
+        <v>3.339509056253794e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9195694953957788</v>
+        <v>0.9582129143449738</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1421,7 @@
         <v>111.023</v>
       </c>
       <c r="C6" t="n">
-        <v>749.0703436887376</v>
+        <v>299.6946161070261</v>
       </c>
       <c r="D6" t="n">
         <v>2.5934e-07</v>
@@ -1486,16 +1454,13 @@
         <v>-13286.15777740048</v>
       </c>
       <c r="Y6" t="n">
-        <v>419.4976855283768</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3610.386733990646</v>
+        <v>184.6214674697078</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.490054047196679e-06</v>
+        <v>3.272678622011896e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8208465766555824</v>
+        <v>0.963312870948136</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1471,7 @@
         <v>108.629</v>
       </c>
       <c r="C7" t="n">
-        <v>757.8151581983441</v>
+        <v>305.4345744791619</v>
       </c>
       <c r="D7" t="n">
         <v>2.59097e-07</v>
@@ -1539,16 +1504,13 @@
         <v>-13729.95598918011</v>
       </c>
       <c r="Y7" t="n">
-        <v>434.5103365912532</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>237920712.0999677</v>
+        <v>172.7047557071969</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.627429524089212e-07</v>
+        <v>3.143238013967782e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9482649604966916</v>
+        <v>0.9606552751605881</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1521,7 @@
         <v>106.546</v>
       </c>
       <c r="C8" t="n">
-        <v>774.7211127755741</v>
+        <v>106.546</v>
       </c>
       <c r="D8" t="n">
         <v>2.58949e-07</v>
@@ -1591,11 +1553,10 @@
       <c r="X8" t="n">
         <v>-13847.85787379509</v>
       </c>
-      <c r="Y8" t="n">
-        <v>430.4014385069506</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>133690707.1178724</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>3.58462807520919e-07</v>
@@ -1612,7 +1573,7 @@
         <v>102.538</v>
       </c>
       <c r="C9" t="n">
-        <v>731.8293537151964</v>
+        <v>280.8968878349414</v>
       </c>
       <c r="D9" t="n">
         <v>2.58908e-07</v>
@@ -1645,16 +1606,13 @@
         <v>-13309.10489660023</v>
       </c>
       <c r="Y9" t="n">
-        <v>426.597419479509</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>235269496.7540282</v>
+        <v>187.4220072771888</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.55385637411946e-07</v>
+        <v>3.116172490641323e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9512727297670936</v>
+        <v>0.9716529407192351</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1623,7 @@
         <v>101.966</v>
       </c>
       <c r="C10" t="n">
-        <v>770.0429450508918</v>
+        <v>276.3297947416748</v>
       </c>
       <c r="D10" t="n">
         <v>2.58923e-07</v>
@@ -1698,16 +1656,13 @@
         <v>-14119.92997259863</v>
       </c>
       <c r="Y10" t="n">
-        <v>423.0732388556012</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>347548888.3566003</v>
+        <v>188.6257709202643</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.531580115747654e-07</v>
+        <v>3.1291966861548e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9522221566648701</v>
+        <v>0.9735306657861389</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1673,7 @@
         <v>99.24299999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>732.5653319221127</v>
+        <v>267.3960381421875</v>
       </c>
       <c r="D11" t="n">
         <v>2.58747e-07</v>
@@ -1751,16 +1706,13 @@
         <v>-13594.47007781174</v>
       </c>
       <c r="Y11" t="n">
-        <v>419.7788442639665</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>343953770.7519221</v>
+        <v>193.4405304537988</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.516475567163398e-07</v>
+        <v>3.157738714943498e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.952794073593166</v>
+        <v>0.9760965384000487</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1723,7 @@
         <v>97.50200000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>751.3700864422563</v>
+        <v>271.3880558336265</v>
       </c>
       <c r="D12" t="n">
         <v>2.58569e-07</v>
@@ -1804,16 +1756,13 @@
         <v>-13953.9877206023</v>
       </c>
       <c r="Y12" t="n">
-        <v>416.6056952702053</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>227892616.6250862</v>
+        <v>186.1551196654945</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.487872541914937e-07</v>
+        <v>3.055661958278647e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9539326543696142</v>
+        <v>0.976789064684941</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1773,7 @@
         <v>96.93099999999998</v>
       </c>
       <c r="C13" t="n">
-        <v>778.0355881324057</v>
+        <v>96.93099999999998</v>
       </c>
       <c r="D13" t="n">
         <v>2.58524e-07</v>
@@ -1856,11 +1805,10 @@
       <c r="X13" t="n">
         <v>-14629.52137263942</v>
       </c>
-      <c r="Y13" t="n">
-        <v>413.5657963968105</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>226496233.9343009</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>3.46955902032398e-07</v>
@@ -1877,7 +1825,7 @@
         <v>95.71999999999997</v>
       </c>
       <c r="C14" t="n">
-        <v>770.0002868696703</v>
+        <v>259.2452492371034</v>
       </c>
       <c r="D14" t="n">
         <v>2.58622e-07</v>
@@ -1910,16 +1858,13 @@
         <v>-14410.46686349054</v>
       </c>
       <c r="Y14" t="n">
-        <v>410.5436983794904</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>224314187.4534663</v>
+        <v>190.5356644296069</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.457145011466897e-07</v>
+        <v>2.965040942873178e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9553120612531133</v>
+        <v>0.9827252049052968</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1875,7 @@
         <v>93.02499999999998</v>
       </c>
       <c r="C15" t="n">
-        <v>751.8614978431298</v>
+        <v>257.9980641867082</v>
       </c>
       <c r="D15" t="n">
         <v>2.58401e-07</v>
@@ -1963,16 +1908,13 @@
         <v>-14057.28857993719</v>
       </c>
       <c r="Y15" t="n">
-        <v>407.6201432992885</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>167063955.362845</v>
+        <v>189.0250559542333</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.448318077236802e-07</v>
+        <v>2.936031573922313e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9555942880773387</v>
+        <v>0.9846162082267244</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1925,7 @@
         <v>93.37799999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>798.8076960802003</v>
+        <v>285.3591036857357</v>
       </c>
       <c r="D16" t="n">
         <v>2.58322e-07</v>
@@ -2016,16 +1958,13 @@
         <v>-15064.92912862336</v>
       </c>
       <c r="Y16" t="n">
-        <v>404.7066783950125</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>221101391.716084</v>
+        <v>157.3541163692971</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.418394142851484e-07</v>
+        <v>2.709512346655522e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9568570504678677</v>
+        <v>0.9758100895008444</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1975,7 @@
         <v>91.22000000000003</v>
       </c>
       <c r="C17" t="n">
-        <v>766.4408331436923</v>
+        <v>250.0903876624925</v>
       </c>
       <c r="D17" t="n">
         <v>2.58377e-07</v>
@@ -2069,16 +2008,13 @@
         <v>-14371.82169837948</v>
       </c>
       <c r="Y17" t="n">
-        <v>401.7001586722404</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>110069402.4358505</v>
+        <v>189.3934221108339</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.410235923320787e-07</v>
+        <v>2.866415153886383e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9572641203275785</v>
+        <v>0.9883878636702023</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2025,7 @@
         <v>88.93200000000002</v>
       </c>
       <c r="C18" t="n">
-        <v>741.4228566317064</v>
+        <v>63.47540522298539</v>
       </c>
       <c r="D18" t="n">
         <v>2.58486e-07</v>
@@ -2122,10 +2058,7 @@
         <v>-13715.59214289839</v>
       </c>
       <c r="Y18" t="n">
-        <v>398.8003103118868</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>128816779.3976977</v>
+        <v>482.4085550113679</v>
       </c>
       <c r="AA18" t="n">
         <v>3.393441483635864e-07</v>
@@ -2142,7 +2075,7 @@
         <v>87.98099999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>772.3901811928334</v>
+        <v>87.98099999999999</v>
       </c>
       <c r="D19" t="n">
         <v>2.58477e-07</v>
@@ -2174,11 +2107,10 @@
       <c r="X19" t="n">
         <v>-14476.93932113545</v>
       </c>
-      <c r="Y19" t="n">
-        <v>395.7982449995955</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>164083270.5618534</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>3.381774309808566e-07</v>
@@ -2195,7 +2127,7 @@
         <v>85.44800000000004</v>
       </c>
       <c r="C20" t="n">
-        <v>625.505143681647</v>
+        <v>243.6603014925265</v>
       </c>
       <c r="D20" t="n">
         <v>2.58436e-07</v>
@@ -2228,16 +2160,13 @@
         <v>-13502.75764225445</v>
       </c>
       <c r="Y20" t="n">
-        <v>392.7764364802676</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>551036241.5742298</v>
+        <v>185.8524012390598</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.372725973788375e-07</v>
+        <v>2.808824807831659e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9589931484162577</v>
+        <v>0.9920247426017188</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2177,7 @@
         <v>84.29000000000002</v>
       </c>
       <c r="C21" t="n">
-        <v>742.1748521613763</v>
+        <v>271.6267800408974</v>
       </c>
       <c r="D21" t="n">
         <v>2.58408e-07</v>
@@ -2281,16 +2210,13 @@
         <v>-13732.67334728539</v>
       </c>
       <c r="Y21" t="n">
-        <v>389.650751228401</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>162026564.2009178</v>
+        <v>153.8745458019505</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.350946982634335e-07</v>
+        <v>2.546837796483939e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9599547698236929</v>
+        <v>0.9839459899676958</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2227,7 @@
         <v>84.62599999999998</v>
       </c>
       <c r="C22" t="n">
-        <v>804.2855514340722</v>
+        <v>266.7799262581209</v>
       </c>
       <c r="D22" t="n">
         <v>2.58429e-07</v>
@@ -2334,16 +2260,13 @@
         <v>-14964.80139226499</v>
       </c>
       <c r="Y22" t="n">
-        <v>386.626075689845</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>316634737.7815642</v>
+        <v>154.8551647579869</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.339554145431989e-07</v>
+        <v>2.501687401938885e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9604898051126254</v>
+        <v>0.9861647315828365</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2423,7 @@
         <v>127.1440000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>769.9790416431434</v>
+        <v>371.938469138109</v>
       </c>
       <c r="D2" t="n">
         <v>2.58421e-07</v>
@@ -2533,16 +2456,13 @@
         <v>-14156.60907079565</v>
       </c>
       <c r="Y2" t="n">
-        <v>474.940972567993</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>264274225.8072468</v>
+        <v>154.0166089245928</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.836824299068841e-07</v>
+        <v>3.513437515105609e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9393328586338238</v>
+        <v>0.9328215256183515</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2473,7 @@
         <v>126.216</v>
       </c>
       <c r="C3" t="n">
-        <v>795.4993846942464</v>
+        <v>381.682495858244</v>
       </c>
       <c r="D3" t="n">
         <v>2.56412e-07</v>
@@ -2586,16 +2506,13 @@
         <v>-15440.27682491637</v>
       </c>
       <c r="Y3" t="n">
-        <v>472.1234971601919</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>646073718.2939132</v>
+        <v>140.3599797470666</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.718775417466821e-07</v>
+        <v>3.387501888538049e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9428675605193312</v>
+        <v>0.9306869340944792</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2523,7 @@
         <v>122.717</v>
       </c>
       <c r="C4" t="n">
-        <v>791.121108481082</v>
+        <v>447.8588369273911</v>
       </c>
       <c r="D4" t="n">
         <v>2.55514e-07</v>
@@ -2639,16 +2556,13 @@
         <v>-15076.16360233346</v>
       </c>
       <c r="Y4" t="n">
-        <v>468.2093199297603</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>512473875.0277551</v>
+        <v>68.46760470664971</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.659261456371368e-07</v>
+        <v>2.814153697505869e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9447896744294128</v>
+        <v>0.9215841982004477</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2573,7 @@
         <v>120.883</v>
       </c>
       <c r="C5" t="n">
-        <v>814.5259067031121</v>
+        <v>120.883</v>
       </c>
       <c r="D5" t="n">
         <v>2.54836e-07</v>
@@ -2691,11 +2605,10 @@
       <c r="X5" t="n">
         <v>-15503.24818225107</v>
       </c>
-      <c r="Y5" t="n">
-        <v>463.6177622555926</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>60892684.35987416</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>3.595944668508762e-07</v>
@@ -2712,7 +2625,7 @@
         <v>115.995</v>
       </c>
       <c r="C6" t="n">
-        <v>786.7964868584397</v>
+        <v>341.9188317087776</v>
       </c>
       <c r="D6" t="n">
         <v>2.544e-07</v>
@@ -2745,16 +2658,13 @@
         <v>-14949.68620077269</v>
       </c>
       <c r="Y6" t="n">
-        <v>448.6815921335364</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3774.299972311237</v>
+        <v>164.3802334509311</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.307615251359875e-06</v>
+        <v>3.293829849620484e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8542048937062423</v>
+        <v>0.9471446820404331</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2675,7 @@
         <v>116.777</v>
       </c>
       <c r="C7" t="n">
-        <v>831.7611886766609</v>
+        <v>334.9409481720053</v>
       </c>
       <c r="D7" t="n">
         <v>2.54052e-07</v>
@@ -2798,16 +2708,13 @@
         <v>-16713.11102416616</v>
       </c>
       <c r="Y7" t="n">
-        <v>434.9773937411602</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3733.140458215095</v>
+        <v>165.5018061728215</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.301724932490023e-06</v>
+        <v>3.23786257348787e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8642360737634867</v>
+        <v>0.9500701204194404</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2725,7 @@
         <v>112.283</v>
       </c>
       <c r="C8" t="n">
-        <v>820.9722548703857</v>
+        <v>112.283</v>
       </c>
       <c r="D8" t="n">
         <v>2.54037e-07</v>
@@ -2850,11 +2757,10 @@
       <c r="X8" t="n">
         <v>-16136.46163690372</v>
       </c>
-      <c r="Y8" t="n">
-        <v>434.7262552700104</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>7441.511081075255</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>3.597721446077188e-07</v>
@@ -2871,7 +2777,7 @@
         <v>107.853</v>
       </c>
       <c r="C9" t="n">
-        <v>776.3413640131756</v>
+        <v>357.6419398590171</v>
       </c>
       <c r="D9" t="n">
         <v>2.53716e-07</v>
@@ -2904,16 +2810,13 @@
         <v>-15299.46735871453</v>
       </c>
       <c r="Y9" t="n">
-        <v>445.008667827318</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>486373584.8139477</v>
+        <v>131.3135710145079</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.441654179782531e-07</v>
+        <v>2.917609580625833e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9530521382708723</v>
+        <v>0.9450530178708098</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2827,7 @@
         <v>104.977</v>
       </c>
       <c r="C10" t="n">
-        <v>790.604434091499</v>
+        <v>371.8294254764298</v>
       </c>
       <c r="D10" t="n">
         <v>2.53629e-07</v>
@@ -2957,16 +2860,13 @@
         <v>-15215.18828857467</v>
       </c>
       <c r="Y10" t="n">
-        <v>440.893649765704</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>271883201.9115602</v>
+        <v>112.9092702586106</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.414356616121575e-07</v>
+        <v>2.764657481136685e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9542145919593925</v>
+        <v>0.9455227437045913</v>
       </c>
     </row>
     <row r="11">
@@ -2977,7 +2877,7 @@
         <v>103.166</v>
       </c>
       <c r="C11" t="n">
-        <v>809.5966989096476</v>
+        <v>103.166</v>
       </c>
       <c r="D11" t="n">
         <v>2.53481e-07</v>
@@ -3009,11 +2909,10 @@
       <c r="X11" t="n">
         <v>-15663.8652472838</v>
       </c>
-      <c r="Y11" t="n">
-        <v>436.9422448663099</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>179493570.8718365</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>3.395003737481824e-07</v>
@@ -3030,7 +2929,7 @@
         <v>99.22300000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>773.5444879549773</v>
+        <v>477.5944548938966</v>
       </c>
       <c r="D12" t="n">
         <v>2.53387e-07</v>
@@ -3063,16 +2962,13 @@
         <v>-14468.74078383779</v>
       </c>
       <c r="Y12" t="n">
-        <v>433.2828176238438</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>473482797.4171944</v>
+        <v>0.2419169795772483</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.368441139985179e-07</v>
+        <v>2.492726733746164e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9561329531221543</v>
+        <v>0.9172777787060682</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2979,7 @@
         <v>99.452</v>
       </c>
       <c r="C13" t="n">
-        <v>807.0877531293008</v>
+        <v>326.1299824868346</v>
       </c>
       <c r="D13" t="n">
         <v>2.53204e-07</v>
@@ -3116,16 +3012,13 @@
         <v>-15875.79091736646</v>
       </c>
       <c r="Y13" t="n">
-        <v>429.7443921062749</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>117771042.3196444</v>
+        <v>145.5015938584397</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.343280724412004e-07</v>
+        <v>2.865322391606407e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9571664789309613</v>
+        <v>0.9581640212162504</v>
       </c>
     </row>
     <row r="14">
@@ -3136,7 +3029,7 @@
         <v>98.798</v>
       </c>
       <c r="C14" t="n">
-        <v>854.6019771770884</v>
+        <v>288.0147729394255</v>
       </c>
       <c r="D14" t="n">
         <v>2.53008e-07</v>
@@ -3169,16 +3062,13 @@
         <v>-16876.55652121696</v>
       </c>
       <c r="Y14" t="n">
-        <v>426.4700305922341</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>349439032.2707579</v>
+        <v>179.1748408365601</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.321317152969503e-07</v>
+        <v>2.939926609646586e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9580557726845003</v>
+        <v>0.9711034212846585</v>
       </c>
     </row>
     <row r="15">
@@ -3189,7 +3079,7 @@
         <v>95.03299999999996</v>
       </c>
       <c r="C15" t="n">
-        <v>806.9524713605816</v>
+        <v>319.5332533765264</v>
       </c>
       <c r="D15" t="n">
         <v>2.52919e-07</v>
@@ -3222,16 +3112,13 @@
         <v>-15598.73986141956</v>
       </c>
       <c r="Y15" t="n">
-        <v>423.1897734463594</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>231090589.7369125</v>
+        <v>144.0935369543707</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.312041895641052e-07</v>
+        <v>2.745496134336673e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9584411570238839</v>
+        <v>0.963061685267614</v>
       </c>
     </row>
     <row r="16">
@@ -3242,7 +3129,7 @@
         <v>92.06999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>774.8898735317663</v>
+        <v>288.9643491045799</v>
       </c>
       <c r="D16" t="n">
         <v>2.52793e-07</v>
@@ -3275,16 +3162,13 @@
         <v>-14845.89365442346</v>
       </c>
       <c r="Y16" t="n">
-        <v>420.1364422536576</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>229488003.6014582</v>
+        <v>171.6062762806031</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.283815292238171e-07</v>
+        <v>2.879137177870972e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9596587564260722</v>
+        <v>0.9728939090630653</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3179,7 @@
         <v>90.416</v>
       </c>
       <c r="C17" t="n">
-        <v>753.2736593465946</v>
+        <v>278.7737549783109</v>
       </c>
       <c r="D17" t="n">
         <v>2.5275e-07</v>
@@ -3328,16 +3212,13 @@
         <v>-14845.28514461852</v>
       </c>
       <c r="Y17" t="n">
-        <v>417.1300157044847</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>227902862.8026039</v>
+        <v>177.8235217445739</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.278471387005311e-07</v>
+        <v>2.843995176999211e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9598885543490819</v>
+        <v>0.9773054930627708</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3229,7 @@
         <v>90.17599999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>823.7298692865413</v>
+        <v>90.17599999999999</v>
       </c>
       <c r="D18" t="n">
         <v>2.52591e-07</v>
@@ -3380,11 +3261,10 @@
       <c r="X18" t="n">
         <v>-15811.26067139286</v>
       </c>
-      <c r="Y18" t="n">
-        <v>414.3051543601015</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>460058898.2584543</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>3.261811176964296e-07</v>
@@ -3401,7 +3281,7 @@
         <v>89.93199999999996</v>
       </c>
       <c r="C19" t="n">
-        <v>845.0989610980768</v>
+        <v>280.294967512676</v>
       </c>
       <c r="D19" t="n">
         <v>2.52559e-07</v>
@@ -3434,16 +3314,13 @@
         <v>-16420.46539105344</v>
       </c>
       <c r="Y19" t="n">
-        <v>411.5490035160651</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>168752308.0618253</v>
+        <v>169.5671932889515</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.251941750184349e-07</v>
+        <v>2.719553489334487e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9610217472889362</v>
+        <v>0.9783727008475666</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3331,7 @@
         <v>87.96199999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>809.5146414070073</v>
+        <v>270.8558412581488</v>
       </c>
       <c r="D20" t="n">
         <v>2.52297e-07</v>
@@ -3487,16 +3364,13 @@
         <v>-16062.84613889791</v>
       </c>
       <c r="Y20" t="n">
-        <v>408.8704165918489</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>168095581.7973329</v>
+        <v>175.4444791842861</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.229772076629964e-07</v>
+        <v>2.708839093413237e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9619043666040857</v>
+        <v>0.9815264285342374</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3381,7 @@
         <v>86.75200000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>811.8817423752565</v>
+        <v>349.4324094076645</v>
       </c>
       <c r="D21" t="n">
         <v>2.52289e-07</v>
@@ -3540,16 +3414,13 @@
         <v>-16189.76253744107</v>
       </c>
       <c r="Y21" t="n">
-        <v>406.284325692896</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>332543948.5380579</v>
+        <v>94.39163065333339</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.231087856751578e-07</v>
+        <v>2.311291726507102e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.961851215372903</v>
+        <v>0.9606238628141651</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3431,7 @@
         <v>85.67599999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>806.0935424308382</v>
+        <v>267.4376665123333</v>
       </c>
       <c r="D22" t="n">
         <v>2.52152e-07</v>
@@ -3593,16 +3464,13 @@
         <v>-16001.83436353783</v>
       </c>
       <c r="Y22" t="n">
-        <v>403.7662899693652</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>165378171.6926379</v>
+        <v>173.4887364252217</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.210059814721662e-07</v>
+        <v>2.661731324703165e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9627495211170048</v>
+        <v>0.985300383914528</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3627,7 @@
         <v>153.955</v>
       </c>
       <c r="C2" t="n">
-        <v>6189.082884579291</v>
+        <v>384.620686790406</v>
       </c>
       <c r="D2" t="n">
         <v>2.82179e-07</v>
@@ -3792,16 +3660,13 @@
         <v>-6207.442793447139</v>
       </c>
       <c r="Y2" t="n">
-        <v>451.6044662754214</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>123710028.0486032</v>
+        <v>109.1904578233875</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.987296709227189e-07</v>
+        <v>1.973273181449503e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8860798530389814</v>
+        <v>0.9594007059206939</v>
       </c>
     </row>
     <row r="3">
@@ -3812,7 +3677,7 @@
         <v>103.72</v>
       </c>
       <c r="C3" t="n">
-        <v>947.9746486402793</v>
+        <v>268.4931356187633</v>
       </c>
       <c r="D3" t="n">
         <v>2.81987e-07</v>
@@ -3845,16 +3710,13 @@
         <v>-7085.928005201331</v>
       </c>
       <c r="Y3" t="n">
-        <v>405.7275238830791</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3497.19477476956</v>
+        <v>198.7207084519527</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.930271585502584e-06</v>
+        <v>3.086283285845805e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8090104878817128</v>
+        <v>0.975387066579277</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3727,7 @@
         <v>93.56900000000002</v>
       </c>
       <c r="C4" t="n">
-        <v>810.7598585317664</v>
+        <v>261.6425076443134</v>
       </c>
       <c r="D4" t="n">
         <v>2.77439e-07</v>
@@ -3898,16 +3760,13 @@
         <v>-8148.78475507964</v>
       </c>
       <c r="Y4" t="n">
-        <v>417.0788436500541</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>171108914.0719451</v>
+        <v>195.856163906974</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.406417280158856e-07</v>
+        <v>3.131484196825904e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9294396848737421</v>
+        <v>0.9759805735450716</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3777,7 @@
         <v>91.02599999999995</v>
       </c>
       <c r="C5" t="n">
-        <v>892.1402764082138</v>
+        <v>259.8610588232357</v>
       </c>
       <c r="D5" t="n">
         <v>2.73509e-07</v>
@@ -3951,16 +3810,13 @@
         <v>-9233.578607174244</v>
       </c>
       <c r="Y5" t="n">
-        <v>411.95015765415</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>122678950.6087333</v>
+        <v>191.666654154508</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.159569684637911e-07</v>
+        <v>3.029753258025574e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9359526637122982</v>
+        <v>0.9796947833900198</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3827,7 @@
         <v>87.70499999999998</v>
       </c>
       <c r="C6" t="n">
-        <v>889.1620024093568</v>
+        <v>87.70499999999998</v>
       </c>
       <c r="D6" t="n">
         <v>2.70279e-07</v>
@@ -4003,11 +3859,10 @@
       <c r="X6" t="n">
         <v>-9791.983836112289</v>
       </c>
-      <c r="Y6" t="n">
-        <v>407.2572311950503</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>166679622.0401532</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>3.980804043968316e-07</v>
@@ -4024,7 +3879,7 @@
         <v>83.68599999999998</v>
       </c>
       <c r="C7" t="n">
-        <v>845.0128609700602</v>
+        <v>246.6773879535345</v>
       </c>
       <c r="D7" t="n">
         <v>2.68014e-07</v>
@@ -4057,16 +3912,13 @@
         <v>-10126.91612636652</v>
       </c>
       <c r="Y7" t="n">
-        <v>402.3693947042688</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>219554492.4735357</v>
+        <v>192.7408039544886</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.84345606726226e-07</v>
+        <v>2.758600996968194e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9447820658291792</v>
+        <v>0.9912298863290699</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3929,7 @@
         <v>81.24900000000002</v>
       </c>
       <c r="C8" t="n">
-        <v>930.5615658803188</v>
+        <v>241.3882761002113</v>
       </c>
       <c r="D8" t="n">
         <v>2.65986e-07</v>
@@ -4110,16 +3962,13 @@
         <v>-10775.87667963186</v>
       </c>
       <c r="Y8" t="n">
-        <v>397.3423208388615</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>216845551.8079745</v>
+        <v>191.6290155934657</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.735928600554866e-07</v>
+        <v>2.658021469510942e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9479219536291398</v>
+        <v>0.9951342293284972</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3979,7 @@
         <v>79.82499999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>944.9416680229909</v>
+        <v>238.0408099291093</v>
       </c>
       <c r="D9" t="n">
         <v>2.64515e-07</v>
@@ -4163,16 +4012,13 @@
         <v>-11360.28440174351</v>
       </c>
       <c r="Y9" t="n">
-        <v>392.540273618457</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>222635345.1394069</v>
+        <v>189.2656303686368</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.652005862649169e-07</v>
+        <v>2.588567475599677e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9505198874354319</v>
+        <v>0.9979989163928418</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4029,7 @@
         <v>76.28800000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>926.2812813035268</v>
+        <v>245.8128262802653</v>
       </c>
       <c r="D10" t="n">
         <v>2.63282e-07</v>
@@ -4216,16 +4062,13 @@
         <v>-11370.08337581963</v>
       </c>
       <c r="Y10" t="n">
-        <v>388.0951011812932</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>423062157.5231858</v>
+        <v>177.7703981779107</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.585997180361561e-07</v>
+        <v>2.504059227778809e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9525680438297079</v>
+        <v>0.9977400689072703</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4079,7 @@
         <v>72.517</v>
       </c>
       <c r="C11" t="n">
-        <v>837.5354711499788</v>
+        <v>260.4046740486132</v>
       </c>
       <c r="D11" t="n">
         <v>2.62378e-07</v>
@@ -4269,16 +4112,13 @@
         <v>-11075.06631422567</v>
       </c>
       <c r="Y11" t="n">
-        <v>383.9272286990046</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>254617483.0617626</v>
+        <v>161.201973706781</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.533173101994421e-07</v>
+        <v>2.289044705368428e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9542903154861091</v>
+        <v>0.9997152251049822</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +4275,7 @@
         <v>156.033</v>
       </c>
       <c r="C2" t="n">
-        <v>1153.220572953452</v>
+        <v>341.5126940537235</v>
       </c>
       <c r="D2" t="n">
         <v>2.74005e-07</v>
@@ -4468,16 +4308,13 @@
         <v>-9558.347632635645</v>
       </c>
       <c r="Y2" t="n">
-        <v>487.9594042690175</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>20870563.31481155</v>
+        <v>198.8481533714786</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.064964654546895e-07</v>
+        <v>3.522890125479346e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.906431124011674</v>
+        <v>0.9434957882090091</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4325,7 @@
         <v>132.4780000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>822.4331656731661</v>
+        <v>312.832523973799</v>
       </c>
       <c r="D3" t="n">
         <v>2.69425e-07</v>
@@ -4521,16 +4358,13 @@
         <v>-11400.5074043747</v>
       </c>
       <c r="Y3" t="n">
-        <v>475.5846047802367</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>62337363.4492505</v>
+        <v>214.6969413430861</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.386627859863791e-07</v>
+        <v>4.073488248156012e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.925488981423517</v>
+        <v>0.9459804811008092</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4375,7 @@
         <v>126.674</v>
       </c>
       <c r="C4" t="n">
-        <v>786.7698965945493</v>
+        <v>126.674</v>
       </c>
       <c r="D4" t="n">
         <v>2.66225e-07</v>
@@ -4573,11 +4407,10 @@
       <c r="X4" t="n">
         <v>-12495.55134428585</v>
       </c>
-      <c r="Y4" t="n">
-        <v>470.224807312236</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>40256233.97970039</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>4.126434324001954e-07</v>
@@ -4594,7 +4427,7 @@
         <v>122.492</v>
       </c>
       <c r="C5" t="n">
-        <v>804.9592942507388</v>
+        <v>310.1135315377255</v>
       </c>
       <c r="D5" t="n">
         <v>2.64118e-07</v>
@@ -4627,16 +4460,13 @@
         <v>-13397.3099027157</v>
       </c>
       <c r="Y5" t="n">
-        <v>465.4798622222645</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>510318735.3978912</v>
+        <v>205.3271501372671</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.972672512095646e-07</v>
+        <v>4.010472955741849e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9374266052950188</v>
+        <v>0.9465719357510054</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4477,7 @@
         <v>120.781</v>
       </c>
       <c r="C6" t="n">
-        <v>824.3506363670142</v>
+        <v>298.6258601752028</v>
       </c>
       <c r="D6" t="n">
         <v>2.6246e-07</v>
@@ -4680,16 +4510,13 @@
         <v>-14245.03114372677</v>
       </c>
       <c r="Y6" t="n">
-        <v>460.7156419459649</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>632546268.4056382</v>
+        <v>209.6329187623107</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.863215574310486e-07</v>
+        <v>3.722025032780936e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9407106410451536</v>
+        <v>0.9539582735738446</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4527,7 @@
         <v>117.48</v>
       </c>
       <c r="C7" t="n">
-        <v>800.2835929732237</v>
+        <v>329.2949939477349</v>
       </c>
       <c r="D7" t="n">
         <v>2.61492e-07</v>
@@ -4733,16 +4560,13 @@
         <v>-14663.55578002072</v>
       </c>
       <c r="Y7" t="n">
-        <v>455.9903720540548</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>623760284.3014617</v>
+        <v>174.3995094992139</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.770012462716079e-07</v>
+        <v>3.397639581373871e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9438348303464029</v>
+        <v>0.9498562201822816</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4577,7 @@
         <v>112.723</v>
       </c>
       <c r="C8" t="n">
-        <v>795.2704471792111</v>
+        <v>303.5348998632514</v>
       </c>
       <c r="D8" t="n">
         <v>2.60746e-07</v>
@@ -4786,16 +4610,13 @@
         <v>-14189.71567726549</v>
       </c>
       <c r="Y8" t="n">
-        <v>447.6027129400221</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3715.982269439966</v>
+        <v>194.0306974174223</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.771898486089274e-06</v>
+        <v>3.493100403337354e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8228173929287063</v>
+        <v>0.9570905092031583</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4627,7 @@
         <v>110.07</v>
       </c>
       <c r="C9" t="n">
-        <v>779.3592661637773</v>
+        <v>295.5814856614403</v>
       </c>
       <c r="D9" t="n">
         <v>2.59913e-07</v>
@@ -4839,16 +4660,13 @@
         <v>-14333.15111980325</v>
       </c>
       <c r="Y9" t="n">
-        <v>430.1826088687079</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6012.003209406022</v>
+        <v>197.022342486217</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.648794861625218e-07</v>
+        <v>3.452569082248832e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9981333489221115</v>
+        <v>0.9595432960408571</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4677,7 @@
         <v>108.158</v>
       </c>
       <c r="C10" t="n">
-        <v>790.9894031575437</v>
+        <v>320.6207326219905</v>
       </c>
       <c r="D10" t="n">
         <v>2.59559e-07</v>
@@ -4892,16 +4710,13 @@
         <v>-14928.62125492235</v>
       </c>
       <c r="Y10" t="n">
-        <v>443.8291156226697</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>485415571.4548267</v>
+        <v>167.9502294127847</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.611478261242188e-07</v>
+        <v>3.253531337311352e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9492233587210586</v>
+        <v>0.9537248166004444</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4727,7 @@
         <v>104.332</v>
       </c>
       <c r="C11" t="n">
-        <v>748.8544162162301</v>
+        <v>104.332</v>
       </c>
       <c r="D11" t="n">
         <v>2.59046e-07</v>
@@ -4944,11 +4759,10 @@
       <c r="X11" t="n">
         <v>-14343.35053086576</v>
       </c>
-      <c r="Y11" t="n">
-        <v>440.5091394705662</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>722536310.2237729</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>3.579905095827634e-07</v>
@@ -4965,7 +4779,7 @@
         <v>104.526</v>
       </c>
       <c r="C12" t="n">
-        <v>792.9269411598302</v>
+        <v>346.3048172674563</v>
       </c>
       <c r="D12" t="n">
         <v>2.58745e-07</v>
@@ -4998,16 +4812,13 @@
         <v>-15231.52346824154</v>
       </c>
       <c r="Y12" t="n">
-        <v>437.4265430628149</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>183619405.8780275</v>
+        <v>133.4467600836614</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.547027152124949e-07</v>
+        <v>2.852212192578965e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9514947352039828</v>
+        <v>0.9509468811780504</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4829,7 @@
         <v>101.212</v>
       </c>
       <c r="C13" t="n">
-        <v>759.7877319627366</v>
+        <v>299.158557678455</v>
       </c>
       <c r="D13" t="n">
         <v>2.58398e-07</v>
@@ -5051,16 +4862,13 @@
         <v>-14498.78684531403</v>
       </c>
       <c r="Y13" t="n">
-        <v>434.5431997849405</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>475148769.1456621</v>
+        <v>178.2241384642971</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.513936096180505e-07</v>
+        <v>3.199060461458433e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9527096493110544</v>
+        <v>0.9616299743877114</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4879,7 @@
         <v>99.29599999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>744.447867885845</v>
+        <v>284.4372737711196</v>
       </c>
       <c r="D14" t="n">
         <v>2.58086e-07</v>
@@ -5104,16 +4912,13 @@
         <v>-14460.95431466357</v>
       </c>
       <c r="Y14" t="n">
-        <v>431.6683188885536</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>178171907.8930506</v>
+        <v>189.5667740257337</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.491869959400736e-07</v>
+        <v>3.184292017058723e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9534823363442003</v>
+        <v>0.9687286016310429</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4929,7 @@
         <v>98.173</v>
       </c>
       <c r="C15" t="n">
-        <v>754.2133300141475</v>
+        <v>290.2842117776127</v>
       </c>
       <c r="D15" t="n">
         <v>2.58077e-07</v>
@@ -5157,16 +4962,13 @@
         <v>-14604.73772751724</v>
       </c>
       <c r="Y15" t="n">
-        <v>428.9262120647479</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>132531860.5347188</v>
+        <v>180.5463951158167</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.470279622545723e-07</v>
+        <v>3.101742826933462e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9544215287585653</v>
+        <v>0.9679764721627356</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4979,7 @@
         <v>96.27600000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>754.0969417648274</v>
+        <v>96.27600000000001</v>
       </c>
       <c r="D16" t="n">
         <v>2.57822e-07</v>
@@ -5209,11 +5011,10 @@
       <c r="X16" t="n">
         <v>-14682.52046921089</v>
       </c>
-      <c r="Y16" t="n">
-        <v>426.2185258010602</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>116603561.0165156</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>3.455093855836768e-07</v>
@@ -5230,7 +5031,7 @@
         <v>94.75800000000004</v>
       </c>
       <c r="C17" t="n">
-        <v>752.0200055395501</v>
+        <v>65.08340084705549</v>
       </c>
       <c r="D17" t="n">
         <v>2.57668e-07</v>
@@ -5263,10 +5064,7 @@
         <v>-14485.50824843448</v>
       </c>
       <c r="Y17" t="n">
-        <v>423.5447604490373</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>231617670.8661659</v>
+        <v>510.1965741395969</v>
       </c>
       <c r="AA17" t="n">
         <v>3.437330883833342e-07</v>
@@ -5283,7 +5081,7 @@
         <v>96.72000000000003</v>
       </c>
       <c r="C18" t="n">
-        <v>816.7804482163108</v>
+        <v>281.6378922000838</v>
       </c>
       <c r="D18" t="n">
         <v>2.57459e-07</v>
@@ -5316,16 +5114,13 @@
         <v>-16154.3909398742</v>
       </c>
       <c r="Y18" t="n">
-        <v>420.8521465643094</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>345035231.1221668</v>
+        <v>178.9529015239474</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.414782119410137e-07</v>
+        <v>2.964999241395971e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9565266153540315</v>
+        <v>0.9730262812967327</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5131,7 @@
         <v>92.48900000000003</v>
       </c>
       <c r="C19" t="n">
-        <v>746.0535899790285</v>
+        <v>281.1403253889771</v>
       </c>
       <c r="D19" t="n">
         <v>2.57329e-07</v>
@@ -5369,16 +5164,13 @@
         <v>-14610.46845341834</v>
       </c>
       <c r="Y19" t="n">
-        <v>418.1504168581953</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>342507630.4153895</v>
+        <v>177.0298908395665</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.400493193536306e-07</v>
+        <v>2.948644143619547e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9570916827740816</v>
+        <v>0.9738446425431295</v>
       </c>
     </row>
     <row r="20">
@@ -5389,7 +5181,7 @@
         <v>92.012</v>
       </c>
       <c r="C20" t="n">
-        <v>775.2709639458604</v>
+        <v>265.9752418926728</v>
       </c>
       <c r="D20" t="n">
         <v>2.57036e-07</v>
@@ -5422,16 +5214,13 @@
         <v>-15201.22609870797</v>
       </c>
       <c r="Y20" t="n">
-        <v>415.4622142704876</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>113521306.5080879</v>
+        <v>188.7753938197784</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.380965401563013e-07</v>
+        <v>2.962967590135202e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.957803369536288</v>
+        <v>0.9801906670416515</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5231,7 @@
         <v>89.89599999999996</v>
       </c>
       <c r="C21" t="n">
-        <v>769.6214543107071</v>
+        <v>271.7289305945652</v>
       </c>
       <c r="D21" t="n">
         <v>2.57127e-07</v>
@@ -5475,16 +5264,13 @@
         <v>-15131.63707616863</v>
       </c>
       <c r="Y21" t="n">
-        <v>412.7535966023984</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>115862872.8638789</v>
+        <v>179.412209314526</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.367067698790006e-07</v>
+        <v>2.875092299773471e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9584805877494693</v>
+        <v>0.9771714620706903</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5281,7 @@
         <v>89.17500000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>768.280271696451</v>
+        <v>262.5524962950908</v>
       </c>
       <c r="D22" t="n">
         <v>2.57021e-07</v>
@@ -5528,16 +5314,13 @@
         <v>-15046.68486187088</v>
       </c>
       <c r="Y22" t="n">
-        <v>409.9987329059463</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>447755241.8436182</v>
+        <v>186.2964953763841</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.35471195665405e-07</v>
+        <v>2.916948161378201e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9589846919945907</v>
+        <v>0.9825259383785855</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5477,7 @@
         <v>142.614</v>
       </c>
       <c r="C2" t="n">
-        <v>7522.919433164251</v>
+        <v>348.7821727803554</v>
       </c>
       <c r="D2" t="n">
         <v>2.87562e-07</v>
@@ -5727,16 +5510,13 @@
         <v>-5675.637107472598</v>
       </c>
       <c r="Y2" t="n">
-        <v>445.3914207522574</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>33151691.97325099</v>
+        <v>137.3879898419361</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.166507926225259e-07</v>
+        <v>2.044990029197659e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8846643467100372</v>
+        <v>0.9662896989536379</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5527,7 @@
         <v>100.243</v>
       </c>
       <c r="C3" t="n">
-        <v>1122.975886901015</v>
+        <v>261.1914444516413</v>
       </c>
       <c r="D3" t="n">
         <v>2.86036e-07</v>
@@ -5780,16 +5560,13 @@
         <v>-6970.264701729548</v>
       </c>
       <c r="Y3" t="n">
-        <v>420.5912316038754</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>116789534.394143</v>
+        <v>199.6705970919874</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.943178437464874e-07</v>
+        <v>3.030106076438414e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9168955139039886</v>
+        <v>0.9785281455855793</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5577,7 @@
         <v>88.24000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>864.6409521131634</v>
+        <v>248.9093947491759</v>
       </c>
       <c r="D4" t="n">
         <v>2.81188e-07</v>
@@ -5833,16 +5610,13 @@
         <v>-7716.640528928568</v>
       </c>
       <c r="Y4" t="n">
-        <v>412.6878403183973</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>451117728.3695154</v>
+        <v>202.5983295672766</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.495844151210855e-07</v>
+        <v>3.129384911239832e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9285234756006745</v>
+        <v>0.9812084935041522</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5627,7 @@
         <v>85.76999999999998</v>
       </c>
       <c r="C5" t="n">
-        <v>866.5409159622992</v>
+        <v>250.5734521396404</v>
       </c>
       <c r="D5" t="n">
         <v>2.76874e-07</v>
@@ -5886,16 +5660,13 @@
         <v>-8713.051459121381</v>
       </c>
       <c r="Y5" t="n">
-        <v>407.5198338579776</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>111323395.5913109</v>
+        <v>194.979109337134</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.214655057801039e-07</v>
+        <v>2.961273727289667e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9358830006248612</v>
+        <v>0.9840904268141065</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5677,7 @@
         <v>81.64400000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>856.6403052765819</v>
+        <v>283.2205887738071</v>
       </c>
       <c r="D6" t="n">
         <v>2.73642e-07</v>
@@ -5939,16 +5710,13 @@
         <v>-9209.406278370005</v>
       </c>
       <c r="Y6" t="n">
-        <v>402.4984344616082</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>439760819.851115</v>
+        <v>155.9916345319034</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.03122837915406e-07</v>
+        <v>2.631945766365674e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9408105351430178</v>
+        <v>0.9746910921682437</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5727,7 @@
         <v>80.916</v>
       </c>
       <c r="C7" t="n">
-        <v>986.3067278864398</v>
+        <v>279.8021174472094</v>
       </c>
       <c r="D7" t="n">
         <v>2.712e-07</v>
@@ -5992,16 +5760,13 @@
         <v>-10243.33841910732</v>
       </c>
       <c r="Y7" t="n">
-        <v>397.6657207369928</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>162911489.1865705</v>
+        <v>153.5102288518864</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.882071865903075e-07</v>
+        <v>2.53955866714409e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9451251787765573</v>
+        <v>0.9790912391988458</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5777,7 @@
         <v>76.28500000000003</v>
       </c>
       <c r="C8" t="n">
-        <v>907.5028009567798</v>
+        <v>318.2313666797387</v>
       </c>
       <c r="D8" t="n">
         <v>2.69367e-07</v>
@@ -6045,16 +5810,13 @@
         <v>-10413.31872808785</v>
       </c>
       <c r="Y8" t="n">
-        <v>393.0027983229647</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>428485616.9651723</v>
+        <v>109.2881924158987</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.776945056760763e-07</v>
+        <v>2.229403099676383e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9482408226897785</v>
+        <v>0.9696335512289295</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5827,7 @@
         <v>72.05900000000003</v>
       </c>
       <c r="C9" t="n">
-        <v>840.9948212866926</v>
+        <v>343.5162145192754</v>
       </c>
       <c r="D9" t="n">
         <v>2.67726e-07</v>
@@ -6098,16 +5860,13 @@
         <v>-10173.75882095493</v>
       </c>
       <c r="Y9" t="n">
-        <v>388.6197640005519</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>423675658.5636956</v>
+        <v>79.29168929974415</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.697160895668675e-07</v>
+        <v>2.079741906545242e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9505455106039423</v>
+        <v>0.9655014841681671</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5877,7 @@
         <v>71.06999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>885.3855058677075</v>
+        <v>288.6774978650132</v>
       </c>
       <c r="D10" t="n">
         <v>2.66442e-07</v>
@@ -6151,16 +5910,13 @@
         <v>-10962.09122833541</v>
       </c>
       <c r="Y10" t="n">
-        <v>384.5405361846218</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>419182986.3963848</v>
+        <v>129.5920999219205</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.625566196419015e-07</v>
+        <v>2.244149140688562e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9527704634707345</v>
+        <v>0.9826354021049372</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5927,7 @@
         <v>70.26800000000003</v>
       </c>
       <c r="C11" t="n">
-        <v>997.8959805738725</v>
+        <v>291.2761737870491</v>
       </c>
       <c r="D11" t="n">
         <v>2.65438e-07</v>
@@ -6204,16 +5960,13 @@
         <v>-11287.12531539341</v>
       </c>
       <c r="Y11" t="n">
-        <v>380.6599388984416</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>414789006.4149199</v>
+        <v>122.2686776832073</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.57347364853231e-07</v>
+        <v>2.151771557760136e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.954390280794259</v>
+        <v>0.9837058153822389</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6123,7 @@
         <v>155.4870000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1099.451079010621</v>
+        <v>357.2997016382524</v>
       </c>
       <c r="D2" t="n">
         <v>2.84397e-07</v>
@@ -6403,16 +6156,13 @@
         <v>-7313.383695658047</v>
       </c>
       <c r="Y2" t="n">
-        <v>479.8108571237261</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>263079561.5056703</v>
+        <v>174.428222563911</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.893989755513716e-07</v>
+        <v>3.162871254473823e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8893284196781287</v>
+        <v>0.944676941817059</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6173,7 @@
         <v>130.846</v>
       </c>
       <c r="C3" t="n">
-        <v>819.6422669150433</v>
+        <v>130.846</v>
       </c>
       <c r="D3" t="n">
         <v>2.75614e-07</v>
@@ -6455,11 +6205,10 @@
       <c r="X3" t="n">
         <v>-9757.482711696241</v>
       </c>
-      <c r="Y3" t="n">
-        <v>466.0123437508557</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>192729227.9384485</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>4.691099528880948e-07</v>
@@ -6476,7 +6225,7 @@
         <v>125.73</v>
       </c>
       <c r="C4" t="n">
-        <v>806.2914689555191</v>
+        <v>303.6672467292017</v>
       </c>
       <c r="D4" t="n">
         <v>2.70856e-07</v>
@@ -6509,16 +6258,13 @@
         <v>-11495.01299186346</v>
       </c>
       <c r="Y4" t="n">
-        <v>460.2784191496814</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>44358802.97051834</v>
+        <v>206.8228075044588</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.316267546161293e-07</v>
+        <v>3.958887198245995e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9287083495419479</v>
+        <v>0.9504822808471655</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6275,7 @@
         <v>119.708</v>
       </c>
       <c r="C5" t="n">
-        <v>763.4661919803003</v>
+        <v>295.2126049429235</v>
       </c>
       <c r="D5" t="n">
         <v>2.67791e-07</v>
@@ -6562,16 +6308,13 @@
         <v>-11767.16723840775</v>
       </c>
       <c r="Y5" t="n">
-        <v>456.0211804082514</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>250219409.6483359</v>
+        <v>209.390953459062</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.115220061307796e-07</v>
+        <v>3.860321707873968e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9341833414340105</v>
+        <v>0.9543519869792322</v>
       </c>
     </row>
     <row r="6">
@@ -6582,7 +6325,7 @@
         <v>115.502</v>
       </c>
       <c r="C6" t="n">
-        <v>745.2124390752806</v>
+        <v>295.100682258092</v>
       </c>
       <c r="D6" t="n">
         <v>2.65727e-07</v>
@@ -6615,16 +6358,13 @@
         <v>-12059.02033481012</v>
       </c>
       <c r="Y6" t="n">
-        <v>451.9243178839052</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>186168449.9489576</v>
+        <v>204.0373278915327</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.980248030971606e-07</v>
+        <v>3.692156408395705e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9380505623270022</v>
+        <v>0.9562586617043815</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6375,7 @@
         <v>113.607</v>
       </c>
       <c r="C7" t="n">
-        <v>770.4450543658349</v>
+        <v>312.8180322101638</v>
       </c>
       <c r="D7" t="n">
         <v>2.6437e-07</v>
@@ -6668,16 +6408,13 @@
         <v>-12896.8185038987</v>
       </c>
       <c r="Y7" t="n">
-        <v>447.9321091230277</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>429146801.0924662</v>
+        <v>181.3193816091841</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.885643224081772e-07</v>
+        <v>3.483778102904631e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9409127731355369</v>
+        <v>0.9514639533681155</v>
       </c>
     </row>
     <row r="8">
@@ -6688,7 +6425,7 @@
         <v>109.807</v>
       </c>
       <c r="C8" t="n">
-        <v>734.6883358508969</v>
+        <v>291.0471687798623</v>
       </c>
       <c r="D8" t="n">
         <v>2.63508e-07</v>
@@ -6721,16 +6458,13 @@
         <v>-12594.82157947218</v>
       </c>
       <c r="Y8" t="n">
-        <v>426.8191531617577</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3653.478883969704</v>
+        <v>197.8100945929579</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.592105281647223e-06</v>
+        <v>3.426766744965216e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8352073689632808</v>
+        <v>0.9611087240941616</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6475,7 @@
         <v>108.085</v>
       </c>
       <c r="C9" t="n">
-        <v>756.1621713841814</v>
+        <v>285.943053303367</v>
       </c>
       <c r="D9" t="n">
         <v>2.62824e-07</v>
@@ -6774,16 +6508,13 @@
         <v>-13132.41584036204</v>
       </c>
       <c r="Y9" t="n">
-        <v>425.4320827613182</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>7300.385852477982</v>
+        <v>199.4622555328555</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.677177381748076e-07</v>
+        <v>3.497871789067068e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9999740495977159</v>
+        <v>0.9625626004764691</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6525,7 @@
         <v>105.667</v>
       </c>
       <c r="C10" t="n">
-        <v>730.9984949561509</v>
+        <v>105.667</v>
       </c>
       <c r="D10" t="n">
         <v>2.62254e-07</v>
@@ -6826,11 +6557,10 @@
       <c r="X10" t="n">
         <v>-13021.20211902497</v>
       </c>
-      <c r="Y10" t="n">
-        <v>437.235899553066</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>478305514.0727226</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>3.722280096243427e-07</v>
@@ -6847,7 +6577,7 @@
         <v>103.9400000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>745.957724417341</v>
+        <v>103.9400000000001</v>
       </c>
       <c r="D11" t="n">
         <v>2.61677e-07</v>
@@ -6879,11 +6609,10 @@
       <c r="X11" t="n">
         <v>-13407.73164438409</v>
       </c>
-      <c r="Y11" t="n">
-        <v>434.0356234338695</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>387057710.379193</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>3.673077680427291e-07</v>
@@ -6900,7 +6629,7 @@
         <v>103.677</v>
       </c>
       <c r="C12" t="n">
-        <v>766.1396859840642</v>
+        <v>310.4390590533075</v>
       </c>
       <c r="D12" t="n">
         <v>2.61527e-07</v>
@@ -6933,16 +6662,13 @@
         <v>-13924.8385968852</v>
       </c>
       <c r="Y12" t="n">
-        <v>430.8922112294288</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>236154793.0845484</v>
+        <v>163.7528379572183</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.646095659671054e-07</v>
+        <v>3.096589140942915e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9489188871614367</v>
+        <v>0.9603429792373926</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6679,7 @@
         <v>100.934</v>
       </c>
       <c r="C13" t="n">
-        <v>758.7793659643439</v>
+        <v>100.934</v>
       </c>
       <c r="D13" t="n">
         <v>2.61226e-07</v>
@@ -6985,11 +6711,10 @@
       <c r="X13" t="n">
         <v>-13762.51679414403</v>
       </c>
-      <c r="Y13" t="n">
-        <v>427.6949893090637</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>352754192.0720581</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>3.618877796593501e-07</v>
@@ -7006,7 +6731,7 @@
         <v>100.679</v>
       </c>
       <c r="C14" t="n">
-        <v>758.4943021006861</v>
+        <v>293.2782263983309</v>
       </c>
       <c r="D14" t="n">
         <v>2.60879e-07</v>
@@ -7039,16 +6764,13 @@
         <v>-14255.21617138809</v>
       </c>
       <c r="Y14" t="n">
-        <v>424.533169671479</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>290117497.2340956</v>
+        <v>173.4652602369784</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.593102726972235e-07</v>
+        <v>3.08405111674119e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.950780547666497</v>
+        <v>0.9670371862945492</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6781,7 @@
         <v>98.35199999999998</v>
       </c>
       <c r="C15" t="n">
-        <v>766.1113510396697</v>
+        <v>98.35199999999998</v>
       </c>
       <c r="D15" t="n">
         <v>2.60783e-07</v>
@@ -7091,11 +6813,10 @@
       <c r="X15" t="n">
         <v>-14262.61079368881</v>
       </c>
-      <c r="Y15" t="n">
-        <v>420.9721895559343</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>345012531.730469</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>3.561030430931987e-07</v>
@@ -7112,7 +6833,7 @@
         <v>96.30099999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>768.4236135829952</v>
+        <v>96.30099999999999</v>
       </c>
       <c r="D16" t="n">
         <v>2.60631e-07</v>
@@ -7144,11 +6865,10 @@
       <c r="X16" t="n">
         <v>-14416.03887302562</v>
       </c>
-      <c r="Y16" t="n">
-        <v>417.5882387120285</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>118373990.5439707</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>3.539173651349342e-07</v>
@@ -7165,7 +6885,7 @@
         <v>94.339</v>
       </c>
       <c r="C17" t="n">
-        <v>758.3943132545231</v>
+        <v>94.339</v>
       </c>
       <c r="D17" t="n">
         <v>2.60393e-07</v>
@@ -7197,11 +6917,10 @@
       <c r="X17" t="n">
         <v>-13952.92705948735</v>
       </c>
-      <c r="Y17" t="n">
-        <v>414.5571719338185</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>453135520.0351815</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>3.514813113505032e-07</v>
@@ -7218,7 +6937,7 @@
         <v>91.86200000000002</v>
       </c>
       <c r="C18" t="n">
-        <v>730.0169999953633</v>
+        <v>270.7266092890143</v>
       </c>
       <c r="D18" t="n">
         <v>2.60207e-07</v>
@@ -7251,16 +6970,13 @@
         <v>-13660.22456612663</v>
       </c>
       <c r="Y18" t="n">
-        <v>411.5259476161896</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>168743346.0635722</v>
+        <v>179.2835335901659</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.493103631632429e-07</v>
+        <v>2.886223856552106e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9546866090518605</v>
+        <v>0.9771375396193712</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +6987,7 @@
         <v>91.96699999999998</v>
       </c>
       <c r="C19" t="n">
-        <v>769.0072880343744</v>
+        <v>91.96699999999998</v>
       </c>
       <c r="D19" t="n">
         <v>2.6022e-07</v>
@@ -7303,11 +7019,10 @@
       <c r="X19" t="n">
         <v>-14606.62462238206</v>
       </c>
-      <c r="Y19" t="n">
-        <v>408.5105256298336</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>334777631.6739607</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>3.476259962158232e-07</v>
@@ -7324,7 +7039,7 @@
         <v>88.40000000000003</v>
       </c>
       <c r="C20" t="n">
-        <v>714.4206272791724</v>
+        <v>88.40000000000003</v>
       </c>
       <c r="D20" t="n">
         <v>2.60188e-07</v>
@@ -7356,11 +7071,10 @@
       <c r="X20" t="n">
         <v>-13508.93400573216</v>
       </c>
-      <c r="Y20" t="n">
-        <v>405.4855688446784</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>221692713.7646232</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>3.45904275648366e-07</v>
@@ -7377,7 +7091,7 @@
         <v>87.82999999999998</v>
       </c>
       <c r="C21" t="n">
-        <v>745.020882085448</v>
+        <v>266.6284044352167</v>
       </c>
       <c r="D21" t="n">
         <v>2.59964e-07</v>
@@ -7410,16 +7124,13 @@
         <v>-13874.02972793589</v>
       </c>
       <c r="Y21" t="n">
-        <v>402.5010659986688</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>331821560.834577</v>
+        <v>174.2202227471122</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.442378256849942e-07</v>
+        <v>2.800393386691166e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9567788086081715</v>
+        <v>0.9826751730258209</v>
       </c>
     </row>
     <row r="22">
@@ -7430,7 +7141,7 @@
         <v>86.04000000000002</v>
       </c>
       <c r="C22" t="n">
-        <v>727.0434734155206</v>
+        <v>245.7064597142962</v>
       </c>
       <c r="D22" t="n">
         <v>2.60098e-07</v>
@@ -7463,16 +7174,13 @@
         <v>-13663.81967361734</v>
       </c>
       <c r="Y22" t="n">
-        <v>399.5148303094026</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>436922180.5574364</v>
+        <v>190.2397370319769</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.422039977735035e-07</v>
+        <v>2.805291330907906e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9577455068094651</v>
+        <v>0.990866512814892</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7337,7 @@
         <v>147.4259999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>5342.922156756319</v>
+        <v>331.6494925038148</v>
       </c>
       <c r="D2" t="n">
         <v>2.92483e-07</v>
@@ -7662,16 +7370,13 @@
         <v>-5134.761399588653</v>
       </c>
       <c r="Y2" t="n">
-        <v>447.2608542610588</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>360712415.1757494</v>
+        <v>157.6508476808662</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.787841699857573e-07</v>
+        <v>2.1190560620034e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.872894448800701</v>
+        <v>0.9719902516259846</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7387,7 @@
         <v>100.088</v>
       </c>
       <c r="C3" t="n">
-        <v>970.8397076339409</v>
+        <v>263.6849982581309</v>
       </c>
       <c r="D3" t="n">
         <v>2.88417e-07</v>
@@ -7715,16 +7420,13 @@
         <v>-6697.681925217379</v>
       </c>
       <c r="Y3" t="n">
-        <v>400.1974333256916</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3457.066656048483</v>
+        <v>197.7441083231239</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.49665477798724e-06</v>
+        <v>3.102480777499167e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8486630098005334</v>
+        <v>0.9761892394027186</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7437,7 @@
         <v>92.08699999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>856.557096609115</v>
+        <v>251.3614447711928</v>
       </c>
       <c r="D4" t="n">
         <v>2.8179e-07</v>
@@ -7768,16 +7470,13 @@
         <v>-8090.892774284126</v>
       </c>
       <c r="Y4" t="n">
-        <v>412.4612535545218</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>175598348.1537231</v>
+        <v>200.3334084090336</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.487309756219125e-07</v>
+        <v>3.171816326608181e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9291018201345514</v>
+        <v>0.9780913028495957</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7487,7 @@
         <v>86.22900000000004</v>
       </c>
       <c r="C5" t="n">
-        <v>791.5740628060598</v>
+        <v>257.4491480452668</v>
       </c>
       <c r="D5" t="n">
         <v>2.76729e-07</v>
@@ -7821,16 +7520,13 @@
         <v>-8829.035159041612</v>
       </c>
       <c r="Y5" t="n">
-        <v>407.3470578961657</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>111318800.5883842</v>
+        <v>188.2891606022847</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.182032860857763e-07</v>
+        <v>2.956339042893424e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9369465305917135</v>
+        <v>0.9814525934552345</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7537,7 @@
         <v>83.91899999999998</v>
       </c>
       <c r="C6" t="n">
-        <v>822.127028168791</v>
+        <v>247.0635625539697</v>
       </c>
       <c r="D6" t="n">
         <v>2.73217e-07</v>
@@ -7874,16 +7570,13 @@
         <v>-9770.280128072411</v>
       </c>
       <c r="Y6" t="n">
-        <v>402.3688986980127</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>329501850.603974</v>
+        <v>191.8970862365161</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.9729317622861e-07</v>
+        <v>2.835607865582683e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9427244016307051</v>
+        <v>0.9881065728778805</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7587,7 @@
         <v>80.80300000000005</v>
       </c>
       <c r="C7" t="n">
-        <v>837.0553962204218</v>
+        <v>242.0969695687142</v>
       </c>
       <c r="D7" t="n">
         <v>2.70654e-07</v>
@@ -7927,16 +7620,13 @@
         <v>-10307.51734490165</v>
       </c>
       <c r="Y7" t="n">
-        <v>397.415658651056</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>218840704.1563608</v>
+        <v>191.4323762590205</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.836214915534863e-07</v>
+        <v>2.770899905408413e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9465849246484479</v>
+        <v>0.9921422967557744</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7637,7 @@
         <v>77.88200000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>808.2339817889705</v>
+        <v>237.2601817454584</v>
       </c>
       <c r="D8" t="n">
         <v>2.68647e-07</v>
@@ -7980,16 +7670,13 @@
         <v>-10652.90482962498</v>
       </c>
       <c r="Y8" t="n">
-        <v>392.7104613324146</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>107181455.5656053</v>
+        <v>190.4317322799241</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.731376418170977e-07</v>
+        <v>2.691974455929202e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9496478548149111</v>
+        <v>0.995453330208687</v>
       </c>
     </row>
     <row r="9">
@@ -8000,7 +7687,7 @@
         <v>75.80199999999996</v>
       </c>
       <c r="C9" t="n">
-        <v>809.3465693700382</v>
+        <v>234.9179041483194</v>
       </c>
       <c r="D9" t="n">
         <v>2.6731e-07</v>
@@ -8033,16 +7720,13 @@
         <v>-11149.28377621135</v>
       </c>
       <c r="Y9" t="n">
-        <v>388.4101290095276</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>158973472.4001223</v>
+        <v>188.7756452683986</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.65152339941978e-07</v>
+        <v>2.731526496538042e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9521606934071773</v>
+        <v>0.9958183825932944</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7737,7 @@
         <v>73.09899999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>835.6500622061048</v>
+        <v>242.3001621382172</v>
       </c>
       <c r="D10" t="n">
         <v>2.66119e-07</v>
@@ -8086,16 +7770,13 @@
         <v>-11274.80434193135</v>
       </c>
       <c r="Y10" t="n">
-        <v>384.4091790697254</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>628613980.98006</v>
+        <v>176.9482499838314</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.598723325225615e-07</v>
+        <v>2.533114000046016e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9537048599395087</v>
+        <v>0.9978425045443563</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7787,7 @@
         <v>72.19800000000004</v>
       </c>
       <c r="C11" t="n">
-        <v>817.6381060496526</v>
+        <v>302.6581854831005</v>
       </c>
       <c r="D11" t="n">
         <v>2.65386e-07</v>
@@ -8139,16 +7820,13 @@
         <v>-11794.19885323564</v>
       </c>
       <c r="Y11" t="n">
-        <v>380.3166287316536</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>207343975.1091103</v>
+        <v>116.2092459431736</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.539633503169021e-07</v>
+        <v>3.4939542542288e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9557811164962613</v>
+        <v>0.9434525875841969</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +7983,7 @@
         <v>151.935</v>
       </c>
       <c r="C2" t="n">
-        <v>1075.218365368932</v>
+        <v>151.935</v>
       </c>
       <c r="D2" t="n">
         <v>2.72978e-07</v>
@@ -8337,11 +8015,10 @@
       <c r="X2" t="n">
         <v>-9647.422723588208</v>
       </c>
-      <c r="Y2" t="n">
-        <v>476.5721033888777</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>32616356.86377891</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>4.840721463029202e-07</v>
@@ -8358,7 +8035,7 @@
         <v>128.668</v>
       </c>
       <c r="C3" t="n">
-        <v>800.3699388318648</v>
+        <v>305.4749047933711</v>
       </c>
       <c r="D3" t="n">
         <v>2.6855e-07</v>
@@ -8391,16 +8068,13 @@
         <v>-11709.43650743262</v>
       </c>
       <c r="Y3" t="n">
-        <v>462.5869755842085</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>26239456.73372998</v>
+        <v>206.0744254290606</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.217473612483152e-07</v>
+        <v>3.802220054551853e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9308786942661749</v>
+        <v>0.9516803248783304</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8085,7 @@
         <v>120.865</v>
       </c>
       <c r="C4" t="n">
-        <v>733.1775652583228</v>
+        <v>299.701761273067</v>
       </c>
       <c r="D4" t="n">
         <v>2.6613e-07</v>
@@ -8444,16 +8118,13 @@
         <v>-12376.45852350311</v>
       </c>
       <c r="Y4" t="n">
-        <v>456.9434479126721</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>188258830.4061645</v>
+        <v>205.8946676760852</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.017273873978845e-07</v>
+        <v>3.828718528054207e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9368504156747148</v>
+        <v>0.953184755079917</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8135,7 @@
         <v>118.387</v>
       </c>
       <c r="C5" t="n">
-        <v>742.6363284171247</v>
+        <v>292.1335426107776</v>
       </c>
       <c r="D5" t="n">
         <v>2.64506e-07</v>
@@ -8497,16 +8168,13 @@
         <v>-12926.94694102056</v>
       </c>
       <c r="Y5" t="n">
-        <v>452.2621544931089</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>124547803.1700962</v>
+        <v>207.2590214089588</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.908531247009425e-07</v>
+        <v>3.699036624930983e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9400894695746561</v>
+        <v>0.9574775021378484</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8185,7 @@
         <v>117.028</v>
       </c>
       <c r="C6" t="n">
-        <v>767.5239914743345</v>
+        <v>117.028</v>
       </c>
       <c r="D6" t="n">
         <v>2.63705e-07</v>
@@ -8549,11 +8217,10 @@
       <c r="X6" t="n">
         <v>-13841.23949737114</v>
       </c>
-      <c r="Y6" t="n">
-        <v>426.5961128333809</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3684.652092205249</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>1.335455556498187e-06</v>
@@ -8570,7 +8237,7 @@
         <v>111.347</v>
       </c>
       <c r="C7" t="n">
-        <v>726.0840891802217</v>
+        <v>283.8186690817873</v>
       </c>
       <c r="D7" t="n">
         <v>2.63134e-07</v>
@@ -8603,16 +8270,13 @@
         <v>-13149.56585572598</v>
       </c>
       <c r="Y7" t="n">
-        <v>422.6749463804728</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3642.189151459356</v>
+        <v>203.9901094841214</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.864454460717978e-06</v>
+        <v>3.569230200047374e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8134851209493507</v>
+        <v>0.962222727958115</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8287,7 @@
         <v>109.383</v>
       </c>
       <c r="C8" t="n">
-        <v>758.2523672785405</v>
+        <v>302.233366139802</v>
       </c>
       <c r="D8" t="n">
         <v>2.62561e-07</v>
@@ -8656,16 +8320,13 @@
         <v>-13956.66516406941</v>
       </c>
       <c r="Y8" t="n">
-        <v>438.112749893103</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>179792642.771854</v>
+        <v>180.3895061076551</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.721556559962741e-07</v>
+        <v>3.320426889420632e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9464071651728816</v>
+        <v>0.9592675712512461</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8337,7 @@
         <v>105.665</v>
       </c>
       <c r="C9" t="n">
-        <v>727.038417687603</v>
+        <v>295.6112049347632</v>
       </c>
       <c r="D9" t="n">
         <v>2.62244e-07</v>
@@ -8709,16 +8370,13 @@
         <v>-13686.82832258121</v>
       </c>
       <c r="Y9" t="n">
-        <v>434.2094682901393</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>475241279.9076642</v>
+        <v>182.0143004388395</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.673586660074046e-07</v>
+        <v>3.297043440761162e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9481880184656595</v>
+        <v>0.9606646172953563</v>
       </c>
     </row>
     <row r="10">
@@ -8729,7 +8387,7 @@
         <v>103.884</v>
       </c>
       <c r="C10" t="n">
-        <v>744.9746054166079</v>
+        <v>288.9473180817542</v>
       </c>
       <c r="D10" t="n">
         <v>2.62047e-07</v>
@@ -8762,16 +8420,13 @@
         <v>-13804.79004941218</v>
       </c>
       <c r="Y10" t="n">
-        <v>430.6504935008618</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>117791125.0711426</v>
+        <v>185.4555430762468</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.643612089453659e-07</v>
+        <v>3.288745724137648e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9493289101683569</v>
+        <v>0.9658722834963556</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8437,7 @@
         <v>100.768</v>
       </c>
       <c r="C11" t="n">
-        <v>726.1026812956326</v>
+        <v>286.8144661390343</v>
       </c>
       <c r="D11" t="n">
         <v>2.61863e-07</v>
@@ -8815,16 +8470,13 @@
         <v>-13755.97854030204</v>
       </c>
       <c r="Y11" t="n">
-        <v>427.2898349614363</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>175414089.0588971</v>
+        <v>181.9219616503166</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.617815616241259e-07</v>
+        <v>3.166885635907712e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9503068576419258</v>
+        <v>0.9672035066713476</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8487,7 @@
         <v>99.03199999999998</v>
       </c>
       <c r="C12" t="n">
-        <v>725.1250434507513</v>
+        <v>275.9076493602461</v>
       </c>
       <c r="D12" t="n">
         <v>2.6172e-07</v>
@@ -8868,16 +8520,13 @@
         <v>-13843.93283311992</v>
       </c>
       <c r="Y12" t="n">
-        <v>424.2052365218456</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>174333779.1887518</v>
+        <v>189.486257995698</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.58150876896356e-07</v>
+        <v>3.194154365585028e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9517458764680145</v>
+        <v>0.9696990182532238</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8537,7 @@
         <v>99.37199999999996</v>
       </c>
       <c r="C13" t="n">
-        <v>752.2194303387037</v>
+        <v>322.0587448997073</v>
       </c>
       <c r="D13" t="n">
         <v>2.61548e-07</v>
@@ -8921,16 +8570,13 @@
         <v>-14493.37747334547</v>
       </c>
       <c r="Y13" t="n">
-        <v>421.1424903195542</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>172944089.5054938</v>
+        <v>139.8990539543249</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.569231144901565e-07</v>
+        <v>2.911097099618625e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9521874686474737</v>
+        <v>0.9571464011441985</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8587,7 @@
         <v>96.66500000000002</v>
       </c>
       <c r="C14" t="n">
-        <v>749.4604500450446</v>
+        <v>96.66500000000002</v>
       </c>
       <c r="D14" t="n">
         <v>2.61366e-07</v>
@@ -8973,11 +8619,10 @@
       <c r="X14" t="n">
         <v>-14382.64092711181</v>
       </c>
-      <c r="Y14" t="n">
-        <v>418.1995125728263</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>114458354.7393551</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>3.542281346934422e-07</v>
@@ -8994,7 +8639,7 @@
         <v>93.41800000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>705.6330908268736</v>
+        <v>270.0765336966751</v>
       </c>
       <c r="D15" t="n">
         <v>2.61342e-07</v>
@@ -9027,16 +8672,13 @@
         <v>-13528.19225082068</v>
       </c>
       <c r="Y15" t="n">
-        <v>415.2940601923247</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>113880481.0897932</v>
+        <v>185.3707152838704</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.527569266650081e-07</v>
+        <v>3.077228066504854e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.953851472500422</v>
+        <v>0.9754443469266113</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8689,7 @@
         <v>95.50299999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>790.1110086801538</v>
+        <v>266.9097895182252</v>
       </c>
       <c r="D16" t="n">
         <v>2.61245e-07</v>
@@ -9080,16 +8722,13 @@
         <v>-15366.03192059773</v>
       </c>
       <c r="Y16" t="n">
-        <v>412.4653666218679</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>170016055.2832703</v>
+        <v>184.6582718304708</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.508072820551902e-07</v>
+        <v>3.028548572693173e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.954636768680206</v>
+        <v>0.9774621306323007</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8739,7 @@
         <v>93.28700000000003</v>
       </c>
       <c r="C17" t="n">
-        <v>743.471555208539</v>
+        <v>314.6851323848542</v>
       </c>
       <c r="D17" t="n">
         <v>2.61202e-07</v>
@@ -9133,16 +8772,13 @@
         <v>-14747.40100343068</v>
       </c>
       <c r="Y17" t="n">
-        <v>409.6914866273248</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>223941085.9405902</v>
+        <v>134.1794923037629</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.489212786123147e-07</v>
+        <v>2.726298041975357e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.955429408991967</v>
+        <v>0.9636861098518151</v>
       </c>
     </row>
     <row r="18">
@@ -9153,7 +8789,7 @@
         <v>92.59300000000002</v>
       </c>
       <c r="C18" t="n">
-        <v>752.270313649955</v>
+        <v>313.6616824325292</v>
       </c>
       <c r="D18" t="n">
         <v>2.61212e-07</v>
@@ -9186,16 +8822,13 @@
         <v>-14718.15831226745</v>
       </c>
       <c r="Y18" t="n">
-        <v>406.9016518111838</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>445599249.1035966</v>
+        <v>132.0162645957237</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.472231600958838e-07</v>
+        <v>2.683660028378087e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9561750058948451</v>
+        <v>0.9643469895267894</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8839,7 @@
         <v>90.75699999999995</v>
       </c>
       <c r="C19" t="n">
-        <v>748.0573938704252</v>
+        <v>90.75699999999995</v>
       </c>
       <c r="D19" t="n">
         <v>2.61205e-07</v>
@@ -9238,11 +8871,10 @@
       <c r="X19" t="n">
         <v>-14929.60479392341</v>
       </c>
-      <c r="Y19" t="n">
-        <v>404.0651842629732</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>661839284.8314869</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>3.453166066346132e-07</v>
@@ -9259,7 +8891,7 @@
         <v>89.47899999999998</v>
       </c>
       <c r="C20" t="n">
-        <v>757.4092679406039</v>
+        <v>89.47899999999998</v>
       </c>
       <c r="D20" t="n">
         <v>2.60874e-07</v>
@@ -9291,11 +8923,10 @@
       <c r="X20" t="n">
         <v>-14975.82267919341</v>
       </c>
-      <c r="Y20" t="n">
-        <v>401.2731753297563</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>109954655.0377423</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>3.439855398064399e-07</v>
@@ -9312,7 +8943,7 @@
         <v>86.88099999999997</v>
       </c>
       <c r="C21" t="n">
-        <v>734.4330713570612</v>
+        <v>278.6406609917376</v>
       </c>
       <c r="D21" t="n">
         <v>2.61001e-07</v>
@@ -9345,16 +8976,13 @@
         <v>-14283.62846338707</v>
       </c>
       <c r="Y21" t="n">
-        <v>398.4425835561854</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>109012463.3348543</v>
+        <v>156.7075704507924</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.426062937967993e-07</v>
+        <v>2.703965030190399e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9580991501604325</v>
+        <v>0.9764483984864412</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +8993,7 @@
         <v>85.89600000000002</v>
       </c>
       <c r="C22" t="n">
-        <v>736.2240680977075</v>
+        <v>244.5958680784024</v>
       </c>
       <c r="D22" t="n">
         <v>2.60994e-07</v>
@@ -9398,16 +9026,13 @@
         <v>-14444.86047287876</v>
       </c>
       <c r="Y22" t="n">
-        <v>395.5741458391194</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>216197133.3926557</v>
+        <v>188.0131557241154</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.420991244525461e-07</v>
+        <v>2.842372516899024e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9583389134329636</v>
+        <v>0.9910300562386715</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9189,7 @@
         <v>109.144</v>
       </c>
       <c r="C2" t="n">
-        <v>2386.675364230263</v>
+        <v>258.6021232568511</v>
       </c>
       <c r="D2" t="n">
         <v>2.834e-07</v>
@@ -9597,16 +9222,13 @@
         <v>-5813.034705871516</v>
       </c>
       <c r="Y2" t="n">
-        <v>413.3995528377526</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>225684152.6048389</v>
+        <v>192.6214760913499</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.241173545103358e-07</v>
+        <v>2.353009419617842e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9067081040977826</v>
+        <v>0.9946098306492175</v>
       </c>
     </row>
     <row r="3">
@@ -9617,7 +9239,7 @@
         <v>89.58800000000002</v>
       </c>
       <c r="C3" t="n">
-        <v>1328.558266342234</v>
+        <v>281.1010652388206</v>
       </c>
       <c r="D3" t="n">
         <v>2.73136e-07</v>
@@ -9650,16 +9272,13 @@
         <v>-8647.872406315368</v>
       </c>
       <c r="Y3" t="n">
-        <v>397.8529853889657</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>112885517.5216535</v>
+        <v>153.8834322764548</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.160469132995124e-07</v>
+        <v>2.496768940618397e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9357369062570795</v>
+        <v>0.9809164857420077</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9289,7 @@
         <v>81.76600000000002</v>
       </c>
       <c r="C4" t="n">
-        <v>995.6471073911562</v>
+        <v>327.5031801536978</v>
       </c>
       <c r="D4" t="n">
         <v>2.683e-07</v>
@@ -9703,16 +9322,13 @@
         <v>-9808.825267630049</v>
       </c>
       <c r="Y4" t="n">
-        <v>391.3386659647608</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>108290984.225836</v>
+        <v>99.44531229572154</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.837920383609075e-07</v>
+        <v>2.186531133588345e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9451749698400085</v>
+        <v>0.9696332461099255</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9339,7 @@
         <v>78.61800000000005</v>
       </c>
       <c r="C5" t="n">
-        <v>1053.265476699659</v>
+        <v>314.8463096054972</v>
       </c>
       <c r="D5" t="n">
         <v>2.65526e-07</v>
@@ -9756,16 +9372,13 @@
         <v>-10553.44763209426</v>
       </c>
       <c r="Y5" t="n">
-        <v>386.3690046309804</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>157949997.6588617</v>
+        <v>105.2710088859292</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.688402224524403e-07</v>
+        <v>2.091372980525757e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9496075244343175</v>
+        <v>0.9749053031655608</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9389,7 @@
         <v>74.786</v>
       </c>
       <c r="C6" t="n">
-        <v>972.5608252219367</v>
+        <v>298.0656925855728</v>
       </c>
       <c r="D6" t="n">
         <v>2.63917e-07</v>
@@ -9809,16 +9422,13 @@
         <v>-10847.43029960969</v>
       </c>
       <c r="Y6" t="n">
-        <v>381.3808015938022</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>518900397.9970644</v>
+        <v>116.4295867170543</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.580863380424837e-07</v>
+        <v>2.094650626760719e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9531556670278618</v>
+        <v>0.9830453447708324</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9439,7 @@
         <v>71.185</v>
       </c>
       <c r="C7" t="n">
-        <v>1005.947245365639</v>
+        <v>305.6654586744285</v>
       </c>
       <c r="D7" t="n">
         <v>2.62756e-07</v>
@@ -9862,16 +9472,13 @@
         <v>-10925.45541698337</v>
       </c>
       <c r="Y7" t="n">
-        <v>376.3327505729329</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>205146431.2838763</v>
+        <v>102.3650099342863</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.515607192078831e-07</v>
+        <v>1.946921503761123e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9552877675534639</v>
+        <v>0.9825486264573114</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9489,7 @@
         <v>70.31399999999996</v>
       </c>
       <c r="C8" t="n">
-        <v>1190.784595482574</v>
+        <v>314.4112661345652</v>
       </c>
       <c r="D8" t="n">
         <v>2.62081e-07</v>
@@ -9915,16 +9522,13 @@
         <v>-11732.96445154462</v>
       </c>
       <c r="Y8" t="n">
-        <v>371.3978966041586</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>101185515.6043342</v>
+        <v>87.96854310862422</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.451356492579932e-07</v>
+        <v>1.858683185567618e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9576837039638305</v>
+        <v>0.9825633593288128</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9539,7 @@
         <v>67.03799999999995</v>
       </c>
       <c r="C9" t="n">
-        <v>1053.185439353647</v>
+        <v>301.6850162769252</v>
       </c>
       <c r="D9" t="n">
         <v>2.61662e-07</v>
@@ -9968,16 +9572,13 @@
         <v>-11509.33134619516</v>
       </c>
       <c r="Y9" t="n">
-        <v>366.7219718483795</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>398717668.0373393</v>
+        <v>95.67599106847047</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.414772267556041e-07</v>
+        <v>1.851605691463141e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9590654145840383</v>
+        <v>0.9879635978066577</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9589,7 @@
         <v>59.34199999999998</v>
       </c>
       <c r="C10" t="n">
-        <v>777.9372346278989</v>
+        <v>59.34199999999998</v>
       </c>
       <c r="D10" t="n">
         <v>2.61241e-07</v>
@@ -10020,11 +9621,10 @@
       <c r="X10" t="n">
         <v>-9790.787598396972</v>
       </c>
-      <c r="Y10" t="n">
-        <v>362.3537054803389</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>197025356.9286698</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>3.378478295031829e-07</v>
@@ -10041,7 +9641,7 @@
         <v>62.63499999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>1140.851635996534</v>
+        <v>276.2426265828398</v>
       </c>
       <c r="D11" t="n">
         <v>2.6101e-07</v>
@@ -10074,16 +9674,13 @@
         <v>-11700.28864134019</v>
       </c>
       <c r="Y11" t="n">
-        <v>358.2962929249304</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>97464261.31029435</v>
+        <v>111.8680093784897</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.351133738062318e-07</v>
+        <v>1.867888620047778e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9615519162759297</v>
+        <v>0.9974362634868575</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 32.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>1.234273032482909e-06</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8431218361672124</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>149.777</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>873.2433125811762</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.55167e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-83.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.02468063230052142</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7223507722953233</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.725813518465618</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.027474133888236</v>
+      </c>
+      <c r="L12" t="n">
+        <v>36.66260068243022</v>
+      </c>
+      <c r="M12" t="n">
+        <v>87.39461527861948</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>21.97613367545502</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-12302.18729375609</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-270.682412308426</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.107426050646521e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9269404206140992</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>143.134</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9556473957950818</v>
+      </c>
+      <c r="D13" t="n">
+        <v>792.9353525945221</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9080348411151575</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.53626e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.389</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3367499908956064</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.057839843674871</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.803518104362572</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.921904618626211</v>
+      </c>
+      <c r="L13" t="n">
+        <v>42.04387526295907</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.67246975244326</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>24.60301384559166</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-13530.06999235967</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-213.6910748520646</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.915264688983131e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9332769936041232</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>138.388</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9239602876276067</v>
+      </c>
+      <c r="D14" t="n">
+        <v>956.6925888875484</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.095562456767872</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.52538e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-83.628</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3097648922637231</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.194038854019889</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.90349027458267</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.328278826145074</v>
+      </c>
+      <c r="L14" t="n">
+        <v>47.79082171941959</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.80919344445904</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>26.14007773126362</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-14158.24750389202</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-362.6662429662517</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.800388687384269e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9371488906703588</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>133.665</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8924267410884184</v>
+      </c>
+      <c r="D15" t="n">
+        <v>805.7300805840069</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9226868032947081</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.52018e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.79000000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6123541264162851</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9724603340802042</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.90186867911259</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.21257689290987</v>
+      </c>
+      <c r="L15" t="n">
+        <v>50.94373413765487</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.88978892630244</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>27.1394039362598</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-14484.73554295575</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-241.1068635713561</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.725087214834107e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9398869957070792</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>128.212</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8560192819992393</v>
+      </c>
+      <c r="D16" t="n">
+        <v>776.0171905653348</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.888660902849109</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.51621e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.97199999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4059792016327246</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.205815406964122</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.853119470156728</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.41470305982541</v>
+      </c>
+      <c r="L16" t="n">
+        <v>57.59334697904124</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.89963115757922</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>27.26669273675385</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-14312.64573083237</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-222.7360984838306</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.650324725381416e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9427200774762674</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>121.961</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8142839020677408</v>
+      </c>
+      <c r="D17" t="n">
+        <v>753.4678369178959</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8628383705461861</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.51403e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-84.12</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1433735274142708</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.6890121806129709</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.755624509043857</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.140119830424565</v>
+      </c>
+      <c r="L17" t="n">
+        <v>60.26977227127002</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.84186301966545</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>26.53616564366855</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-13685.16593608196</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-210.2973891302182</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.593354466531468e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9449788471280697</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>120.783</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8064188760624126</v>
+      </c>
+      <c r="D18" t="n">
+        <v>791.0096439157957</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.90582960386801</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.50996e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-84.19499999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4770907877110659</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.142038105334138</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.941412193906207</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.445039549368193</v>
+      </c>
+      <c r="L18" t="n">
+        <v>62.49756038549588</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.98768526015695</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>28.46086545289152</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-14541.54287731682</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-249.2461916952902</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.552398619253264e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.946501646498408</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>115.751</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7728222624301464</v>
+      </c>
+      <c r="D19" t="n">
+        <v>769.40769604789</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8810919991744756</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.50784e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.295</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8641654975803801</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.681925911534731</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.881182622210962</v>
+      </c>
+      <c r="L19" t="n">
+        <v>57.15136736746962</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.94828864672735</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>27.91391066599932</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-14048.10619405686</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-236.6539705122606</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.563779375131226e-06</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8250916320786401</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>114.622</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7652843894589955</v>
+      </c>
+      <c r="D20" t="n">
+        <v>807.6698229311627</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9249081112843703</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.50683e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.428</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5405883252969977</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.289522063031289</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.20111458711104</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.906911906355747</v>
+      </c>
+      <c r="L20" t="n">
+        <v>63.75158425048162</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.10017472847596</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>30.14739332413253</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-15050.77117242096</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-275.4832038925495</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.368033539037081e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9927233101423436</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>110.539</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7380238621417173</v>
+      </c>
+      <c r="D21" t="n">
+        <v>780.3407328488936</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8936120341332171</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.50499e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.474</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4443479644157224</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8819333715118952</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.972205003780633</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.27090028106383</v>
+      </c>
+      <c r="L21" t="n">
+        <v>66.112977970831</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.06272806623817</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>29.56422516144653</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-14576.0684310631</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-257.0804476489589</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.234273032482909e-06</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8431218361672124</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>3.339554145431989e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9604898051126254</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>143.8410000000001</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1046.589317843959</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.63713e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-82.971</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2446673036181181</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9152593731966566</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.475728564664138</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.58350096019537</v>
+      </c>
+      <c r="L23" t="n">
+        <v>35.13377296319581</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.3183707240958</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>21.35042960103915</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-11554.18489641194</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-432.7549614021689</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.22327079787798e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9278647255626057</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>124.12</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8628972267990347</v>
+      </c>
+      <c r="D24" t="n">
+        <v>805.209208966378</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7693650176223472</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.61359e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-83.666</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1174394053856148</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9804948457484631</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.895710746432112</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.223661102628612</v>
+      </c>
+      <c r="L24" t="n">
+        <v>48.28188471900242</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.7168858655324</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>25.08216724749043</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-12928.23248599209</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-256.5186879856529</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.876169113099555e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9394832776535654</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>116.746</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8116322884295849</v>
+      </c>
+      <c r="D25" t="n">
+        <v>759.6011448599658</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7257872136749806</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.60231e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.902</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3945249287516861</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.039703151077775</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.922289695772817</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.941161553738549</v>
+      </c>
+      <c r="L25" t="n">
+        <v>49.39825433605395</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.79074755562127</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>25.92161050751799</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-13112.04858847742</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-226.0486160934728</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.762666515441864e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9433403338041504</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>114.907</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7988473383805725</v>
+      </c>
+      <c r="D26" t="n">
+        <v>750.3234709292261</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7169225388951421</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.59858e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.02800000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2983369746051242</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.166156916020517</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.906211810464645</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.133035221180742</v>
+      </c>
+      <c r="L26" t="n">
+        <v>55.80784175569714</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.89770132987779</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>27.24164053426838</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-13642.24631611201</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-222.9663116835281</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7.572356582753557e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9195694953957788</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>111.023</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7718453014091947</v>
+      </c>
+      <c r="D27" t="n">
+        <v>737.1169646655522</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7043039252340739</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.5934e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-84.15600000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1619565725179314</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8900578908555352</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.963002120522948</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.227892630644385</v>
+      </c>
+      <c r="L27" t="n">
+        <v>59.04705274341686</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.87090305260176</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>26.89844862017729</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-13286.15777740048</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-217.0346481171204</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.490054047196679e-06</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8208465766555824</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>108.629</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7552019243470215</v>
+      </c>
+      <c r="D28" t="n">
+        <v>305.4345744791619</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.2918380393069333</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.59097e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.205</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3174274232300977</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.119284581662237</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.157532684433602</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.12627003593697</v>
+      </c>
+      <c r="L28" t="n">
+        <v>56.87598220535168</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.95822994094442</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>28.04993831943644</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-13729.95598918011</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>172.7047557071969</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.143238013967782e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9606552751605881</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106.546</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7407206568363676</v>
+      </c>
+      <c r="D29" t="n">
+        <v>744.7988528382601</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7116438512601995</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.58949e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.322</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.29527301740742</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8608834783723007</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.832577902255167</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.005411858417313</v>
+      </c>
+      <c r="L29" t="n">
+        <v>58.35427696913376</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.9994241946994</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>28.62800450269415</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-13847.85787379509</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-233.988711399381</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.58462807520919e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9499794626816725</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>102.538</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7128565568926795</v>
+      </c>
+      <c r="D30" t="n">
+        <v>280.8968878349414</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.2683926570296045</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.58908e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.414</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1903399503790306</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.7391182737028369</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.838759607100537</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.960528352103645</v>
+      </c>
+      <c r="L30" t="n">
+        <v>58.97706243037763</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.94642311723564</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>27.88853115028803</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-13309.10489660023</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>187.4220072771888</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.116172490641323e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9716529407192351</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101.966</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7088799438268641</v>
+      </c>
+      <c r="D31" t="n">
+        <v>761.8935353043465</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7279775574949454</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.58923e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.47799999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4548434509161758</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.033216064207229</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.901622655934532</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.114587355459048</v>
+      </c>
+      <c r="L31" t="n">
+        <v>62.21877932922133</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.0763815727701</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>29.77422630497227</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-14119.92997259863</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-258.529954747756</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.531580115747654e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9522221566648701</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99.24299999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6899493190397727</v>
+      </c>
+      <c r="D32" t="n">
+        <v>267.3960381421875</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.2554928027481118</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.58747e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.50700000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4793058616906226</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9781788580511607</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.272633983505106</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.169025385319678</v>
+      </c>
+      <c r="L32" t="n">
+        <v>61.76704446443623</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.0241065231758</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>28.98590684697566</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-13594.47007781174</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>193.4405304537988</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.157738714943498e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9760965384000487</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97.50200000000001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6778456768237149</v>
+      </c>
+      <c r="D33" t="n">
+        <v>271.3880558336265</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.2593071142678039</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.58569e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.59099999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2590718093320893</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.156736815297303</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.110652735939223</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.435107798859895</v>
+      </c>
+      <c r="L33" t="n">
+        <v>68.94733370357062</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.08897335398645</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>29.97055611390621</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-13953.9877206023</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>186.1551196654945</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.055661958278647e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.976789064684941</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>96.93099999999998</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6738760158786433</v>
+      </c>
+      <c r="D34" t="n">
+        <v>760.9206476871557</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7270479783366228</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.58524e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-84.646</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.6126877421403306</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.277937536163018</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.070644721318421</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.553402897500489</v>
+      </c>
+      <c r="L34" t="n">
+        <v>70.52950130724689</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.1872777332149</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>31.59704182746031</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-14629.52137263942</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-268.7711157084852</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.46955902032398e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9547084023002697</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>95.71999999999997</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6654569976571348</v>
+      </c>
+      <c r="D35" t="n">
+        <v>760.7797714035763</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7269133732138899</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.58622e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-84.68899999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6595714692082586</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.127844055161468</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.169452792553672</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.257961343934822</v>
+      </c>
+      <c r="L35" t="n">
+        <v>66.73759723354802</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.17638969275393</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>31.40826232809791</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-14410.46686349054</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-272.1204404657573</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.457145011466897e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9553120612531133</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93.02499999999998</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6467210322508877</v>
+      </c>
+      <c r="D36" t="n">
+        <v>257.9980641867082</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.2465131831444646</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.58401e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-84.696</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.439150548159369</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.060714598872798</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.003288951588586</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.23180274514394</v>
+      </c>
+      <c r="L36" t="n">
+        <v>66.59737268294236</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.14866558434818</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>30.93759701559114</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-14057.28857993719</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>189.0250559542333</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.936031573922313e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9846162082267244</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>93.37799999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6491751308736726</v>
+      </c>
+      <c r="D37" t="n">
+        <v>799.1879309891901</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7636117791031618</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.58322e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-84.803</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.7505911752922237</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.508269154532604</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.421718148101912</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.818621091194854</v>
+      </c>
+      <c r="L37" t="n">
+        <v>77.15459975202229</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.27917396102336</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>33.28549741258575</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-15064.92912862336</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-312.5574396085764</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.418394142851484e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9568570504678677</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91.22000000000003</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6341724543071863</v>
+      </c>
+      <c r="D38" t="n">
+        <v>757.9222644037998</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7241830692149315</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.58377e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-84.82599999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.4027985990467226</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.097912256467849</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.020691678386705</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.908952317528506</v>
+      </c>
+      <c r="L38" t="n">
+        <v>66.89344000595914</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.21556661339291</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>32.09828610340357</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-14371.82169837948</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-279.5398465176459</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.410235923320787e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9572641203275785</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>88.93200000000002</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6182660020439233</v>
+      </c>
+      <c r="D39" t="n">
+        <v>308.9598771034681</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.2952064117565667</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.58486e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-84.893</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1085398713823943</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.043303564413204</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.999623576242072</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.415889358333452</v>
+      </c>
+      <c r="L39" t="n">
+        <v>74.74975790552804</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.15173826279475</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>30.98906560861343</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-13715.59214289839</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>127.0049538695433</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.505226057598872e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9689130430171595</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>87.98099999999999</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6116545352159674</v>
+      </c>
+      <c r="D40" t="n">
+        <v>755.4399487858429</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.721811254812057</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.58477e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-84.928</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3205626207027286</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.291224340317331</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.253281407447089</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.70043654957548</v>
+      </c>
+      <c r="L40" t="n">
+        <v>77.23191125906266</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.25754330700138</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>32.87204498014256</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-14476.93932113545</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-283.7325832948147</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.381774309808566e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9585904550350178</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>85.44800000000004</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5940448133703186</v>
+      </c>
+      <c r="D41" t="n">
+        <v>714.863637655776</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6830412134613038</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.58436e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-84.955</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.06935331645685489</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.859158636493821</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.949797061530425</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.180265061292823</v>
+      </c>
+      <c r="L41" t="n">
+        <v>69.57133399299772</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.1554096332045</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>31.05078729366587</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-13502.75764225445</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-251.4139685920841</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.372725973788375e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9589931484162577</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>84.29000000000002</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.585994257548265</v>
+      </c>
+      <c r="D42" t="n">
+        <v>726.1903473378851</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6938637103939524</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.58408e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-85.033</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.1893543576500098</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9435070427458986</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.053348758644695</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.446606744100502</v>
+      </c>
+      <c r="L42" t="n">
+        <v>78.03636334963925</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.19933669033118</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>31.80878652467958</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-13732.67334728539</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-264.8836980778539</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.350946982634335e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9599547698236929</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>84.62599999999998</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5883301701183942</v>
+      </c>
+      <c r="D43" t="n">
+        <v>816.6990204008541</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7803433557713987</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.58429e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-85.072</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5874310842980298</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.263513613460264</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.154060299690826</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.355606164787722</v>
+      </c>
+      <c r="L43" t="n">
+        <v>76.5484309646145</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.35404138940973</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>34.80039954130096</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-14964.80139226499</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-348.4022764739335</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.339554145431989e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9604898051126254</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>3.210059814721662e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9627495211170048</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>127.1440000000001</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>764.4406176780981</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.58421e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-83.563</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1588128181484924</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9463621973551511</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.85621582417549</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.155244595789438</v>
+      </c>
+      <c r="L23" t="n">
+        <v>49.27083666727413</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.82463100570338</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>26.32576175233953</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-14156.60907079565</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-204.2751582679682</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.836824299068841e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9393328586338238</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>126.216</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9927011892027928</v>
+      </c>
+      <c r="D24" t="n">
+        <v>788.4518616583902</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.031410214770146</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.56412e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-83.821</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3411504199824087</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.057858784307783</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.853639314080611</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.053558006395951</v>
+      </c>
+      <c r="L24" t="n">
+        <v>56.02589409781329</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.01404903950372</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>28.83899630220304</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-15440.27682491637</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-227.7497979481603</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.718775417466821e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9428675605193312</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>122.717</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9651812118542749</v>
+      </c>
+      <c r="D25" t="n">
+        <v>778.8102349960392</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.018797558614281</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.55514e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.947</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1698722169417027</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9433693995119473</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.862990416107186</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.206003110955715</v>
+      </c>
+      <c r="L25" t="n">
+        <v>61.98454667126511</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.98906967238008</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>28.4804752716678</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-15076.16360233346</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-223.4473988572964</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.659261456371368e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9447896744294128</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>120.883</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9507566224123822</v>
+      </c>
+      <c r="D26" t="n">
+        <v>786.433819288342</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.028770320547652</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.54836e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-84.096</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2573662946045169</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.331040603851968</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.004209826464066</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.5788290429016</v>
+      </c>
+      <c r="L26" t="n">
+        <v>70.20916067189182</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.06437747428716</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>29.58943701951071</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-15503.24818225107</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-235.4135023617557</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.595944668508762e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9470377830456328</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>115.995</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.9123120241615802</v>
+      </c>
+      <c r="D27" t="n">
+        <v>940.8957186915666</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.230829049284993</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.544e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-84.226</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1992060104305761</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8659061100085119</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.61763705110867</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.900605420219045</v>
+      </c>
+      <c r="L27" t="n">
+        <v>65.15169910283635</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.02232667868783</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>28.95979972881238</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-14949.68620077269</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-375.872336566319</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.307615251359875e-06</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8542048937062423</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>116.777</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9184625306738811</v>
+      </c>
+      <c r="D28" t="n">
+        <v>831.8250284252558</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.088148653000452</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.54052e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-84.318</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6404010617742047</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.244755352103616</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.393383817986193</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.745790557725597</v>
+      </c>
+      <c r="L28" t="n">
+        <v>77.84965516903853</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.2415176291673</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>32.57228465432224</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-16713.11102416616</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-286.8827626666302</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.301724932490023e-06</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8642360737634867</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>112.283</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.883116780972755</v>
+      </c>
+      <c r="D29" t="n">
+        <v>361.1751390669408</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.4724698435883345</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.54037e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.426</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3332620523280944</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9819341655054736</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.123252562679584</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.007545021771657</v>
+      </c>
+      <c r="L29" t="n">
+        <v>74.24096570731638</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.20451644591891</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>31.90061143838176</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-16136.46163690372</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>132.7396514189293</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.973354677131737e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.944520095795763</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>107.853</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.848274397533505</v>
+      </c>
+      <c r="D30" t="n">
+        <v>357.6419398590171</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.4678479028826517</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.53716e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.496</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2645958349069977</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9017219902471229</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.727889263543213</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.720485418109289</v>
+      </c>
+      <c r="L30" t="n">
+        <v>72.85281803858638</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.13382768216373</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>30.69144075935094</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-15299.46735871453</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>131.3135710145079</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.917609580625833e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9450530178708098</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>104.977</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.825654376140439</v>
+      </c>
+      <c r="D31" t="n">
+        <v>371.8294254764298</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.4864072066262252</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.53629e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.57299999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1608473681537302</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9080810187715076</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.017064238264356</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.437952024632305</v>
+      </c>
+      <c r="L31" t="n">
+        <v>84.34328643491419</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.14466889571358</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>30.87090587850576</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-15215.18828857467</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>112.9092702586106</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.764657481136685e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9455227437045913</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>103.166</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8114106839489079</v>
+      </c>
+      <c r="D32" t="n">
+        <v>784.3228823066049</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.026008906602709</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.53481e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.61799999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4858818281318047</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9785970715954621</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.147096728032547</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.285343099581218</v>
+      </c>
+      <c r="L32" t="n">
+        <v>78.1259004128614</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.21390437859245</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>32.06839441071253</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-15663.8652472838</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-266.9694866154832</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.395003737481824e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9550009412094956</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99.22300000000001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.780398603158623</v>
+      </c>
+      <c r="D33" t="n">
+        <v>477.5944548938966</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.624763315618335</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.53387e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.706</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.7573473565427579</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.822854315755767</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.266179193163782</v>
+      </c>
+      <c r="L33" t="n">
+        <v>85.49060355563836</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.09327901199157</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>30.03828422501105</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-14468.74078383779</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.2419169795772483</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.492726733746164e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9172777787060682</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99.452</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7821997105643991</v>
+      </c>
+      <c r="D34" t="n">
+        <v>797.7243854476395</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.043540030448195</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.53204e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-84.77800000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.4001676686618602</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.152927271710897</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.9875438057797</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.109394555256071</v>
+      </c>
+      <c r="L34" t="n">
+        <v>85.65882565309302</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.27045075152152</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>33.11751636561024</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-15875.79091736646</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-287.5371923104682</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.343280724412004e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9571664789309613</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98.798</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7770559365758506</v>
+      </c>
+      <c r="D35" t="n">
+        <v>288.0147729394255</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.3767653971792313</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.53008e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-84.842</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.8026212992742908</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.584505680395904</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.15193445722186</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.409712612866524</v>
+      </c>
+      <c r="L35" t="n">
+        <v>87.53052867950232</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.38258771142314</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>35.41494009102442</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-16876.55652121696</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>179.1748408365601</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.939926609646586e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9711034212846585</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>95.03299999999996</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7474438432014088</v>
+      </c>
+      <c r="D36" t="n">
+        <v>789.469639496683</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.03274161686307</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.52919e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-84.86199999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2884047273209878</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.073850823114411</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.97117799440497</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.620486508216529</v>
+      </c>
+      <c r="L36" t="n">
+        <v>92.44182578631333</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.27201891195358</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>33.14758910579193</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-15598.73986141956</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-288.204647807479</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.312041895641052e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9584411570238839</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92.06999999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7241395582961048</v>
+      </c>
+      <c r="D37" t="n">
+        <v>760.1286451800105</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9943593100649404</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.52793e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-84.959</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.07883904940250246</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7509282484778455</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.811812607705878</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.912266849052492</v>
+      </c>
+      <c r="L37" t="n">
+        <v>85.59601206041822</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.20429940099785</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>31.89675311092161</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-14845.89365442346</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-265.8799838763717</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.283815292238171e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9596587564260722</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90.416</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7111306864657393</v>
+      </c>
+      <c r="D38" t="n">
+        <v>278.7737549783109</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.3646767957268606</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.5275e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-84.971</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1453075542020658</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9566086628544048</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.893820598997455</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.458725974622966</v>
+      </c>
+      <c r="L38" t="n">
+        <v>94.64255600170026</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.21897423688192</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>32.15973921060205</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-14845.28514461852</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>177.8235217445739</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.843995176999211e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9773054930627708</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>90.17599999999999</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7092430629837031</v>
+      </c>
+      <c r="D39" t="n">
+        <v>786.2563685401575</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.02853818904642</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.52591e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-85.02</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3883237521182217</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.250366068075689</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.03046720832574</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.771343086547224</v>
+      </c>
+      <c r="L39" t="n">
+        <v>100.4010061051088</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.33506109208007</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>34.40345550514105</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-15811.26067139286</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-296.1053317448341</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.261811176964296e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9605759033464433</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>89.93199999999996</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7073239791102994</v>
+      </c>
+      <c r="D40" t="n">
+        <v>833.8697865391646</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.090823495318642</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.52559e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-85.053</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4966249012978276</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.174901781626295</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.17465802632463</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.226629633041304</v>
+      </c>
+      <c r="L40" t="n">
+        <v>92.80058029876579</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.40596399788193</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>35.93456861809906</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-16420.46539105344</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-341.1530482997681</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.251941750184349e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9610217472889362</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>87.96199999999999</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6918297363619199</v>
+      </c>
+      <c r="D41" t="n">
+        <v>799.762469005081</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.046206141471484</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.52297e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-85.123</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.671926698576684</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.362713036006851</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.205540315116692</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.857436947350248</v>
+      </c>
+      <c r="L41" t="n">
+        <v>106.4959436450616</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.3843942276353</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>35.45456092351829</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-16062.84613889791</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-314.2164303563907</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.229772076629964e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9619043666040857</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>86.75200000000001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6823129679733213</v>
+      </c>
+      <c r="D42" t="n">
+        <v>812.1311336508974</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.062386161684676</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.52289e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-85.11199999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.4601298577318467</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.274296297074516</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.346819571812321</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.834531555693543</v>
+      </c>
+      <c r="L42" t="n">
+        <v>98.95250726861256</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.40770087856779</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>35.97378628632862</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-16189.76253744107</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-328.2696044525277</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.231087856751578e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.961851215372903</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>85.67599999999999</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.6738501226955259</v>
+      </c>
+      <c r="D43" t="n">
+        <v>795.8392337648772</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.041073976657793</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.52152e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-85.187</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5305615207392302</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.05712558273266</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.158291421207924</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.456377305570472</v>
+      </c>
+      <c r="L43" t="n">
+        <v>103.5196344469469</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.40101844248152</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>35.82336766127325</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-16001.83436353783</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-316.4902174659518</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.210059814721662e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9627495211170048</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>3.533173101994421e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9542903154861091</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>153.955</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>384.620686790406</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.82179e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-79.95399999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4868496705966273</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9305461352244767</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.486515990899356</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.652863543536844</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13.9010996237902</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.01732849397618</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11.47000536722762</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-6207.442793447139</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>109.1904578233875</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.973273181449503e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9594007059206939</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>103.72</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6737033548764252</v>
+      </c>
+      <c r="D13" t="n">
+        <v>947.7233882305478</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.464046840899635</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.81987e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-81.723</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.04672743795167802</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.700242719078051</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.503605158159591</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.511008396866347</v>
+      </c>
+      <c r="L13" t="n">
+        <v>18.14526817472773</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.13004301724143</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.78275420665694</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-7085.928005201331</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-411.106029439012</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.930271585502584e-06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8090104878817128</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93.56900000000002</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6077685037835733</v>
+      </c>
+      <c r="D14" t="n">
+        <v>819.4893015975176</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.130642811846695</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.77439e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-82.58499999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.04344880580977804</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7067497689889668</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.573202444611359</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.572315850662743</v>
+      </c>
+      <c r="L14" t="n">
+        <v>22.35958682587758</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.73368248333327</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>17.52239242859145</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-8148.78475507964</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-316.9114163071424</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.406417280158856e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9294396848737421</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91.02599999999995</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.591250690136728</v>
+      </c>
+      <c r="D15" t="n">
+        <v>892.6620691152814</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.320889384719252</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.73509e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.063</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5325310100409251</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.083572950115151</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.051245052085944</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.086214529595213</v>
+      </c>
+      <c r="L15" t="n">
+        <v>26.46226441848635</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.14803493896184</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>20.0733355752719</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-9233.578607174244</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-389.77404444386</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.159569684637911e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9359526637122982</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>87.70499999999998</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5696794517878601</v>
+      </c>
+      <c r="D16" t="n">
+        <v>833.1778852984968</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.166232638840162</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.70279e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.426</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5056609429324158</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.186078074515096</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.173132411387343</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.247864822818564</v>
+      </c>
+      <c r="L16" t="n">
+        <v>30.0577205542993</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.35074216504593</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>21.6116908548818</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-9791.983836112289</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-343.08339303088</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.980804043968316e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9407758982001798</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83.68599999999998</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5435744210970738</v>
+      </c>
+      <c r="D17" t="n">
+        <v>832.8067440288039</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.165267684841484</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.68014e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.744</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3418838659433213</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9933868795111681</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.956715802572316</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.149640197916274</v>
+      </c>
+      <c r="L17" t="n">
+        <v>33.54175318950324</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.4801081196277</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>22.72273395339994</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-10126.91612636652</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-348.6475744577259</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.84345606726226e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9447820658291792</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>81.24900000000002</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5277451203273686</v>
+      </c>
+      <c r="D18" t="n">
+        <v>930.0624934864625</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.418129147570494</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.65986e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-83.986</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4688145750425372</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.204920423547245</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.098267300836661</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.4198853832538</v>
+      </c>
+      <c r="L18" t="n">
+        <v>36.56272359303742</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.65942084978334</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>24.46569877432603</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-10775.87667963186</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-441.5431500548907</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.735928600554866e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9479219536291398</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79.82499999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5184956643174954</v>
+      </c>
+      <c r="D19" t="n">
+        <v>965.4500246334014</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.510135460185247</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.64515e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.188</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6730476019988526</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.298915375964702</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.996322071243428</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.039340365109102</v>
+      </c>
+      <c r="L19" t="n">
+        <v>38.40535605278079</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.80683387269596</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>26.11192683974458</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-11360.28440174351</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-479.6695757755296</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.652005862649169e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9505198874354319</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>76.28800000000001</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4955214185963432</v>
+      </c>
+      <c r="D20" t="n">
+        <v>926.8913383382921</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.409884257846457</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.63282e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.34999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5263471096558071</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.160569209941172</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.040775188615683</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.018968229501574</v>
+      </c>
+      <c r="L20" t="n">
+        <v>40.859885876192</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.84182568801585</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>26.5357061921519</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-11370.08337581963</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-451.1228831928716</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.585997180361561e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9525680438297079</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>72.517</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.471027248221883</v>
+      </c>
+      <c r="D21" t="n">
+        <v>860.9089615028547</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.238332443028463</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.62378e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.488</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2782087807888748</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.039474195010175</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.841860140978564</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.322170451791392</v>
+      </c>
+      <c r="L21" t="n">
+        <v>43.69273590542747</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.82035798253104</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>26.27410240961785</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-11075.06631422567</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-397.8849224095842</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.533173101994421e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9542903154861091</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>2.916948161378201e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9825259383785855</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>156.033</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1137.004525504506</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.74005e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-81.417</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5748356467758182</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.05960778332942</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.717089526359442</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.653771215004786</v>
+      </c>
+      <c r="L23" t="n">
+        <v>21.76948728423834</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.57765001895916</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>16.72173307057</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-9558.347632635645</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-486.3167010282042</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.064964654546895e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.906431124011674</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>132.4780000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8490383444527764</v>
+      </c>
+      <c r="D24" t="n">
+        <v>815.8989227281579</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7175863458996626</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.69425e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-82.57299999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3492555959743472</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.14911994905871</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.756190088455087</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.810197594637567</v>
+      </c>
+      <c r="L24" t="n">
+        <v>30.2048480491726</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.27250598703715</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>20.99087772608685</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-11400.5074043747</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-243.1228256670818</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.386627859863791e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.925488981423517</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>126.674</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8118410848987074</v>
+      </c>
+      <c r="D25" t="n">
+        <v>779.5511339715349</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6856183211985341</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.66225e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.05800000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2969679358242454</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.031316870016483</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.827728234924031</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.890325670547747</v>
+      </c>
+      <c r="L25" t="n">
+        <v>35.6541549855468</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.55303441183727</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>23.40079520230523</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-12495.55134428585</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-220.4949299859088</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.126434324001954e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9328994003297738</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>122.492</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7850390622496524</v>
+      </c>
+      <c r="D26" t="n">
+        <v>798.639791209371</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7024068711204142</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.64118e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-83.373</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.526966634684777</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9143536872983123</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.008143124059732</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.028628035828875</v>
+      </c>
+      <c r="L26" t="n">
+        <v>41.73157588427322</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.743258424204</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>25.37558924461288</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-13397.3099027157</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-243.413062532275</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.972672512095646e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9374266052950188</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>120.781</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7740734331840059</v>
+      </c>
+      <c r="D27" t="n">
+        <v>816.1026197040891</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.71776549819973</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.6246e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.59099999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.6215597412208376</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.298853116515421</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.17532902262293</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.382107666008354</v>
+      </c>
+      <c r="L27" t="n">
+        <v>47.9111308234765</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.89947405281634</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>27.26465154911606</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-14245.03114372677</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-264.3498821472357</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.863215574310486e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9407106410451536</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>117.48</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7529176520351465</v>
+      </c>
+      <c r="D28" t="n">
+        <v>808.0933426198592</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7107213071656828</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.61492e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-83.816</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.6607842528268411</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.319963363227983</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.03249923903955</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.199499308497972</v>
+      </c>
+      <c r="L28" t="n">
+        <v>52.79919539965933</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.98571453966041</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>28.43299721607567</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-14663.55578002072</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-263.3703610104587</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.770012462716079e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9438348303464029</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>112.723</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7224305114943634</v>
+      </c>
+      <c r="D29" t="n">
+        <v>781.2899992791764</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6871476601489397</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.60746e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-83.95099999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6185837830408326</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9657436290814027</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.190632654499531</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.225105104117374</v>
+      </c>
+      <c r="L29" t="n">
+        <v>56.28828286672975</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.94885360512119</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>27.92160572166736</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-14189.71567726549</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-245.9948080682785</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.771898486089274e-06</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8228173929287063</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>110.07</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7054276979869641</v>
+      </c>
+      <c r="D30" t="n">
+        <v>779.6335136084688</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6856907744166928</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.59913e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.06699999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3559412103919379</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.032128751127427</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.954389929417107</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.248093053502418</v>
+      </c>
+      <c r="L30" t="n">
+        <v>57.27811431808519</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.99169408013763</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>28.51772345981155</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-14333.15111980325</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-249.7903970828845</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.648794861625218e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9981333489221115</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>108.158</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6931738798843835</v>
+      </c>
+      <c r="D31" t="n">
+        <v>861.1751636590541</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7574069797804349</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.59559e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.18600000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.56605944572541</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.283946272007962</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.166579867458769</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.471956970822943</v>
+      </c>
+      <c r="L31" t="n">
+        <v>64.85297544713929</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.08755977573321</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>29.94838696364187</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-14928.62125492235</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-325.9054018313674</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.611478261242188e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9492233587210586</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>104.332</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.668653425877859</v>
+      </c>
+      <c r="D32" t="n">
+        <v>754.3915694290193</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6634903841691261</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.59046e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.254</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2463238201643122</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.89445080651793</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.829974252835309</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.818962116842231</v>
+      </c>
+      <c r="L32" t="n">
+        <v>58.47775493192427</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.03234012241425</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>29.10729330903288</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-14343.35053086576</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-236.5283340158836</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.579905095827634e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9502722135641067</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>104.526</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6698967526100245</v>
+      </c>
+      <c r="D33" t="n">
+        <v>346.3048172674563</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.3045764634171493</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.58745e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.33799999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.5126535172226138</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.270902487066229</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.30772968572546</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.52742155028443</v>
+      </c>
+      <c r="L33" t="n">
+        <v>69.10106554047931</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.15665508396445</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>31.07178116833471</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-15231.52346824154</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>133.4467600836614</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.852212192578965e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9509468811780504</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101.212</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6486576557523087</v>
+      </c>
+      <c r="D34" t="n">
+        <v>299.158557678455</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.263111140692878</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.58398e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-84.428</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2267232485201308</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.119275411450559</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.094256570402491</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.430304107782438</v>
+      </c>
+      <c r="L34" t="n">
+        <v>70.92965672324281</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.08499578560517</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>29.90825939147066</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-14498.78684531403</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>178.2241384642971</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.199060461458433e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9616299743877114</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99.29599999999999</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6363782020470028</v>
+      </c>
+      <c r="D35" t="n">
+        <v>744.6562629738686</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6549281434420445</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.58086e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-84.47799999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1699191449805814</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.177882813074193</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.850361767590661</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.227434718623907</v>
+      </c>
+      <c r="L35" t="n">
+        <v>69.29584418620011</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.09518927042227</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>30.06843065911325</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-14460.95431466357</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-238.5977960631192</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.491869959400736e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9534823363442003</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98.173</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.629181006581941</v>
+      </c>
+      <c r="D36" t="n">
+        <v>747.3398017097777</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6572883264278759</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.58077e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-84.55</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.1829024069604703</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8217121245833016</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.923089042084646</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.298567079211065</v>
+      </c>
+      <c r="L36" t="n">
+        <v>72.67654801320894</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.12709752425977</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>30.58107480726776</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-14604.73772751724</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-244.246238797235</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.470279622545723e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9544215287585653</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>96.27600000000001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6170233219895791</v>
+      </c>
+      <c r="D37" t="n">
+        <v>741.2473453225141</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6519299868165536</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.57822e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-84.57899999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1875191281508037</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.177907326013075</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.856041126822081</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.416883207610051</v>
+      </c>
+      <c r="L37" t="n">
+        <v>72.08253099740354</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.15007254934933</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>30.96114302908175</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-14682.52046921089</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-241.8434595206919</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.455093855836768e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9549543509790713</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>94.75800000000004</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6072946107554174</v>
+      </c>
+      <c r="D38" t="n">
+        <v>286.668061154538</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.2521256993478888</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.57668e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-84.63200000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3389724207367263</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.054992162070655</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.733668930270764</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.959163884402924</v>
+      </c>
+      <c r="L38" t="n">
+        <v>69.06293447080684</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.13983374339404</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>30.79060657063703</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-14485.50824843448</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>176.8713595510796</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.984356242351823e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9705301398161186</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>96.72000000000003</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6198688738920614</v>
+      </c>
+      <c r="D39" t="n">
+        <v>281.6378922000838</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.2477016457565258</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.57459e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-84.69799999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.303661183557752</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.033849167717337</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.064510478208242</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.322020410244675</v>
+      </c>
+      <c r="L39" t="n">
+        <v>74.04600404857823</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.33375385228582</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>34.37644934918732</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-16154.3909398742</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>178.9529015239474</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.964999241395971e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9730262812967327</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92.48900000000003</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5927528151096244</v>
+      </c>
+      <c r="D40" t="n">
+        <v>281.1403253889771</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.2472640337682306</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.57329e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-84.73699999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2221367188626711</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.6217592092470657</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.91243947813153</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.038954453207784</v>
+      </c>
+      <c r="L40" t="n">
+        <v>72.02067912238269</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.18140532774646</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>31.49494391529041</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-14610.46845341834</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>177.0298908395665</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.948644143619547e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9738446425431295</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92.012</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5896957694846603</v>
+      </c>
+      <c r="D41" t="n">
+        <v>766.8824689850177</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6744761799824329</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.57036e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-84.78700000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.5479085555043246</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.141181211867724</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.106621445796754</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.475691612037422</v>
+      </c>
+      <c r="L41" t="n">
+        <v>81.05592696890399</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.2608556166102</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>32.9346904344378</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-15201.22609870797</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-276.6637205960195</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.380965401563013e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.957803369536288</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>89.89599999999996</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5761345356431008</v>
+      </c>
+      <c r="D42" t="n">
+        <v>271.7289305945652</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.238986674634382</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.57127e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-84.839</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2763935460470526</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.063772525189788</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.209174426616221</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.346155537522304</v>
+      </c>
+      <c r="L42" t="n">
+        <v>80.99620197720108</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.26645523106805</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>33.04113978405893</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-15131.63707616863</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>179.412209314526</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.875092299773471e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9771714620706903</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>89.17500000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5715137182519082</v>
+      </c>
+      <c r="D43" t="n">
+        <v>262.5524962950908</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.2309159641898456</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.57021e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-84.876</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3248306689112525</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.076188676245403</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.152573695275685</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.25880947692925</v>
+      </c>
+      <c r="L43" t="n">
+        <v>78.97688435275302</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.26996277800785</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>33.10816957625536</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-15046.68486187088</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>186.2964953763841</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.916948161378201e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9825259383785855</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>3.57347364853231e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.954390280794259</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>142.614</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>348.7821727803554</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.87562e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-79.666</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.366961488135045</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7344728535012454</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.305516669057611</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.301663182458624</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.60961014693909</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.69042849471109</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.76012889062441</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5675.637107472598</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>137.3879898419361</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.044990029197659e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9662896989536379</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100.243</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7028973312578006</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1122.729298512852</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.218998521521018</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.86036e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-81.589</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7407254614268683</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.28419441979076</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.165334452960385</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.248009816753901</v>
+      </c>
+      <c r="L13" t="n">
+        <v>17.79902109540234</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.11028026646228</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.70741700445989</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6970.264701729548</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-574.1037189463198</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.943178437464874e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9168955139039886</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>88.24000000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6187330837084717</v>
+      </c>
+      <c r="D14" t="n">
+        <v>843.7345394888807</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.419087342575333</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.81188e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-82.41500000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1208609360626289</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.879768997148763</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.797881634399896</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.628180061821881</v>
+      </c>
+      <c r="L14" t="n">
+        <v>20.92427266471121</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.60238351202463</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16.84375057426774</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-7716.640528928568</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-346.3787388668532</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.495844151210855e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9285234756006745</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>85.76999999999998</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6014136059573392</v>
+      </c>
+      <c r="D15" t="n">
+        <v>854.5433269107356</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.450077422531804</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.76874e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-82.971</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4582943823860412</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.242753045030164</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.010984874438387</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.156901884406637</v>
+      </c>
+      <c r="L15" t="n">
+        <v>25.20600717123226</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.02982823978692</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>19.2731098015596</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8713.051459121381</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-362.7651135359671</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.214655057801039e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9358830006248612</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>81.64400000000001</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5724823649852048</v>
+      </c>
+      <c r="D16" t="n">
+        <v>855.7722063819351</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.45360076623198</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.73642e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.34699999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2793207948066145</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9526671092969087</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.653289550951597</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.747880731698404</v>
+      </c>
+      <c r="L16" t="n">
+        <v>27.52436405445816</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.23515113651769</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>20.70684590026306</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-9209.406278370005</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-371.3268098184236</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.03122837915406e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9408105351430178</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80.916</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5673776768059235</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1006.456450222623</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.885630427150404</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.712e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.68600000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.647193551036374</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.479149511399824</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.220330998105737</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.342158731231792</v>
+      </c>
+      <c r="L17" t="n">
+        <v>32.12753694434153</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.53531326335293</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>23.23233749803563</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-10243.33841910732</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-512.2231010550267</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.882071865903075e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9451251787765573</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>76.28500000000003</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5349054090061285</v>
+      </c>
+      <c r="D18" t="n">
+        <v>920.3596048746108</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.638780524640532</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.69367e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-83.928</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5892539157361023</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.20579971014292</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.232922133307423</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.021844659399987</v>
+      </c>
+      <c r="L18" t="n">
+        <v>34.18718747294839</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.6169836842146</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>24.02951989766204</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-10413.31872808785</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-441.7897262211266</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.776945056760763e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9482408226897785</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>72.05900000000003</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.505272974602774</v>
+      </c>
+      <c r="D19" t="n">
+        <v>865.2576339258262</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.480796615917407</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.67726e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.108</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8669029311801114</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.682770595395264</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.00547822619101</v>
+      </c>
+      <c r="L19" t="n">
+        <v>35.87052335486677</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.60470699987309</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>23.9062179925182</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-10173.75882095493</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-398.5184311386078</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.697160895668675e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9505455106039423</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>71.06999999999999</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4983381715680086</v>
+      </c>
+      <c r="D20" t="n">
+        <v>915.7660241883661</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.625610182103737</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.66442e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.288</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4554567317717332</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.233746928739858</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.211603091215871</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.401245553256979</v>
+      </c>
+      <c r="L20" t="n">
+        <v>40.05877285150549</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.79350935367347</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>25.9540879700834</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-10962.09122833541</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-449.0954991430611</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.625566196419015e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9527704634707345</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>70.26800000000003</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4927146002496249</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1020.837303052496</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.926862043764392</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.65438e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.417</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.582621148254729</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.341671295357583</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.902322074182519</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.997720086284586</v>
+      </c>
+      <c r="L21" t="n">
+        <v>40.23841953981763</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.87956933956821</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>27.00848474292571</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-11287.12531539341</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-548.4202070858222</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.57347364853231e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.954390280794259</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>3.422039977735035e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9577455068094651</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>155.4870000000001</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1086.09150455797</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.84397e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-80.36</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1724522089202629</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7816926849252308</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.301432690320966</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.293054448566362</v>
+      </c>
+      <c r="L23" t="n">
+        <v>15.98833859934444</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.60444786453098</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.00936248900688</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-7313.383695658047</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-444.2229238849464</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.893989755513716e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8893284196781287</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>130.846</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.84152372867185</v>
+      </c>
+      <c r="D24" t="n">
+        <v>799.9895873675089</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7365765996789541</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.75614e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-82.139</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2773103774693476</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9613152974731972</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.730300671867965</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.819481721014794</v>
+      </c>
+      <c r="L24" t="n">
+        <v>24.44635738223</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.8759884752196</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>18.32227238467267</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-9757.482711696241</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-236.8943424602339</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.691099528880948e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.91880454146262</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>125.73</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8086206563892798</v>
+      </c>
+      <c r="D25" t="n">
+        <v>805.9948220172535</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7421058157943021</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.70856e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-82.786</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.074487207296174</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.378623896316485</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.191692665621956</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.120683026077312</v>
+      </c>
+      <c r="L25" t="n">
+        <v>30.65456643452785</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.38538859207533</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>21.89847503128922</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-11495.01299186346</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-252.4037152919557</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.316267546161293e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9287083495419479</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>119.708</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7698907304147607</v>
+      </c>
+      <c r="D26" t="n">
+        <v>757.2164319391824</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6971939553540315</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.67791e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-83.16200000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2017053643983824</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.148774862287414</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.966956948845334</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.161365550840937</v>
+      </c>
+      <c r="L26" t="n">
+        <v>36.01577453852055</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.49001009449013</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>22.81249119607194</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-11767.16723840775</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-216.3831562825503</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>4.115220061307796e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9341833414340105</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>115.502</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7428402374475034</v>
+      </c>
+      <c r="D27" t="n">
+        <v>739.8937144875445</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.6812443623603103</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.65727e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.43000000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0921435694704337</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8006552880987349</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.911132927162139</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.879282877063582</v>
+      </c>
+      <c r="L27" t="n">
+        <v>37.75025328186528</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.58149835851941</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>23.67653819694747</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-12059.02033481012</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-206.5156283817154</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.980248030971606e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9380505623270022</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>113.607</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7306527233788032</v>
+      </c>
+      <c r="D28" t="n">
+        <v>764.3547409808771</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7037664301517236</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.6437e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-83.629</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.4834815859317756</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.128393713392375</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.974431832782421</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.436476359734484</v>
+      </c>
+      <c r="L28" t="n">
+        <v>44.89362237475584</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.75576086883666</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>25.5171001678788</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-12896.8185038987</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-232.9274422809891</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.885643224081772e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9409127731355369</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>109.807</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7062133811829922</v>
+      </c>
+      <c r="D29" t="n">
+        <v>729.2701800372918</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6714629264447644</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.63508e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-83.792</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9071858299250994</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.815432822655203</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.0534444533181</v>
+      </c>
+      <c r="L29" t="n">
+        <v>46.25612832610045</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.73426318697842</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>25.27474074184505</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-12594.82157947218</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-207.4870149488065</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.592105281647223e-06</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8352073689632808</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>108.085</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6951385003247855</v>
+      </c>
+      <c r="D30" t="n">
+        <v>743.8638899428018</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6848998328603518</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.62824e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-83.913</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2704488341237034</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.140742721430283</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.887011907181779</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.049682285007532</v>
+      </c>
+      <c r="L30" t="n">
+        <v>47.43081530555657</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.84293315155519</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>26.54934282808241</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-13132.41584036204</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-224.7070976316433</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.677177381748076e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9999740495977159</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>105.667</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6795873610012411</v>
+      </c>
+      <c r="D31" t="n">
+        <v>719.7031927377875</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.662654288075571</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.62254e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-83.98999999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1527155603781452</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8119589227703328</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.94864279596177</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.333199308210784</v>
+      </c>
+      <c r="L31" t="n">
+        <v>51.05136458947229</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.845923889647</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>26.58623899717546</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-13021.20211902497</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-207.5763633571447</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.722280096243427e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9462048918809975</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>103.9400000000001</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6684803231138294</v>
+      </c>
+      <c r="D32" t="n">
+        <v>734.4642787098842</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6762453031144966</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.61677e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.113</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.3327716310013939</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.348387826361179</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.990617648591031</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.798414634125093</v>
+      </c>
+      <c r="L32" t="n">
+        <v>50.00527152833322</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.92420456922811</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>27.58976542245363</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-13407.73164438409</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-224.4271848433825</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.673077680427291e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9478872190449561</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>103.677</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6667888633776451</v>
+      </c>
+      <c r="D33" t="n">
+        <v>758.8469984468147</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6986952713120235</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.61527e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.184</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.6787474647899472</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.434360233993576</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.024071817102727</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.525283747516431</v>
+      </c>
+      <c r="L33" t="n">
+        <v>55.86926507748024</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.01340184433441</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>28.82959358580806</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-13924.8385968852</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-249.3966819639426</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.646095659671054e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9489188871614367</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>100.934</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6491475171557746</v>
+      </c>
+      <c r="D34" t="n">
+        <v>744.8029547207409</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6857644605404305</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.61226e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-84.249</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3276181384431741</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.103281480349789</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.853633461602472</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.140770967853316</v>
+      </c>
+      <c r="L34" t="n">
+        <v>54.08959453609101</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.00884948439409</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>28.76362767728206</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-13762.51679414403</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-240.7398745661293</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.618877796593501e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9498751442996644</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>100.679</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6475075086663189</v>
+      </c>
+      <c r="D35" t="n">
+        <v>758.3588243800892</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6982457934690638</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.60879e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-84.309</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5855119891887919</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.244891054985618</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.23564402554166</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.673241269583246</v>
+      </c>
+      <c r="L35" t="n">
+        <v>59.42228396367067</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.08937905454511</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>29.97692477266407</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-14255.21617138809</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-255.8639319607357</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.593102726972235e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.950780547666497</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98.35199999999998</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6325416272743054</v>
+      </c>
+      <c r="D36" t="n">
+        <v>749.6850009653363</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6902595203250868</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.60783e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-84.40900000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.377448655860229</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.121517452732289</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.125363248757869</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.481750619132059</v>
+      </c>
+      <c r="L36" t="n">
+        <v>59.5722292407458</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.1091289430927</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>30.29026067009061</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-14262.61079368881</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-252.4686062197476</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.561030430931987e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9520786928258375</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>96.30099999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6193508138944088</v>
+      </c>
+      <c r="D37" t="n">
+        <v>760.2088736669622</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6999491944063779</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.60631e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-84.465</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.7099478657649568</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.47195443880968</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.599293104277672</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.714287781044814</v>
+      </c>
+      <c r="L37" t="n">
+        <v>62.09335464102667</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.14577355566854</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>30.88931015537552</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-14416.03887302562</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-266.1052652864317</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.539173651349342e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9529330964957867</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>94.339</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6067323956343614</v>
+      </c>
+      <c r="D38" t="n">
+        <v>744.0326296862219</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6850551970655886</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.60393e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-84.533</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2803089928407386</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.085174505604829</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.205143872390861</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.553328053875496</v>
+      </c>
+      <c r="L38" t="n">
+        <v>64.00536129478485</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.10473863551152</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>30.22004329418343</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-13952.92705948735</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-255.1986057087718</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.514813113505032e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9538487353078851</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91.86200000000002</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5908018033661977</v>
+      </c>
+      <c r="D39" t="n">
+        <v>715.5158621922557</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6587988757756322</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.60207e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-84.592</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1487432716402615</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.008077297412275</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.740922904542704</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.108672279558191</v>
+      </c>
+      <c r="L39" t="n">
+        <v>59.8506151899095</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.08303827008297</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>29.87769564707455</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-13660.22456612663</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-233.3680019123356</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.493103631632429e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9546866090518605</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91.96699999999998</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5914771009795027</v>
+      </c>
+      <c r="D40" t="n">
+        <v>875.4021261873871</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8060113926990601</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.6022e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-84.648</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.5060991170268129</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.456941126823257</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.322919831960715</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.451109389895034</v>
+      </c>
+      <c r="L40" t="n">
+        <v>65.00373398950133</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.21451588060602</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>32.07938448077157</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-14606.62462238206</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-378.1136227460678</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.476259962158232e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9554258153262858</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>88.40000000000003</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5685362763446461</v>
+      </c>
+      <c r="D41" t="n">
+        <v>708.0293472975609</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6519057964510299</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.60188e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-84.703</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2066005261241105</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8818063340206385</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.862697365775452</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.226556745012293</v>
+      </c>
+      <c r="L41" t="n">
+        <v>66.47584130040504</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.09506374441214</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>30.06644783542827</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-13508.93400573216</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-233.6221495814944</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>3.45904275648366e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9561647101586777</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>87.82999999999998</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5648703750152742</v>
+      </c>
+      <c r="D42" t="n">
+        <v>730.1447981963149</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6722682160132332</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.59964e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-84.744</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2747484608873234</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9980755596547854</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.869539600957623</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.176747817082969</v>
+      </c>
+      <c r="L42" t="n">
+        <v>62.7947401717645</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.15756103992196</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>31.08707019281993</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-13874.02972793589</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-256.4729960099629</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.442378256849942e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9567788086081715</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>86.04000000000002</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5533581585598795</v>
+      </c>
+      <c r="D43" t="n">
+        <v>713.1340042720352</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6566058212215503</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.60098e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-84.825</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4575814987810635</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.7636684644524082</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.97294173691592</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.421379707766566</v>
+      </c>
+      <c r="L43" t="n">
+        <v>70.25433658294513</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.14656903179977</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>30.90257683236327</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-13663.81967361734</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-244.6432241547537</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>3.422039977735035e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9577455068094651</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>3.539633503169021e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9557811164962613</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>147.4259999999999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>331.6494925038148</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.92483e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-78.999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.05832978375257965</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3501916478507179</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.045387552204705</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.859219990728348</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.35399294889431</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.08308845444594</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.648945249555137</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5134.761399588653</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>157.6508476808662</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.1190560620034e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9719902516259846</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100.088</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6789033142050928</v>
+      </c>
+      <c r="D13" t="n">
+        <v>970.0419746358807</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.924901127731178</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.88417e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-81.467</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1610562925012994</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.878908599872532</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.764882583419437</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.827204371187795</v>
+      </c>
+      <c r="L13" t="n">
+        <v>17.17911827594043</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.96212121317983</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.16607470847489</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6697.681925217379</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-437.8676111014491</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.49665477798724e-06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8486630098005334</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92.08699999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6246320187755215</v>
+      </c>
+      <c r="D14" t="n">
+        <v>845.6708954847904</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.549893530969486</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.8179e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-82.496</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4734661030547845</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.211835147549638</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.885236992423122</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.990276554438986</v>
+      </c>
+      <c r="L14" t="n">
+        <v>21.81647924218193</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.74631749462222</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>17.59058442389384</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-8090.892774284126</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-346.219244741732</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.487309756219125e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9291018201345514</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>86.22900000000004</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5848968295958656</v>
+      </c>
+      <c r="D15" t="n">
+        <v>755.3579465656858</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.277579081647464</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.76729e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-83.08199999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2257247119895066</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.725495798073172</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.74489988381427</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.02747996409805</v>
+      </c>
+      <c r="L15" t="n">
+        <v>26.22352976007612</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.07557598061601</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>19.57514214166586</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8829.035159041612</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-273.8130042497252</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.182032860857763e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9369465305917135</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83.91899999999998</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5692279516503196</v>
+      </c>
+      <c r="D16" t="n">
+        <v>887.0750957258175</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.674736780173466</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.73217e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-83.53700000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4994055575734559</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9376938281383639</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.992032588693461</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.880324703570487</v>
+      </c>
+      <c r="L16" t="n">
+        <v>30.09344380231113</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.38996086624113</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>21.93689010589567</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-9770.280128072411</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-396.8949691270242</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.9729317622861e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9427244016307051</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80.80300000000005</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5480919240839478</v>
+      </c>
+      <c r="D17" t="n">
+        <v>816.398664445072</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.461630977576971</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.70654e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-83.833</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3289320236214637</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.030166638636357</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.081641892814186</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.287583005189795</v>
+      </c>
+      <c r="L17" t="n">
+        <v>34.7458248487683</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.56119821939389</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>23.4792237554284</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-10307.51734490165</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-340.6446095385166</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.836214915534863e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9465849246484479</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>77.88200000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5282785940064849</v>
+      </c>
+      <c r="D18" t="n">
+        <v>785.7308553476749</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.369160433250586</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.68647e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-84.069</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2258014914453887</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.018777000642412</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.953659508152739</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.261310470619143</v>
+      </c>
+      <c r="L18" t="n">
+        <v>36.9291831417116</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.67500104510698</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>24.62982932380391</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-10652.90482962498</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-319.856054094438</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.731376418170977e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9496478548149111</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>75.80199999999996</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5141698207914479</v>
+      </c>
+      <c r="D19" t="n">
+        <v>808.1480094006403</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.436753342510677</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.6731e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.26600000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2866525502480102</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.334255229158117</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.222604763808668</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.314889060921618</v>
+      </c>
+      <c r="L19" t="n">
+        <v>40.61492801685059</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.80491201635911</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>26.0890428156437</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-11149.28377621135</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-345.5395398724162</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.65152339941978e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9521606934071773</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>73.09899999999999</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4958351986759461</v>
+      </c>
+      <c r="D20" t="n">
+        <v>825.2785051178673</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.488405752975408</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.66119e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.38200000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2788963290648758</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.005641316306479</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.082315998197027</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.141565419422775</v>
+      </c>
+      <c r="L20" t="n">
+        <v>41.39207985981636</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.85530636547489</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>26.70265629484792</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-11274.80434193135</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-365.8887172580376</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.598723325225615e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9537048599395087</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>72.19800000000004</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.489723657970779</v>
+      </c>
+      <c r="D21" t="n">
+        <v>830.6105183360967</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.504483007241576</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.65386e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-84.55200000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4708472557105602</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.247027035798391</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.197560301350448</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.600923440076155</v>
+      </c>
+      <c r="L21" t="n">
+        <v>46.36607603348832</v>
+      </c>
+      <c r="M21" t="n">
+        <v>87.97109499077021</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>28.22794989551157</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-11794.19885323564</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-375.085337082257</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.539633503169021e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9557811164962613</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>2.842372516899024e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9910300562386715</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>151.935</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1052.171167114146</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.72978e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-81.902</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.08589381367574381</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7322018736644139</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.531328785598934</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.876668637583507</v>
+      </c>
+      <c r="L23" t="n">
+        <v>25.37966137844364</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.6967744138974</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>17.3261815109941</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-9647.422723588208</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-421.3240971907662</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.840721463029202e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9125969666869889</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>128.668</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8468621449962155</v>
+      </c>
+      <c r="D24" t="n">
+        <v>781.1239126223537</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7423924329392053</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.6855e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-82.98999999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4864740162624521</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.022808757779163</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.90887649998498</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.303926665768761</v>
+      </c>
+      <c r="L24" t="n">
+        <v>35.73218651067575</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.42191370389277</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>22.2091504234214</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-11709.43650743262</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-224.9371072497003</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.217473612483152e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9308786942661749</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>120.865</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.795504656596571</v>
+      </c>
+      <c r="D25" t="n">
+        <v>728.4945227182717</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6923726343085016</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.6613e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-83.38500000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.02683039209782336</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9317218555363775</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.828471411141543</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.086516975556523</v>
+      </c>
+      <c r="L25" t="n">
+        <v>39.4096394709042</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.60855465954982</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>23.94472615510886</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-12376.45852350311</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-188.8578626203439</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>4.017273873978845e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9368504156747148</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>118.387</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7791950505150229</v>
+      </c>
+      <c r="D26" t="n">
+        <v>737.1798023008405</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7006272604131025</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.64506e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-83.596</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3009396598473824</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.8979467968107356</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.817841343633992</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.062963638468355</v>
+      </c>
+      <c r="L26" t="n">
+        <v>43.77408767666498</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.73643486088176</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>25.29901472024976</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-12926.94694102056</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-202.222479977831</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.908531247009425e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9400894695746561</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>117.028</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7702504360417282</v>
+      </c>
+      <c r="D27" t="n">
+        <v>760.1901183283303</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7224966261082314</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.63705e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-83.76300000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5592052707371536</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.215474335402579</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.154582474546298</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.28809611649389</v>
+      </c>
+      <c r="L27" t="n">
+        <v>48.08071721584412</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.90473245000915</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>27.33313767076428</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-13841.23949737114</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-227.9668863052682</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.335455556498187e-06</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8709002125473967</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>111.347</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.732859446473821</v>
+      </c>
+      <c r="D28" t="n">
+        <v>719.8837480031784</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.684188818799937</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.63134e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-83.928</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.9804451187032809</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.868976932712027</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.30775358718872</v>
+      </c>
+      <c r="L28" t="n">
+        <v>52.01734549078425</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.83408140324777</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>26.44073728515496</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-13149.56585572598</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-199.1170005852042</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.864454460717978e-06</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8134851209493507</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>109.383</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7199328660282356</v>
+      </c>
+      <c r="D29" t="n">
+        <v>751.6825603512031</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7144109094082942</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.62561e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-84.017</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5391840590059037</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.300624804363292</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.45614081551629</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.601116585679592</v>
+      </c>
+      <c r="L29" t="n">
+        <v>54.64359704910316</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.97585160834232</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>28.29433916885763</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-13956.66516406941</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-232.6627737285249</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.721556559962741e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9464071651728816</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>105.665</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6954618751439762</v>
+      </c>
+      <c r="D30" t="n">
+        <v>721.5760599432863</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.6857972186430438</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.62244e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-84.142</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.138500489160394</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.092264103585721</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.785199391950761</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.144351074743126</v>
+      </c>
+      <c r="L30" t="n">
+        <v>51.69415367677249</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.96396673717531</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>28.12903963097849</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-13686.82832258121</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-211.5407438617646</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.673586660074046e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9481880184656595</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>103.884</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6837397571329846</v>
+      </c>
+      <c r="D31" t="n">
+        <v>737.9830772418265</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7013907055312473</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.62047e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-84.211</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4725324832443177</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.170954154732291</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.855839346327214</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.029462387368145</v>
+      </c>
+      <c r="L31" t="n">
+        <v>52.83968307202336</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.00037049837363</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>28.64156342049365</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-13804.79004941218</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-230.4719000274603</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.643612089453659e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9493289101683569</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>100.768</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6632309869352023</v>
+      </c>
+      <c r="D32" t="n">
+        <v>714.9567089991547</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6795060835587334</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.61863e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-84.276</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1352510484158554</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.162536144610618</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.281336380884205</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.50571657208366</v>
+      </c>
+      <c r="L32" t="n">
+        <v>58.58114754623783</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.01240660309304</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>28.81514625713078</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-13755.97854030204</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-214.3867320400951</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.617815616241259e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9503068576419258</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99.03199999999998</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6518050482114061</v>
+      </c>
+      <c r="D33" t="n">
+        <v>725.1250434507505</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6891702283000164</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.6172e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-84.386</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1328430971679162</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9428907294654837</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.125997324437837</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.435388849627961</v>
+      </c>
+      <c r="L33" t="n">
+        <v>61.1053935006763</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.04229837464453</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>29.25546972939734</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-13843.93283311992</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-226.9377624104708</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.58150876896356e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9517458764680145</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99.37199999999996</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.654042847270214</v>
+      </c>
+      <c r="D34" t="n">
+        <v>737.4572575812174</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7008909582685929</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.61548e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-84.40600000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.501081674075603</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.130024801171136</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.255924385283577</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.526964797319383</v>
+      </c>
+      <c r="L34" t="n">
+        <v>61.84809723145336</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.13913333434772</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>30.77900918731363</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-14493.37747334547</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-241.2724346065032</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.569231144901565e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9521874686474737</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>96.66500000000002</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6362260177049397</v>
+      </c>
+      <c r="D35" t="n">
+        <v>729.3201911032643</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6931573625074858</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.61366e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-84.482</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3562339036299769</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.082936589636582</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.036063820203798</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.315550488970178</v>
+      </c>
+      <c r="L35" t="n">
+        <v>60.5310899400901</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.14187484781961</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>30.82445305451083</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-14382.64092711181</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-237.6606518698031</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>3.542281346934422e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.953230418026092</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93.41800000000001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6148550366933229</v>
+      </c>
+      <c r="D36" t="n">
+        <v>688.6376407494784</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6544920277926328</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.61342e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-84.527</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.04594459834366993</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8471982430348479</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.837057934566277</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.361789380249925</v>
+      </c>
+      <c r="L36" t="n">
+        <v>63.06772815281365</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.04751394560952</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>29.33367906832878</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-13528.19225082068</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-205.148271605513</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.527569266650081e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.953851472500422</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>95.50299999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6285780103333661</v>
+      </c>
+      <c r="D37" t="n">
+        <v>780.9307713246955</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7422088684169156</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.61245e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-84.58499999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.953260025425648</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.638662884025179</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.472401677363899</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.493302894722132</v>
+      </c>
+      <c r="L37" t="n">
+        <v>64.58687898031374</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.28065316677706</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>33.31415114718229</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-15366.03192059773</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-289.7652392695025</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>3.508072820551902e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.954636768680206</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93.28700000000003</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6139928258794881</v>
+      </c>
+      <c r="D38" t="n">
+        <v>314.6851323848542</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.2990816914779754</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.61202e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-84.648</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.329730002088063</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.233159010663049</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.344681462730618</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.408350972405506</v>
+      </c>
+      <c r="L38" t="n">
+        <v>66.8249629500563</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.22652662564285</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>32.29678048461521</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-14747.40100343068</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>134.1794923037629</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.726298041975357e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9636861098518151</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92.59300000000002</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6094250830947445</v>
+      </c>
+      <c r="D39" t="n">
+        <v>743.359941360158</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7065009616249197</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.61212e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-84.706</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5249888641857724</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.301741040405934</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.386259228231592</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.46987992931944</v>
+      </c>
+      <c r="L39" t="n">
+        <v>66.69610672591601</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.23707281632849</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>32.49010951883623</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-14718.15831226745</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-262.8513782177631</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.472231600958838e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9561750058948451</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>90.75699999999995</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5973409681771806</v>
+      </c>
+      <c r="D40" t="n">
+        <v>876.7465173554039</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8332736580875052</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.61205e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-84.77200000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6165431194578478</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.169410769897473</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.289321268072667</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.52852005495124</v>
+      </c>
+      <c r="L40" t="n">
+        <v>71.58379072361994</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.27434074236413</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>33.19221537660921</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-14929.60479392341</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-383.8352112769206</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>3.453166066346132e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9570047943069957</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>89.47899999999998</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5889294764208377</v>
+      </c>
+      <c r="D41" t="n">
+        <v>309.259325442144</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.2939249193554395</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.60874e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-84.791</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6148948953477004</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.167841836417439</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.252716527022888</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.498050842256809</v>
+      </c>
+      <c r="L41" t="n">
+        <v>69.82922835043733</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.29242628008754</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>33.54397784248615</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-14975.82267919341</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>129.7799247976549</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.612330250239521e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9676744541342233</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>86.88099999999997</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5718300589067692</v>
+      </c>
+      <c r="D42" t="n">
+        <v>720.408097933534</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6846871692078784</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.61001e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-84.846</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2324892365175061</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.996847922834762</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.227311044928475</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.452877909713164</v>
+      </c>
+      <c r="L42" t="n">
+        <v>69.85623554556142</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.22900338411642</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>32.34197673372037</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-14283.62846338707</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-252.0260010260122</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>3.426062937967993e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9580991501604325</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>85.89600000000002</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5653470233981638</v>
+      </c>
+      <c r="D43" t="n">
+        <v>244.5958680784024</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.2324677540340423</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.60994e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-84.86</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3632715296455039</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.251512927527007</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.378854929313955</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.619448488318949</v>
+      </c>
+      <c r="L43" t="n">
+        <v>70.59258547796802</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.26054355963502</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>32.92877834850029</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-14444.86047287876</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>188.0131557241154</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.842372516899024e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9910300562386715</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.9615519162759297</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>109.144</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>258.6021232568511</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.834e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-81.051</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.06368801255861183</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6128739397867219</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.331913211709849</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.303724796468092</v>
+      </c>
+      <c r="L12" t="n">
+        <v>15.10752563238996</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.34755638349567</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12.28812254041511</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5813.034705871516</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>192.6214760913499</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.353009419617842e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9946098306492175</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>89.58800000000002</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8208238657186837</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1291.70016960623</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.994932575720874</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.73136e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.092</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6460453725209708</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.415212628814962</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.108251107166484</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.106380678769282</v>
+      </c>
+      <c r="L13" t="n">
+        <v>25.61434889727027</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.03956231471548</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>19.33659428884635</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-8647.872406315368</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-748.7551024439899</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.160469132995124e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9357369062570795</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>81.76600000000002</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7491570768892474</v>
+      </c>
+      <c r="D14" t="n">
+        <v>995.6591173018346</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.850158323382818</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.683e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-83.806</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3449166687044798</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.216922438045941</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.939951878640338</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.997214950294377</v>
+      </c>
+      <c r="L14" t="n">
+        <v>32.5820616156744</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.45931583278877</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>22.53653611026656</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-9808.825267630049</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-502.581114190468</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.837920383609075e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9451749698400085</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78.61800000000005</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7203144469691422</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1052.412439485786</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.069620257682493</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.65526e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-84.142</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5332000933665396</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.408815121063665</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.131843190763319</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.143875779299127</v>
+      </c>
+      <c r="L15" t="n">
+        <v>37.21856224599434</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.67444672224893</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>24.62395206506019</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-10553.44763209426</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-560.3888181596708</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.688402224524403e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9496075244343175</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>74.786</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6852048669647438</v>
+      </c>
+      <c r="D16" t="n">
+        <v>972.8025915110054</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.761773411832314</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.63917e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-84.42400000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3804472063088298</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.104422476028958</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.800309221911419</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.062615258812547</v>
+      </c>
+      <c r="L16" t="n">
+        <v>42.55129164322822</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.77620126723748</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>25.75188361344238</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-10847.43029960969</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-496.0204879033968</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.580863380424837e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9531556670278618</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>71.185</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6522117569449535</v>
+      </c>
+      <c r="D17" t="n">
+        <v>985.6463842652802</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.811439642691208</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.62756e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-84.581</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2331167996821988</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8825543621714648</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.668613271302677</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.767341105985299</v>
+      </c>
+      <c r="L17" t="n">
+        <v>42.7585441020376</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.82889808127788</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>26.37755201383237</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-10925.45541698337</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-514.599005333274</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.515607192078831e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9552877675534639</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>70.31399999999996</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6442314740159786</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1156.93975164432</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.473821549002576</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.62081e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-84.77500000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3957024322300078</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.248273921621915</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.035198630167017</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.818188467867079</v>
+      </c>
+      <c r="L18" t="n">
+        <v>47.87513209381097</v>
+      </c>
+      <c r="M18" t="n">
+        <v>88.00106853694072</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>28.65157334687012</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-11732.96445154462</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-673.9332343207398</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.451356492579932e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9576837039638305</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>67.03799999999995</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6142160815069995</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1055.025519781767</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4.079724893572839</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.61662e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-84.881</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4474356256169449</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.898629288362466</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.845110574505296</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.930993900605347</v>
+      </c>
+      <c r="L19" t="n">
+        <v>49.68107767055674</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.99679155326329</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>28.59035060636527</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-11509.33134619516</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-589.4332525947967</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.414772267556041e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9590654145840383</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>59.34199999999998</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5437037308509857</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1062.448500947815</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4.108429148095432</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.61241e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-84.98399999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.03272061506378311</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.065013422387355</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.245747161035312</v>
+      </c>
+      <c r="L20" t="n">
+        <v>46.63772311722867</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.70829093751166</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>24.98799812700887</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-9790.787598396972</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-602.5190530012495</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.378478295031829e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.960453219125349</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>62.63499999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5738748808912995</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1178.305586961594</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4.556442043560744</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.6101e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-85.069</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3198664355744759</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.356484017700686</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.046790864949957</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.214822156642091</v>
+      </c>
+      <c r="L21" t="n">
+        <v>55.22623998671386</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.08199058568086</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>29.86136320688936</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-11700.28864134019</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-712.5574354711102</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.351133738062318e-07</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9615519162759297</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
